--- a/dados_injetaveis.xlsx
+++ b/dados_injetaveis.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elton.freitas\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ejonh\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A70AD58F-1506-4D04-A807-DE5FC17BAD46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3BFBA8B-EFE5-4EF3-B8A4-6D5446BC3C7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6531" uniqueCount="1431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6644" uniqueCount="1487">
   <si>
     <t>MEDICAMENTO</t>
   </si>
@@ -5328,14 +5328,182 @@
     <t>09 mL de Cloreto de Sódio 0,9% ou  Soro Glicosado 5%.</t>
   </si>
   <si>
-    <t>Incompatibilidades</t>
+    <t>Cloridrato de Amiodarona: Requer pH estritamente ácido (3,5 a 4,5). O contato com qualquer base ou soluções tamponadas (Furosemida, Bicarbonato) causa precipitação imediata da amiodarona base livre. Medicamentos incompatíveis:  Aminofilina, Ampicilina Sódica, Lactato de Ciprofloxacino, Furosemida, Heparina Sódica, Piperacilina + Tazobactam, Bicarbonato de Sódio, .</t>
+  </si>
+  <si>
+    <t>Cloreto de Potássio: Eletrólito concentrado puro. Quebra o equilíbrio coloidal da anfotericina e reage reduzindo a solubilidade do veículo da fenitoína. Medicamentos incompatíveis: Anfotericina B, Fenitoína Sódica.</t>
+  </si>
+  <si>
+    <t>Cloridrato de Dobutamina: Catecolamina ácida sensível à oxidação. Meios alcalinos (Bicarbonato, Furosemida, Fenitoína) causam inativação e escurecimento químico da solução. Medicamentos incompatíveis: Aciclovir Sódico, Aminofilina, Ampicilina Sódica, Diazepam, Furosemida, Heparina Sódica, Succinato Sódico de Hidrocortisona, Fenitoína Sódica, Piperacilina + Tazobactam, Bicarbonato de Sódio, .</t>
+  </si>
+  <si>
+    <t>Cloridrato de Dopamina: Apresenta o mesmo comportamento crítico da dobutamina, oxidando-se e precipitando na presença de bases fortes. Medicamentos incompatíveis: Aciclovir Sódico, Aminofilina, Ampicilina Sódica, Ampicilina+Sulbactam, Anfotericina B, Diazepam, Furosemida, Fenitoína Sódica, Bicarbonato de Sódio, , Tiopental Sódico.</t>
+  </si>
+  <si>
+    <t>Citrato de Fentanila: Sedativo opioide com pH ácido. Sofre precipitação da base livre em contato com o pH 12 da Fenitoína Sódica. Medicamentos incompatíveis: Diazepam, Fenitoína Sódica.</t>
+  </si>
+  <si>
+    <t>Lactato de Ciprofloxacino: Solução ácida (pH 3,5 a 4,6). Precipita imediatamente com soluções alcalinas (Bicarbonato, Furosemida) ou por complexação com íons bivalentes (Cálcio). MEDICAMENTOS INCOMPATÍVEIS: Aminofilina, Cloridrato de Amiodarona, Anfotericina B, Gliconato de Cálcio, Furosemida, Heparina Sódica, Hidrocortisona, Fenitoína Sódica, Bicarbonato de Sódio, Teicoplanina.</t>
+  </si>
+  <si>
+    <t>Cloridrato de Doxorrubicina: Agente antineoplásico que forma complexos físicos insolúveis imediatos com heparina e compostos sódicos tamponados. MEDICAMENTOS INCOMPATÍVEIS: Furosemida, Heparina Sódica, Piperacilina + Tazobactam.</t>
+  </si>
+  <si>
+    <t>Aciclovir Sódico: pH muito alcalino (10,5 a 11,5). Precipita imediatamente ao entrar em contato com soluções ácidas ou sais na forma de cloridratos. MEDICAMENTOS INCOMPATÍVEIS: Anfotericina B, Cloridrato de Dobutamina, Cloridrato de Dopamina, Lactato de Haloperidol, , Cloridrato de Midazolam, Sulfato de Morfina, Bitartarato de Norepinefrina, Cloridrato de Ondansetrona.</t>
+  </si>
+  <si>
+    <t>Adenosina: Bastante estável em Y com a maioria dos fármacos, mas o contato com o complexo da Anfotericina B quebra o equilíbrio de solubilidade. MEDICAMENTOS INCOMPATÍVEIS: Anfotericina B.</t>
+  </si>
+  <si>
+    <t>Cloridrato de Alfentanila: O sal de alfentanila interage eletrostaticamente com a macromolécula aniônica da heparina, gerando risco de opalescência. MEDICAMENTOS INCOMPATÍVEIS:Heparina Sódica.</t>
+  </si>
+  <si>
+    <t>Sulfato de Amicacina: Sendo um aminoglicosídeo catiônico, precipita na presença de polímeros aniônicos (Heparina) e soluções de pH nitidamente alcalino (Bicarbonato, Fenitoína). MEDICAMENTOS INCOMPATÍVEIS:Anfotericina B, Heparina Sódica, Fenitoína Sódica, Piperacilina + Tazobactam, Bicarbonato de Sódio.</t>
+  </si>
+  <si>
+    <t>Aminofilina: Solução de caráter básico. Sofre neutralização ácido-base com deposição de cristais ao cruzar com a linha de cloridratos ou vasopressores em Y. MEDICAMENTOS INCOMPATÍVEIS: Lactato de Ciprofloxacino, Cloridrato de Dobutamina, Cloridrato de Dopamina, Cloridrato de Hidralazina, Cloridrato de Midazolam, Bitartarato de Norepinefrina, Cloridrato de Ondansetrona, Fenitoína Sódica, Cloridrato de Prometazina.</t>
+  </si>
+  <si>
+    <t>Anfotericina B (Deoxicolato): Altamente sensível a eletrólitos (salting-out). MEDICAMENTOS INCOMPATÍVEIS: Aciclovir Sódico, Adenosina, Sulfato de Amicacina, Gliconato de Cálcio, Lactato de Ciprofloxacino, Cloridrato de Difenidramina, Cloridrato de Dopamina, Furosemida, Sulfato de Gentamicina, Heparina Sódica, Sulfato de Magnésio, Cloridrato de Metoclopramida, Sulfato de Morfina, Paclitaxel, Piperacilina + Tazobactam, Cloreto de Potássio, Cloridrato de Ranitidina, Bicarbonato de Sódio, Cloridrato de Vancomicina.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Formulações Lipídicas/Lipossomais: Embora o Stabilis aponte incompatibilidade com Amicacina, Gentamicina e Heparina para os complexos lipídicos, eles possuem uma proteção micelar que reduz a velocidade de precipitação frente a eletrólitos isolados, mas o contato em Y deve ser evitado. MEDICAMENTOS INCOMPATÍVEIS: Amicacina, Gentamicina e Heparina sódica</t>
+  </si>
+  <si>
+    <t>Ampicilina Sódica: Instável em soluções hidrofílicas ácidas. Sofre degradação acelerada ou complexação cruzada com agentes cardiovasculares e vancomicina. MEDICAMENTOS INCOMPATÍVEIS: Cloridrato de Amiodarona, Cloridrato de Dobutamina, Cloridrato de Dopamina, Fluconazol, Cloridrato de Hidralazina, Cloridrato de Midazolam, Cloridrato de Ondansetrona, Cloridrato de Vancomicina, Cloridrato de Verapamil.</t>
+  </si>
+  <si>
+    <t>Ampicilina Sódica + Sulbactam Sódico: A adição do sulbactam mantém o caráter alcalino da mistura, perpetuando a incompatibilidade física com cloridratos e aminoglicosídeos em Y. MEDICAMENTOS INCOMPATÍVEIS: Cloridrato de Amiodarona, Cloridrato de Dobutamina, Cloridrato de Dopamina, Sulfato de Gentamicina, Idarubicina, Cloridrato de Midazolam, Cloridrato de Vancomicina.</t>
+  </si>
+  <si>
+    <t>Besilato de Atracúrio: Instável em ambientes com pH elevado. Soluções alcalinas quebram a estabilidade do besilato, inativando o bloqueador neuromuscular. MEDICAMENTOS INCOMPATÍVEIS: Aminofilina, Fenitoína Sódica, Bicarbonato de Sódio.</t>
+  </si>
+  <si>
+    <t>Sulfato de Atropina: O pH extremamente elevado da Fenitoína Sódica (~12) quebra o equilíbrio iônico do sulfato de atropina em Y. MEDICAMENTOS INCOMPATÍVEIS: Fenitoína Sódica.</t>
+  </si>
+  <si>
+    <t>Azitromicina: Solução incompatível com o sistema coloidal da Anfotericina B e com o veículo tamponado da Furosemida Sódica. MEDICAMENTOS INCOMPATÍVEIS: Anfotericina B, Furosemida.</t>
+  </si>
+  <si>
+    <t>Aztreonam: Apresenta risco de opalescência ou redução de potência por interação física direta quando misturado com vancomicina ou metronidazol na mesma linha. MEDICAMENTOS INCOMPATÍVEIS: Metronidazol, Cloridrato de Vancomicina.</t>
+  </si>
+  <si>
+    <t>Cloridrato de Bupivacaína: O anestésico local precipita na forma de base livre se exposto ao pH da Fenitoína ou se misturado ao veículo lipofílico do Diazepam. MEDICAMENTOS INCOMPATÍVEIS: Diazepam, Cetoprofeno, Fenitoína Sódica.</t>
+  </si>
+  <si>
+    <t>Cloridrato de Clorpromazina: Incompatibilidade catiônica-aniônica com a Heparina e reação de neutralização com o Fenobarbital Sódico. MEDICAMENTOS INCOMPATÍVEIS: Heparina Sódica, Fenobarbital Sódico.</t>
+  </si>
+  <si>
+    <t>Cloridrato de Clonidina: Incompatibilidade física relacionada à estabilidade do veículo e pH quando cruzado com Diazepam ou Cetoprofeno em Y. MEDICAMENTOS INCOMPATÍVEIS: Diazepam, Cetoprofeno.</t>
+  </si>
+  <si>
+    <t>Diazepam (Veículo Cossolvente): Não possui sal aquoso livre. O propilenoglicol precipita o diazepam molecular insolúvel ao entrar em contato em Y com qualquer solução puramente aquosa da lista. MEDICAMENTOS INCOMPATÍVEIS: Cloridrato de Bupivacaína, Cloridrato de Clonidina, Cloridrato de Dobutamina, Cloridrato de Dopamina, Citrato de Fentanila, Furosemida, Heparina Sódica, Succinato Sódico de Hidrocortisona, Cetoprofeno, Cloridrato de Midazolam, Sulfato de Morfina, Bitartarato de Norepinefrina, Propofol, Cloridrato de Vancomicina.</t>
+  </si>
+  <si>
+    <t>Fenobarbital Sódico: Barbitúrico altamente alcalino. Neutraliza e precipita cloridratos ácidos e glicopeptídeos em Y. MEDICAMENTOS INCOMPATÍVEIS: Cloridrato de Clorpromazina, Cloridrato de Midazolam, Cloridrato de Vancomicina.</t>
+  </si>
+  <si>
+    <t>Fenitoína Sódica: É o fármaco com o maior espectro de incompatibilidade em Y do banco Stabilis devido ao seu pH extremo (~12). Interage com praticamente todos os eletrólitos, sulfatos e cloridratos hospitalares. MEDICAMENTOS INCOMPATÍVEIS: Sulfato de Amicacina, Aminofilina, Cloridrato de Amiodarona, Besilato de Atracúrio, Sulfato de Atropina, Cloridrato de Bupivacaína, Lactato de Ciprofloxacino, Fosfato de Clindamicina, Cloridrato de Dobutamina, Cloridrato de Dopamina, Citrato de Fentanila, Fluconazol, Furosemida, Sulfato de Gentamicina, Heparina Sódica, Cloridrato de Hidralazina, Insulina, Cloridrato de Lidocaína, Sulfato de Magnésio, Cloridrato de Metoclopramida, Cloridrato de Midazolam, Sulfato de Morfina, Nitroglicerina, Bitartarato de Norepinefrina, Cloridrato de Ondansetrona, Piperacilina + Tazobactam, Cloreto de Potássio, Cloridrato de Prometazina, Cloridrato de Ranitidina, Brometo de Rocurônio, Bicarbonato de Sódio, Cloreto de Suxametônio, Cloridrato de Vancomicina.</t>
+  </si>
+  <si>
+    <t>Citrato de Fentanila: Sedativo opioide com pH ácido. Sofre precipitação da base livre em contato com o pH 12 da Fenitoína Sódica. MEDICAMENTOS INCOMPATÍVEIS: Diazepam, Fenitoína Sódica.</t>
+  </si>
+  <si>
+    <t>Fluconazol: Apresenta incompatibilidade física e redução de solubilidade em Y quando misturado com sais sódicos antibióticos ou diuréticos. MEDICAMENTOS INCOMPATÍVEIS: Ampicilina Sódica, Gliconato de Cálcio, Fosfato de Clindamicina, Furosemida, Fenitoína Sódica, Piperacilina + Tazobactam.</t>
+  </si>
+  <si>
+    <t>Furosemida Sódica: Solução alcalina tamponada (pH 8,5 a 9,3). É o diurético com maior índice de incompatibilidade em Y devido à precipitação imediata ao cruzar com cloridratos ou sulfatos ácidos. MEDICAMENTOS INCOMPATÍVEIS: Cloridrato de Amiodarona, Anfotericina B, Azitromicina, Gliconato de Cálcio, Lactato de Ciprofloxacino, Diazepam, Cloridrato de Dobutamina, Cloridrato de Dopamina, Cloridrato de Doxorrubicina, Filgrastim, Fluconazol, Sulfato de Gentamicina, Lactato de Haloperidol, Cloridrato de Hidralazina, Levofloxacino, Cloridrato de Midazolam, Lactato de Milrinone, Sulfato de Morfina, Bitartarato de Norepinefrina, Cloridrato de Ondansetrona, Cloridrato de Prometazina, Cloridrato de Vancomicina.</t>
+  </si>
+  <si>
+    <t>Sulfato de Gentamicina: Aminoglicosídeo catiônico. Complexa-se diretamente com a Heparina (aniônica) e sofre precipitação em meios fortemente alcalinos. MEDICAMENTOS INCOMPATÍVEIS: Ampicilina+Sulbactam, Anfotericina B, Furosemida, Heparina Sódica, Fenitoína Sódica, Propofol, Bicarbonato de Sódio.</t>
+  </si>
+  <si>
+    <t>Gliconato de Cálcio: Libera íons Ca{2+} que se ligam a carbonatos e sulfatos gerando sais insolúveis. O Cloreto de Cálcio possui maior velocidade iônica de precipitação que o gliconato. MEDICAMENTOS INCOMPATÍVEIS: Anfotericina B, Lactato de Ciprofloxacino, Fluconazol, Furosemida, Indometacina, Succinato Sódico de Metilprednisolona, Bicarbonato de Sódio, .</t>
+  </si>
+  <si>
+    <t>Lactato de Haloperidol: Solução ácida instável na presença de buffers alcalinos ou agentes aniônicos, gerando turvação visível. MEDICAMENTOS INCOMPATÍVEIS: Aciclovir Sódico, Furosemida, Heparina Sódica, Nitroprusseto de Sódio, Fenitoína Sódica, Bicarbonato de Sódio.</t>
+  </si>
+  <si>
+    <t>Heparina Sódica: Polímero aniônico natural altamente carregado negativamente. Neutraliza e se complexa com quase todos os cloridratos catiônicos da rotina intensiva em Y. MEDICAMENTOS INCOMPATÍVEIS: Cloridrato de Amiodarona, Anfotericina B, Cloridrato de Clorpromazina, Lactato de Ciprofloxacino, Diazepam, Cloridrato de Dobutamina, Cloridrato de Doxorrubicina, Filgrastim, Sulfato de Gentamicina, Lactato de Haloperidol, Cloridrato de Midazolam, Sulfato de Morfina, Cloridrato de Ondansetrona, Polimixina B, Cloridrato de Prometazina, Cloridrato de Vancomicina.</t>
+  </si>
+  <si>
+    <t>Cloridrato de Hidralazina: Vasodilatador estável em pH ácido; interage e decai quimicamente frente a soluções de caráter básico. MEDICAMENTOS INCOMPATÍVEIS: Aminofilina, Ampicilina Sódica, Furosemida, Fenitoína Sódica.</t>
+  </si>
+  <si>
+    <t>Succinato Sódico de Hidrocortisona: Corticoide que apresenta incompatibilidade físico-química cruzada com sedativos e aminas em Y.  MEDICAMENTOS INCOMPATÍVEIS: Diazepam, Cloridrato de Dobutamina, Cloridrato de Midazolam, Fenitoína Sódica.</t>
+  </si>
+  <si>
+    <t>Incompatibilidades (Base stabilis.org)</t>
+  </si>
+  <si>
+    <t>Imunoglobulina Antitimócito (Coelho): Proteína de alto peso molecular. Pode sofrer agregação ou precipitação física em contato com polímeros fortemente carregados como a heparina. MEDICAMENTOS INCOMPATÍVEIS: Heparina Sódica.</t>
+  </si>
+  <si>
+    <t>Insulina Regular: Molécula proteica estável em pH neutro a levemente ácido. Sofre desnaturação ou agregação sob o pH extremo da fenitoína. MEDICAMENTOS INCOMPATÍVEIS: Bitartarato de Norepinefrina, Fenitoína Sódica.</t>
+  </si>
+  <si>
+    <t>Sulfato de Magnésio: O íon magnésio precipita o complexo de deoxicolato da anfotericina e reage com buffers alcalinos da fenitoína.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Succinato Sódico de Metilprednisolona: Reage gerando opalescência em contato com o cálcio ou com soluções ácidas de vancomicina. MEDICAMENTOS INCOMPATÍVEIS: Gliconato de Cálcio, Cloridrato de Vancomicina. </t>
+  </si>
+  <si>
+    <t>Metotrexato Sódico: Antineoplásico incompatível com soluções de pH nitidamente ácido (Vancomicina e Midazolam). MEDICAMENTOS INCOMPATÍVEIS: Cloridrato de Midazolam, Cloridrato de Vancomicina.</t>
+  </si>
+  <si>
+    <t>Metonidazol: O Stabilis aponta incompatibilidade em Y restrita ao Aztreonam por potencial de alteração física da mistura.</t>
+  </si>
+  <si>
+    <t>Cloridrato de Midazolam: Depende de pH ácido (&lt;4,0) para manter o anel molecular aberto e solúvel. Sais sódicos ou alcalinos fecham o anel, tornando-o hidrofóbico e insolúvel. MEDICAMENTOS INCOMPATÍVEIS: Aciclovir Sódico, Aminofilina, Ampicilina Sódica, Ampicilina+Sulbactam, Bumetanida, Ceftazidima, Ceftriaxona Sódica, Cefuroxima Sódica, Fosfato Dissódico de Dexametasona, Diazepam, Furosemida, Heparina Sódica, Succinato Sódico de Hidrocortisona, Cetoprofeno, Metotrexato Sódico, Omeprazol, Fenobarbital Sódico, Fenitoína Sódica, Piperacilina + Tazobactam, Cloridrato de Ranitidina, Bicarbonato de Sódio, , Sulfametoxazol+Trimetoprima.</t>
+  </si>
+  <si>
+    <t>Lactato de Milrinone: Inotrópico de caráter ácido que precipita instantaneamente ao entrar em contato com o buffer básico da Furosemida Sódica em Y.</t>
+  </si>
+  <si>
+    <t>Sulfato de Morfina: Opioide catiônico ácido. Sofre precipitação de morfina livre em contato com bases (Furosemida, Fenitoína) ou complexação com a Heparina.MEDICAMENTOS INCOMPATÍVEIS: Aciclovir Sódico, Anfotericina B, Diazepam, Furosemida, Heparina Sódica, Fenitoína Sódica.</t>
+  </si>
+  <si>
+    <t>Nitroglicerina: Além da forte adsorção ao plástico PVC, sofre degradação ou precipitação molecular na presença do pH extremo da fenitoína.</t>
+  </si>
+  <si>
+    <t>Nitroprusseto de Sódio: Fármaco fotossensível; apresenta reação física adversa descrita em Y especificamente com o Haloperidol.</t>
+  </si>
+  <si>
+    <t>Bitartarato de Norepinefrina: Amina vasoativa ácida. Sofre oxidação catalisada por meios básicos e alcalinos, inativando o efeito terapêutico. .MEDICAMENTOS INCOMPATÍVEIS: Aciclovir Sódico, Aminofilina, Diazepam, Furosemida, Insulina, Fenitoína Sódica, Bicarbonato de Sódio, , Tiopental Sódico.</t>
+  </si>
+  <si>
+    <t>Cloridrato de Ondansetrona: Antiemético de pH ácido; precipita de imediato em contato com os buffers sódicos e básicos em Y. MEDICAMENTOS INCOMPATÍVEIS: Aciclovir Sódico, Aminofilina, Ampicilina Sódica, Furosemida, Heparina Sódica, Fenitoína Sódica, Bicarbonato de Sódio.</t>
+  </si>
+  <si>
+    <t>Oxacilina Sódica: Penicilina penicilinase-resistente alcalina. Desenvolve precipitados insolúveis cruzados ao tocar o Cloridrato de Vancomicina.</t>
+  </si>
+  <si>
+    <t>Piperacilina Sódica + Tazobactam Sódico: Antibiótico combinado de caráter sódico/alcalino. Incompatível em Y com aminoglicosídeos, amiodarona e vancomicina por reações de precipitação física.  MEDICAMENTOS INCOMPATÍVEIS:Sulfato de Amicacina, Cloridrato de Amiodarona, Anfotericina B, Cloridrato de Dobutamina, Cloridrato de Doxorrubicina, Fluconazol, Cloridrato de Midazolam, Fenitoína Sódica, Cloridrato de Vancomicina.</t>
+  </si>
+  <si>
+    <t>Cloridrato de Prometazina: Anti-histamínico catiônico ácido. Sofre complexação com a heparina e precipitação física macroscópica em contato com bases. MEDICAMENTOS INCOMPATÍVEIS: Aminofilina, Furosemida, Heparina Sódica, Fenitoína Sódica, Bicarbonato de Sódio.</t>
+  </si>
+  <si>
+    <t>Propofol (Emulsão Lipídica): Sistemas emulsionados óleo em água. Aditivos catiônicos ou variações na força iônica rompem o potencial zeta, causando a coalescência dos lipídeos. MEDICAMENTOS INCOMPATÍVEIS: Besilato de Cisatracúrio, Etomidato, Sulfato de Gentamicina.</t>
+  </si>
+  <si>
+    <t>Cloreto de Suxametônio: Bloqueador neuromuscular despolarizante; sofre quebra iônica e deposição de cristais no pH da fenitoína sódica.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teicoplanina: Antibiótico glicopeptídeo que gera turvação ou micropartículas físicas ao entrar em contato com o ciprofloxacino em Y. </t>
+  </si>
+  <si>
+    <t>Tiopental Sódico: Barbitúrico anestésico de altíssimo pH. Provoca oxidação imediata e destruição molecular de catecolaminas ácidas em Y. MEDICAMENTOS INCOMPATÍVEIS: Bitartarato de Norepinefrina, Cloridrato de Dopamina.</t>
+  </si>
+  <si>
+    <t>Cloridrato de Vancomicina: Estrutura glicopeptídica complexa ácida. Desenvolve precipitados densos e imediatos em Y ao cruzar com quase todas as cefalosporinas e penicilinas baseadas em sais sódicos alcalinos. MEDICAMENTOS INCOMPATÍVEIS: Anfotericina B, Ampicilina Sódica, Ampicilina+Sulbactam, Aztreonam, Cefazolina Sódica, Cloridrato de Cefepima, Cefotaxima Sódica, Ceftazidima, Ceftriaxona Sódica, Cefuroxima Sódica, Diazepam, Furosemida, Heparina Sódica, Cetoprofeno, Metotrexato Sódico, Succinato Sódico de Metilprednisolona, Omeprazol, Oxacilina Sódica, Fenobarbital Sódico, Fenitoína Sódica, Piperacilina + Tazobactam, Bicarbonato de Sódio.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5387,6 +5555,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -5520,7 +5694,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -5528,68 +5702,71 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5616,45 +5793,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
         <vertical style="thin">
           <color indexed="64"/>
         </vertical>
@@ -6283,13 +6421,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -6313,6 +6444,52 @@
       </fill>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -6327,35 +6504,35 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C66CAC23-3932-448E-B212-95E42CAB4E80}" name="Tabela1" displayName="Tabela1" ref="A1:W297" totalsRowShown="0" headerRowDxfId="1" dataDxfId="27" headerRowBorderDxfId="25" tableBorderDxfId="26" totalsRowBorderDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C66CAC23-3932-448E-B212-95E42CAB4E80}" name="Tabela1" displayName="Tabela1" ref="A1:W297" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
   <autoFilter ref="A1:W297" xr:uid="{C66CAC23-3932-448E-B212-95E42CAB4E80}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V297">
     <sortCondition ref="A1:A297"/>
   </sortState>
   <tableColumns count="23">
-    <tableColumn id="1" xr3:uid="{6CF6D1CB-2AAF-4E12-AEEC-882E86A23A49}" name="MEDICAMENTO" dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{FBFAC514-DF42-4475-B14D-C827EFE3BD41}" name="NOME COMERCIAL" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{D915C517-B762-4232-8E23-0DEE85F5C839}" name="LABORATÓRIO" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{FBDB6C5C-EE94-4BC4-9559-2771378D7E29}" name="VIA DE ADMINISTRAÇÃO" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{0380B284-570D-49F4-B0B2-4AF3272CE48F}" name="RECONSTITUIÇÃO" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{EDF02C67-E69F-4BD7-8869-C0A878E20E76}" name="VOLUME EXPANDIDO" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{E4F2DD92-D1EB-4DB3-A9B9-98D27FA9715B}" name="CONCENTRAÇÃO" dataDxfId="17"/>
-    <tableColumn id="8" xr3:uid="{D0B450EF-84EF-4F29-8843-1B4736A1E31A}" name="ESTABILIDADE DO RECONSTITUÍDO (Temp. Ambiente 25°C)" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{276AEC7F-36A7-4281-947F-3470413C358D}" name="ESTABILIDADE DO RECONSTITUÍDO Refrigerada (2º a 8ºC)" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{68A3D7BC-B124-4611-87B6-DED33A2BC96E}" name="DILUIÇÃO" dataDxfId="14"/>
-    <tableColumn id="11" xr3:uid="{46EDDA50-D1C8-40C2-89F6-0CEA5976C831}" name="ESTABILIDADE DA DILUIÇÃO (Temp. Ambiente (25°C)" dataDxfId="13"/>
-    <tableColumn id="12" xr3:uid="{4DA6A3F4-11A1-44F3-AE71-CEB40C8A362E}" name="ESTABILIDADE DA DILUIÇÃO (Refrigerada 2º a 8ºC)" dataDxfId="12"/>
-    <tableColumn id="13" xr3:uid="{480073C8-F209-49B3-B22A-62EEF0307521}" name="DOSE PEDIATRIA (Usual)" dataDxfId="11"/>
-    <tableColumn id="14" xr3:uid="{FB1A5428-347B-4491-BADD-AC4D985F70E3}" name="DOSE Máximaped" dataDxfId="10"/>
-    <tableColumn id="15" xr3:uid="{5FEB84CC-0B6B-4605-84C5-935428D1A89D}" name="DOSE ADULTO (Usual)" dataDxfId="9"/>
-    <tableColumn id="16" xr3:uid="{FA44054B-52E9-4183-A744-C6B8D7463F36}" name="DOSE Máxima adulto" dataDxfId="8"/>
-    <tableColumn id="17" xr3:uid="{E72F1DF1-B624-4464-9DCB-1396324D1776}" name="TEMPO DE INFUSÃO" dataDxfId="7"/>
-    <tableColumn id="18" xr3:uid="{4DBF5794-7F50-499F-AE74-E5044DFCF668}" name="AJUSTE RENAL" dataDxfId="6"/>
-    <tableColumn id="19" xr3:uid="{B2C5555A-E11A-4325-892D-B67AEC4CD91A}" name="AJUSTE HEPÁTICO" dataDxfId="5"/>
-    <tableColumn id="20" xr3:uid="{3381B897-5F21-4B1A-88C9-CB9C7DFB3FED}" name="OBSERVAÇÕES " dataDxfId="4"/>
-    <tableColumn id="21" xr3:uid="{1E22FF74-B6C9-420D-BF9C-1EFEBF09B20F}" name="CONCENTRAÇÃO DE INFUSÃO (Adulto)" dataDxfId="3"/>
-    <tableColumn id="22" xr3:uid="{F1DAB99C-AB02-42ED-85FE-4A8DA8E1658D}" name="CONCENTRAÇÃO_ped INFUSÃO" dataDxfId="2"/>
-    <tableColumn id="23" xr3:uid="{3F2D921C-4D7A-4B21-9D59-254332C02760}" name="Incompatibilidades" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{6CF6D1CB-2AAF-4E12-AEEC-882E86A23A49}" name="MEDICAMENTO" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{FBFAC514-DF42-4475-B14D-C827EFE3BD41}" name="NOME COMERCIAL" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{D915C517-B762-4232-8E23-0DEE85F5C839}" name="LABORATÓRIO" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{FBDB6C5C-EE94-4BC4-9559-2771378D7E29}" name="VIA DE ADMINISTRAÇÃO" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{0380B284-570D-49F4-B0B2-4AF3272CE48F}" name="RECONSTITUIÇÃO" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{EDF02C67-E69F-4BD7-8869-C0A878E20E76}" name="VOLUME EXPANDIDO" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{E4F2DD92-D1EB-4DB3-A9B9-98D27FA9715B}" name="CONCENTRAÇÃO" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{D0B450EF-84EF-4F29-8843-1B4736A1E31A}" name="ESTABILIDADE DO RECONSTITUÍDO (Temp. Ambiente 25°C)" dataDxfId="15"/>
+    <tableColumn id="9" xr3:uid="{276AEC7F-36A7-4281-947F-3470413C358D}" name="ESTABILIDADE DO RECONSTITUÍDO Refrigerada (2º a 8ºC)" dataDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{68A3D7BC-B124-4611-87B6-DED33A2BC96E}" name="DILUIÇÃO" dataDxfId="13"/>
+    <tableColumn id="11" xr3:uid="{46EDDA50-D1C8-40C2-89F6-0CEA5976C831}" name="ESTABILIDADE DA DILUIÇÃO (Temp. Ambiente (25°C)" dataDxfId="12"/>
+    <tableColumn id="12" xr3:uid="{4DA6A3F4-11A1-44F3-AE71-CEB40C8A362E}" name="ESTABILIDADE DA DILUIÇÃO (Refrigerada 2º a 8ºC)" dataDxfId="11"/>
+    <tableColumn id="13" xr3:uid="{480073C8-F209-49B3-B22A-62EEF0307521}" name="DOSE PEDIATRIA (Usual)" dataDxfId="10"/>
+    <tableColumn id="14" xr3:uid="{FB1A5428-347B-4491-BADD-AC4D985F70E3}" name="DOSE Máximaped" dataDxfId="9"/>
+    <tableColumn id="15" xr3:uid="{5FEB84CC-0B6B-4605-84C5-935428D1A89D}" name="DOSE ADULTO (Usual)" dataDxfId="8"/>
+    <tableColumn id="16" xr3:uid="{FA44054B-52E9-4183-A744-C6B8D7463F36}" name="DOSE Máxima adulto" dataDxfId="7"/>
+    <tableColumn id="17" xr3:uid="{E72F1DF1-B624-4464-9DCB-1396324D1776}" name="TEMPO DE INFUSÃO" dataDxfId="6"/>
+    <tableColumn id="18" xr3:uid="{4DBF5794-7F50-499F-AE74-E5044DFCF668}" name="AJUSTE RENAL" dataDxfId="5"/>
+    <tableColumn id="19" xr3:uid="{B2C5555A-E11A-4325-892D-B67AEC4CD91A}" name="AJUSTE HEPÁTICO" dataDxfId="4"/>
+    <tableColumn id="20" xr3:uid="{3381B897-5F21-4B1A-88C9-CB9C7DFB3FED}" name="OBSERVAÇÕES " dataDxfId="3"/>
+    <tableColumn id="21" xr3:uid="{1E22FF74-B6C9-420D-BF9C-1EFEBF09B20F}" name="CONCENTRAÇÃO DE INFUSÃO (Adulto)" dataDxfId="2"/>
+    <tableColumn id="22" xr3:uid="{F1DAB99C-AB02-42ED-85FE-4A8DA8E1658D}" name="CONCENTRAÇÃO_ped INFUSÃO" dataDxfId="1"/>
+    <tableColumn id="23" xr3:uid="{3F2D921C-4D7A-4B21-9D59-254332C02760}" name="Incompatibilidades (Base stabilis.org)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6647,31 +6824,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W297"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="55.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="31.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.5703125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="55.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="31.5546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="23.5546875" style="1" customWidth="1"/>
     <col min="5" max="5" width="25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.85546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="23.42578125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="55.7109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="54.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="126.28515625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="131.42578125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="60.85546875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="255.7109375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="155.28515625" style="1" customWidth="1"/>
-    <col min="15" max="19" width="255.7109375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="101.28515625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="37.5703125" style="1" customWidth="1"/>
-    <col min="22" max="22" width="31.140625" style="1" customWidth="1"/>
-    <col min="23" max="23" width="49.85546875" style="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="6" max="6" width="20.88671875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.44140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="55.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="54.5546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="126.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="131.44140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="60.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="255.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="155.33203125" style="1" customWidth="1"/>
+    <col min="15" max="19" width="255.6640625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="101.33203125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="37.5546875" style="1" customWidth="1"/>
+    <col min="22" max="22" width="31.109375" style="1" customWidth="1"/>
+    <col min="23" max="23" width="49.88671875" style="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -6738,11 +6915,11 @@
       <c r="V1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="3" t="s">
-        <v>1430</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" ht="165" x14ac:dyDescent="0.25">
+      <c r="W1" s="24" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>180</v>
       </c>
@@ -6809,9 +6986,11 @@
       <c r="V2" s="10" t="s">
         <v>1213</v>
       </c>
-      <c r="W2" s="23"/>
-    </row>
-    <row r="3" spans="1:23" ht="165" x14ac:dyDescent="0.25">
+      <c r="W2" s="23" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>180</v>
       </c>
@@ -6878,9 +7057,11 @@
       <c r="V3" s="10" t="s">
         <v>1213</v>
       </c>
-      <c r="W3" s="7"/>
-    </row>
-    <row r="4" spans="1:23" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="W3" s="23" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="78" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>584</v>
       </c>
@@ -6947,9 +7128,11 @@
       <c r="V4" s="10" t="s">
         <v>1215</v>
       </c>
-      <c r="W4" s="7"/>
-    </row>
-    <row r="5" spans="1:23" ht="120" x14ac:dyDescent="0.25">
+      <c r="W4" s="7" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>589</v>
       </c>
@@ -7018,7 +7201,7 @@
       </c>
       <c r="W5" s="7"/>
     </row>
-    <row r="6" spans="1:23" ht="63" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>595</v>
       </c>
@@ -7087,7 +7270,7 @@
       </c>
       <c r="W6" s="7"/>
     </row>
-    <row r="7" spans="1:23" ht="63" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>706</v>
       </c>
@@ -7154,9 +7337,11 @@
       <c r="V7" s="10" t="s">
         <v>1219</v>
       </c>
-      <c r="W7" s="7"/>
-    </row>
-    <row r="8" spans="1:23" ht="63" x14ac:dyDescent="0.25">
+      <c r="W7" s="7" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>711</v>
       </c>
@@ -7223,9 +7408,11 @@
       <c r="V8" s="10" t="s">
         <v>1221</v>
       </c>
-      <c r="W8" s="7"/>
-    </row>
-    <row r="9" spans="1:23" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="W8" s="7" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="78" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>729</v>
       </c>
@@ -7294,7 +7481,7 @@
       </c>
       <c r="W9" s="7"/>
     </row>
-    <row r="10" spans="1:23" ht="150" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" ht="115.2" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>774</v>
       </c>
@@ -7361,9 +7548,11 @@
       <c r="V10" s="10" t="s">
         <v>1225</v>
       </c>
-      <c r="W10" s="7"/>
-    </row>
-    <row r="11" spans="1:23" ht="150" x14ac:dyDescent="0.2">
+      <c r="W10" s="7" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="115.2" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>774</v>
       </c>
@@ -7430,9 +7619,11 @@
       <c r="V11" s="10" t="s">
         <v>1225</v>
       </c>
-      <c r="W11" s="7"/>
-    </row>
-    <row r="12" spans="1:23" ht="150" x14ac:dyDescent="0.25">
+      <c r="W11" s="7" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>188</v>
       </c>
@@ -7501,7 +7692,7 @@
       </c>
       <c r="W12" s="7"/>
     </row>
-    <row r="13" spans="1:23" ht="150" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>188</v>
       </c>
@@ -7570,7 +7761,7 @@
       </c>
       <c r="W13" s="7"/>
     </row>
-    <row r="14" spans="1:23" ht="150" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>188</v>
       </c>
@@ -7639,7 +7830,7 @@
       </c>
       <c r="W14" s="7"/>
     </row>
-    <row r="15" spans="1:23" ht="126" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>462</v>
       </c>
@@ -7708,7 +7899,7 @@
       </c>
       <c r="W15" s="7"/>
     </row>
-    <row r="16" spans="1:23" ht="126" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>462</v>
       </c>
@@ -7777,7 +7968,7 @@
       </c>
       <c r="W16" s="7"/>
     </row>
-    <row r="17" spans="1:23" ht="126" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>476</v>
       </c>
@@ -7846,7 +8037,7 @@
       </c>
       <c r="W17" s="7"/>
     </row>
-    <row r="18" spans="1:23" ht="110.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>480</v>
       </c>
@@ -7915,7 +8106,7 @@
       </c>
       <c r="W18" s="7"/>
     </row>
-    <row r="19" spans="1:23" ht="110.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>480</v>
       </c>
@@ -7984,7 +8175,7 @@
       </c>
       <c r="W19" s="7"/>
     </row>
-    <row r="20" spans="1:23" ht="150" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>489</v>
       </c>
@@ -8053,7 +8244,7 @@
       </c>
       <c r="W20" s="7"/>
     </row>
-    <row r="21" spans="1:23" ht="150" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>489</v>
       </c>
@@ -8122,7 +8313,7 @@
       </c>
       <c r="W21" s="7"/>
     </row>
-    <row r="22" spans="1:23" ht="110.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>512</v>
       </c>
@@ -8191,7 +8382,7 @@
       </c>
       <c r="W22" s="7"/>
     </row>
-    <row r="23" spans="1:23" ht="110.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>502</v>
       </c>
@@ -8260,7 +8451,7 @@
       </c>
       <c r="W23" s="7"/>
     </row>
-    <row r="24" spans="1:23" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>513</v>
       </c>
@@ -8329,7 +8520,7 @@
       </c>
       <c r="W24" s="7"/>
     </row>
-    <row r="25" spans="1:23" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>524</v>
       </c>
@@ -8398,7 +8589,7 @@
       </c>
       <c r="W25" s="7"/>
     </row>
-    <row r="26" spans="1:23" ht="63" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>559</v>
       </c>
@@ -8465,9 +8656,11 @@
       <c r="V26" s="10" t="s">
         <v>1240</v>
       </c>
-      <c r="W26" s="7"/>
-    </row>
-    <row r="27" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+      <c r="W26" s="7" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>569</v>
       </c>
@@ -8536,7 +8729,7 @@
       </c>
       <c r="W27" s="7"/>
     </row>
-    <row r="28" spans="1:23" ht="105" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>548</v>
       </c>
@@ -8605,7 +8798,7 @@
       </c>
       <c r="W28" s="7"/>
     </row>
-    <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>720</v>
       </c>
@@ -8670,9 +8863,11 @@
       <c r="V29" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W29" s="7"/>
-    </row>
-    <row r="30" spans="1:23" ht="180" x14ac:dyDescent="0.25">
+      <c r="W29" s="7" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>22</v>
       </c>
@@ -8741,7 +8936,7 @@
       </c>
       <c r="W30" s="7"/>
     </row>
-    <row r="31" spans="1:23" ht="180" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>22</v>
       </c>
@@ -8810,7 +9005,7 @@
       </c>
       <c r="W31" s="7"/>
     </row>
-    <row r="32" spans="1:23" ht="180" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>22</v>
       </c>
@@ -8879,7 +9074,7 @@
       </c>
       <c r="W32" s="7"/>
     </row>
-    <row r="33" spans="1:23" ht="180" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>22</v>
       </c>
@@ -8948,7 +9143,7 @@
       </c>
       <c r="W33" s="7"/>
     </row>
-    <row r="34" spans="1:23" ht="180" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>22</v>
       </c>
@@ -9017,7 +9212,7 @@
       </c>
       <c r="W34" s="7"/>
     </row>
-    <row r="35" spans="1:23" ht="195" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>22</v>
       </c>
@@ -9086,7 +9281,7 @@
       </c>
       <c r="W35" s="7"/>
     </row>
-    <row r="36" spans="1:23" ht="120" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>41</v>
       </c>
@@ -9153,9 +9348,11 @@
       <c r="V36" s="10" t="s">
         <v>1244</v>
       </c>
-      <c r="W36" s="7"/>
-    </row>
-    <row r="37" spans="1:23" ht="120" x14ac:dyDescent="0.25">
+      <c r="W36" s="7" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>41</v>
       </c>
@@ -9222,9 +9419,11 @@
       <c r="V37" s="10" t="s">
         <v>1244</v>
       </c>
-      <c r="W37" s="7"/>
-    </row>
-    <row r="38" spans="1:23" ht="120" x14ac:dyDescent="0.25">
+      <c r="W37" s="7" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>41</v>
       </c>
@@ -9291,9 +9490,11 @@
       <c r="V38" s="10" t="s">
         <v>1244</v>
       </c>
-      <c r="W38" s="7"/>
-    </row>
-    <row r="39" spans="1:23" ht="105" x14ac:dyDescent="0.25">
+      <c r="W38" s="7" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>55</v>
       </c>
@@ -9362,7 +9563,7 @@
       </c>
       <c r="W39" s="7"/>
     </row>
-    <row r="40" spans="1:23" ht="90" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>64</v>
       </c>
@@ -9431,7 +9632,7 @@
       </c>
       <c r="W40" s="7"/>
     </row>
-    <row r="41" spans="1:23" ht="90" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
         <v>64</v>
       </c>
@@ -9500,7 +9701,7 @@
       </c>
       <c r="W41" s="7"/>
     </row>
-    <row r="42" spans="1:23" ht="90" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
         <v>64</v>
       </c>
@@ -9569,7 +9770,7 @@
       </c>
       <c r="W42" s="7"/>
     </row>
-    <row r="43" spans="1:23" ht="150" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:23" ht="144" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
         <v>78</v>
       </c>
@@ -9638,7 +9839,7 @@
       </c>
       <c r="W43" s="7"/>
     </row>
-    <row r="44" spans="1:23" ht="150" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:23" ht="144" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>78</v>
       </c>
@@ -9707,7 +9908,7 @@
       </c>
       <c r="W44" s="7"/>
     </row>
-    <row r="45" spans="1:23" ht="150" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:23" ht="144" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
         <v>78</v>
       </c>
@@ -9776,7 +9977,7 @@
       </c>
       <c r="W45" s="7"/>
     </row>
-    <row r="46" spans="1:23" ht="150" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:23" ht="144" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>78</v>
       </c>
@@ -9845,7 +10046,7 @@
       </c>
       <c r="W46" s="7"/>
     </row>
-    <row r="47" spans="1:23" ht="75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
         <v>90</v>
       </c>
@@ -9912,9 +10113,11 @@
       <c r="V47" s="10" t="s">
         <v>1247</v>
       </c>
-      <c r="W47" s="7"/>
-    </row>
-    <row r="48" spans="1:23" ht="75" x14ac:dyDescent="0.25">
+      <c r="W47" s="7" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>90</v>
       </c>
@@ -9981,9 +10184,11 @@
       <c r="V48" s="10" t="s">
         <v>1247</v>
       </c>
-      <c r="W48" s="7"/>
-    </row>
-    <row r="49" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+      <c r="W48" s="7" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
         <v>99</v>
       </c>
@@ -10052,7 +10257,7 @@
       </c>
       <c r="W49" s="7"/>
     </row>
-    <row r="50" spans="1:23" ht="195" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:23" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>100</v>
       </c>
@@ -10121,7 +10326,7 @@
       </c>
       <c r="W50" s="7"/>
     </row>
-    <row r="51" spans="1:23" ht="195" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:23" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
         <v>100</v>
       </c>
@@ -10190,7 +10395,7 @@
       </c>
       <c r="W51" s="7"/>
     </row>
-    <row r="52" spans="1:23" ht="195" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:23" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>100</v>
       </c>
@@ -10259,7 +10464,7 @@
       </c>
       <c r="W52" s="7"/>
     </row>
-    <row r="53" spans="1:23" ht="195" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:23" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
         <v>100</v>
       </c>
@@ -10328,7 +10533,7 @@
       </c>
       <c r="W53" s="7"/>
     </row>
-    <row r="54" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
         <v>123</v>
       </c>
@@ -10397,7 +10602,7 @@
       </c>
       <c r="W54" s="7"/>
     </row>
-    <row r="55" spans="1:23" ht="150" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:23" ht="144" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>112</v>
       </c>
@@ -10464,9 +10669,11 @@
       <c r="V55" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="W55" s="7"/>
-    </row>
-    <row r="56" spans="1:23" ht="150" x14ac:dyDescent="0.25">
+      <c r="W55" s="7" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" ht="144" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
         <v>112</v>
       </c>
@@ -10533,9 +10740,11 @@
       <c r="V56" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="W56" s="7"/>
-    </row>
-    <row r="57" spans="1:23" ht="119.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W56" s="7" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" ht="119.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
         <v>124</v>
       </c>
@@ -10604,7 +10813,7 @@
       </c>
       <c r="W57" s="7"/>
     </row>
-    <row r="58" spans="1:23" ht="90" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
         <v>139</v>
       </c>
@@ -10673,7 +10882,7 @@
       </c>
       <c r="W58" s="7"/>
     </row>
-    <row r="59" spans="1:23" ht="90" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
         <v>139</v>
       </c>
@@ -10742,7 +10951,7 @@
       </c>
       <c r="W59" s="7"/>
     </row>
-    <row r="60" spans="1:23" ht="90" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
         <v>139</v>
       </c>
@@ -10811,7 +11020,7 @@
       </c>
       <c r="W60" s="7"/>
     </row>
-    <row r="61" spans="1:23" ht="165" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:23" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
         <v>149</v>
       </c>
@@ -10880,7 +11089,7 @@
       </c>
       <c r="W61" s="7"/>
     </row>
-    <row r="62" spans="1:23" ht="120" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
         <v>162</v>
       </c>
@@ -10947,9 +11156,11 @@
       <c r="V62" s="10" t="s">
         <v>1255</v>
       </c>
-      <c r="W62" s="7"/>
-    </row>
-    <row r="63" spans="1:23" ht="120" x14ac:dyDescent="0.25">
+      <c r="W62" s="7" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
         <v>162</v>
       </c>
@@ -11016,9 +11227,11 @@
       <c r="V63" s="10" t="s">
         <v>1255</v>
       </c>
-      <c r="W63" s="7"/>
-    </row>
-    <row r="64" spans="1:23" ht="120" x14ac:dyDescent="0.25">
+      <c r="W63" s="7" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
         <v>162</v>
       </c>
@@ -11085,9 +11298,11 @@
       <c r="V64" s="10" t="s">
         <v>1255</v>
       </c>
-      <c r="W64" s="7"/>
-    </row>
-    <row r="65" spans="1:23" ht="120" x14ac:dyDescent="0.25">
+      <c r="W64" s="7" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
         <v>162</v>
       </c>
@@ -11154,9 +11369,11 @@
       <c r="V65" s="10" t="s">
         <v>1255</v>
       </c>
-      <c r="W65" s="7"/>
-    </row>
-    <row r="66" spans="1:23" ht="120" x14ac:dyDescent="0.25">
+      <c r="W65" s="7" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
         <v>162</v>
       </c>
@@ -11223,9 +11440,11 @@
       <c r="V66" s="10" t="s">
         <v>1255</v>
       </c>
-      <c r="W66" s="7"/>
-    </row>
-    <row r="67" spans="1:23" ht="120" x14ac:dyDescent="0.25">
+      <c r="W66" s="7" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
         <v>162</v>
       </c>
@@ -11292,9 +11511,11 @@
       <c r="V67" s="10" t="s">
         <v>1255</v>
       </c>
-      <c r="W67" s="7"/>
-    </row>
-    <row r="68" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+      <c r="W67" s="7" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
         <v>172</v>
       </c>
@@ -11363,7 +11584,7 @@
       </c>
       <c r="W68" s="7"/>
     </row>
-    <row r="69" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
         <v>173</v>
       </c>
@@ -11432,7 +11653,7 @@
       </c>
       <c r="W69" s="7"/>
     </row>
-    <row r="70" spans="1:23" ht="90" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
         <v>174</v>
       </c>
@@ -11499,9 +11720,11 @@
       <c r="V70" s="10" t="s">
         <v>1256</v>
       </c>
-      <c r="W70" s="7"/>
-    </row>
-    <row r="71" spans="1:23" ht="90" x14ac:dyDescent="0.25">
+      <c r="W70" s="7" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
         <v>174</v>
       </c>
@@ -11568,9 +11791,11 @@
       <c r="V71" s="10" t="s">
         <v>1256</v>
       </c>
-      <c r="W71" s="7"/>
-    </row>
-    <row r="72" spans="1:23" ht="90" x14ac:dyDescent="0.25">
+      <c r="W71" s="7" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
         <v>174</v>
       </c>
@@ -11637,9 +11862,11 @@
       <c r="V72" s="10" t="s">
         <v>1256</v>
       </c>
-      <c r="W72" s="7"/>
-    </row>
-    <row r="73" spans="1:23" ht="90" x14ac:dyDescent="0.25">
+      <c r="W72" s="7" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
         <v>174</v>
       </c>
@@ -11706,9 +11933,11 @@
       <c r="V73" s="10" t="s">
         <v>1256</v>
       </c>
-      <c r="W73" s="7"/>
-    </row>
-    <row r="74" spans="1:23" ht="135" x14ac:dyDescent="0.25">
+      <c r="W73" s="7" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
         <v>205</v>
       </c>
@@ -11775,9 +12004,11 @@
       <c r="V74" s="10" t="s">
         <v>1258</v>
       </c>
-      <c r="W74" s="7"/>
-    </row>
-    <row r="75" spans="1:23" ht="135" x14ac:dyDescent="0.25">
+      <c r="W74" s="7" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
         <v>205</v>
       </c>
@@ -11844,9 +12075,11 @@
       <c r="V75" s="10" t="s">
         <v>1258</v>
       </c>
-      <c r="W75" s="7"/>
-    </row>
-    <row r="76" spans="1:23" ht="135" x14ac:dyDescent="0.25">
+      <c r="W75" s="7" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
         <v>205</v>
       </c>
@@ -11913,9 +12146,11 @@
       <c r="V76" s="10" t="s">
         <v>1258</v>
       </c>
-      <c r="W76" s="7"/>
-    </row>
-    <row r="77" spans="1:23" ht="135" x14ac:dyDescent="0.25">
+      <c r="W76" s="7" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
         <v>205</v>
       </c>
@@ -11982,9 +12217,11 @@
       <c r="V77" s="10" t="s">
         <v>1258</v>
       </c>
-      <c r="W77" s="7"/>
-    </row>
-    <row r="78" spans="1:23" ht="135" x14ac:dyDescent="0.25">
+      <c r="W77" s="7" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
         <v>221</v>
       </c>
@@ -12051,9 +12288,11 @@
       <c r="V78" s="10" t="s">
         <v>1258</v>
       </c>
-      <c r="W78" s="7"/>
-    </row>
-    <row r="79" spans="1:23" ht="135" x14ac:dyDescent="0.25">
+      <c r="W78" s="7" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
         <v>221</v>
       </c>
@@ -12120,9 +12359,11 @@
       <c r="V79" s="10" t="s">
         <v>1258</v>
       </c>
-      <c r="W79" s="7"/>
-    </row>
-    <row r="80" spans="1:23" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="W79" s="7" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
         <v>223</v>
       </c>
@@ -12189,9 +12430,11 @@
       <c r="V80" s="10" t="s">
         <v>1259</v>
       </c>
-      <c r="W80" s="7"/>
-    </row>
-    <row r="81" spans="1:23" ht="120" x14ac:dyDescent="0.25">
+      <c r="W80" s="7" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
         <v>223</v>
       </c>
@@ -12258,9 +12501,11 @@
       <c r="V81" s="10" t="s">
         <v>1259</v>
       </c>
-      <c r="W81" s="7"/>
-    </row>
-    <row r="82" spans="1:23" ht="120" x14ac:dyDescent="0.25">
+      <c r="W81" s="7" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="82" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A82" s="6" t="s">
         <v>223</v>
       </c>
@@ -12327,9 +12572,11 @@
       <c r="V82" s="10" t="s">
         <v>1259</v>
       </c>
-      <c r="W82" s="7"/>
-    </row>
-    <row r="83" spans="1:23" ht="120" x14ac:dyDescent="0.25">
+      <c r="W82" s="7" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A83" s="6" t="s">
         <v>223</v>
       </c>
@@ -12396,9 +12643,11 @@
       <c r="V83" s="10" t="s">
         <v>1259</v>
       </c>
-      <c r="W83" s="7"/>
-    </row>
-    <row r="84" spans="1:23" ht="120" x14ac:dyDescent="0.25">
+      <c r="W83" s="7" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="84" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
         <v>223</v>
       </c>
@@ -12465,9 +12714,11 @@
       <c r="V84" s="10" t="s">
         <v>1259</v>
       </c>
-      <c r="W84" s="7"/>
-    </row>
-    <row r="85" spans="1:23" ht="120" x14ac:dyDescent="0.25">
+      <c r="W84" s="7" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="85" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
         <v>223</v>
       </c>
@@ -12534,9 +12785,11 @@
       <c r="V85" s="10" t="s">
         <v>1259</v>
       </c>
-      <c r="W85" s="7"/>
-    </row>
-    <row r="86" spans="1:23" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="W85" s="7" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
         <v>223</v>
       </c>
@@ -12603,9 +12856,11 @@
       <c r="V86" s="10" t="s">
         <v>1259</v>
       </c>
-      <c r="W86" s="7"/>
-    </row>
-    <row r="87" spans="1:23" ht="120" x14ac:dyDescent="0.25">
+      <c r="W86" s="7" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="87" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A87" s="6" t="s">
         <v>223</v>
       </c>
@@ -12672,9 +12927,11 @@
       <c r="V87" s="10" t="s">
         <v>1259</v>
       </c>
-      <c r="W87" s="7"/>
-    </row>
-    <row r="88" spans="1:23" ht="105" x14ac:dyDescent="0.25">
+      <c r="W87" s="7" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="88" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A88" s="6" t="s">
         <v>263</v>
       </c>
@@ -12741,9 +12998,11 @@
       <c r="V88" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W88" s="7"/>
-    </row>
-    <row r="89" spans="1:23" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="W88" s="7" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="89" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
         <v>252</v>
       </c>
@@ -12810,9 +13069,11 @@
       <c r="V89" s="10" t="s">
         <v>1261</v>
       </c>
-      <c r="W89" s="7"/>
-    </row>
-    <row r="90" spans="1:23" ht="150" x14ac:dyDescent="0.25">
+      <c r="W89" s="7" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="90" spans="1:23" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="6" t="s">
         <v>239</v>
       </c>
@@ -12879,9 +13140,11 @@
       <c r="V90" s="10" t="s">
         <v>1263</v>
       </c>
-      <c r="W90" s="7"/>
-    </row>
-    <row r="91" spans="1:23" ht="90" x14ac:dyDescent="0.25">
+      <c r="W90" s="7" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="91" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
         <v>273</v>
       </c>
@@ -12950,7 +13213,7 @@
       </c>
       <c r="W91" s="7"/>
     </row>
-    <row r="92" spans="1:23" ht="90" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
         <v>273</v>
       </c>
@@ -13019,7 +13282,7 @@
       </c>
       <c r="W92" s="7"/>
     </row>
-    <row r="93" spans="1:23" ht="90" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A93" s="6" t="s">
         <v>286</v>
       </c>
@@ -13088,7 +13351,7 @@
       </c>
       <c r="W93" s="7"/>
     </row>
-    <row r="94" spans="1:23" ht="75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A94" s="6" t="s">
         <v>290</v>
       </c>
@@ -13155,9 +13418,11 @@
       <c r="V94" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W94" s="7"/>
-    </row>
-    <row r="95" spans="1:23" ht="75" x14ac:dyDescent="0.25">
+      <c r="W94" s="7" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="95" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A95" s="6" t="s">
         <v>290</v>
       </c>
@@ -13224,9 +13489,11 @@
       <c r="V95" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W95" s="7"/>
-    </row>
-    <row r="96" spans="1:23" ht="75" x14ac:dyDescent="0.25">
+      <c r="W95" s="7" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="96" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A96" s="6" t="s">
         <v>290</v>
       </c>
@@ -13293,9 +13560,11 @@
       <c r="V96" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W96" s="7"/>
-    </row>
-    <row r="97" spans="1:23" ht="75" x14ac:dyDescent="0.25">
+      <c r="W96" s="7" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="97" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A97" s="6" t="s">
         <v>300</v>
       </c>
@@ -13362,9 +13631,11 @@
       <c r="V97" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W97" s="7"/>
-    </row>
-    <row r="98" spans="1:23" ht="75" x14ac:dyDescent="0.25">
+      <c r="W97" s="7" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="98" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A98" s="6" t="s">
         <v>300</v>
       </c>
@@ -13431,9 +13702,11 @@
       <c r="V98" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W98" s="7"/>
-    </row>
-    <row r="99" spans="1:23" ht="75" x14ac:dyDescent="0.25">
+      <c r="W98" s="7" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="99" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A99" s="6" t="s">
         <v>300</v>
       </c>
@@ -13500,9 +13773,11 @@
       <c r="V99" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W99" s="7"/>
-    </row>
-    <row r="100" spans="1:23" ht="75" x14ac:dyDescent="0.25">
+      <c r="W99" s="7" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="100" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A100" s="6" t="s">
         <v>300</v>
       </c>
@@ -13569,9 +13844,11 @@
       <c r="V100" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W100" s="7"/>
-    </row>
-    <row r="101" spans="1:23" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="W100" s="7" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="101" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A101" s="6" t="s">
         <v>308</v>
       </c>
@@ -13638,9 +13915,11 @@
       <c r="V101" s="10" t="s">
         <v>1349</v>
       </c>
-      <c r="W101" s="7"/>
-    </row>
-    <row r="102" spans="1:23" ht="165.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W101" s="7" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="102" spans="1:23" ht="165.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="6" t="s">
         <v>308</v>
       </c>
@@ -13707,9 +13986,11 @@
       <c r="V102" s="10" t="s">
         <v>1349</v>
       </c>
-      <c r="W102" s="7"/>
-    </row>
-    <row r="103" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+      <c r="W102" s="7" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="103" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A103" s="6" t="s">
         <v>322</v>
       </c>
@@ -13776,9 +14057,11 @@
       <c r="V103" s="10" t="s">
         <v>1350</v>
       </c>
-      <c r="W103" s="7"/>
-    </row>
-    <row r="104" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+      <c r="W103" s="7" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="104" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A104" s="6" t="s">
         <v>322</v>
       </c>
@@ -13845,9 +14128,11 @@
       <c r="V104" s="10" t="s">
         <v>1351</v>
       </c>
-      <c r="W104" s="7"/>
-    </row>
-    <row r="105" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+      <c r="W104" s="7" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="105" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A105" s="6" t="s">
         <v>338</v>
       </c>
@@ -13916,7 +14201,7 @@
       </c>
       <c r="W105" s="7"/>
     </row>
-    <row r="106" spans="1:23" ht="60" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A106" s="6" t="s">
         <v>338</v>
       </c>
@@ -13985,7 +14270,7 @@
       </c>
       <c r="W106" s="7"/>
     </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A107" s="6" t="s">
         <v>347</v>
       </c>
@@ -14054,7 +14339,7 @@
       </c>
       <c r="W107" s="7"/>
     </row>
-    <row r="108" spans="1:23" ht="90" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A108" s="6" t="s">
         <v>348</v>
       </c>
@@ -14123,7 +14408,7 @@
       </c>
       <c r="W108" s="7"/>
     </row>
-    <row r="109" spans="1:23" ht="90" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A109" s="6" t="s">
         <v>348</v>
       </c>
@@ -14192,7 +14477,7 @@
       </c>
       <c r="W109" s="7"/>
     </row>
-    <row r="110" spans="1:23" ht="135" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A110" s="6" t="s">
         <v>365</v>
       </c>
@@ -14261,7 +14546,7 @@
       </c>
       <c r="W110" s="7"/>
     </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A111" s="6" t="s">
         <v>378</v>
       </c>
@@ -14330,7 +14615,7 @@
       </c>
       <c r="W111" s="7"/>
     </row>
-    <row r="112" spans="1:23" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:23" ht="78" x14ac:dyDescent="0.3">
       <c r="A112" s="6" t="s">
         <v>379</v>
       </c>
@@ -14399,7 +14684,7 @@
       </c>
       <c r="W112" s="7"/>
     </row>
-    <row r="113" spans="1:23" ht="60" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A113" s="6" t="s">
         <v>382</v>
       </c>
@@ -14468,7 +14753,7 @@
       </c>
       <c r="W113" s="7"/>
     </row>
-    <row r="114" spans="1:23" ht="60" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A114" s="6" t="s">
         <v>382</v>
       </c>
@@ -14537,7 +14822,7 @@
       </c>
       <c r="W114" s="7"/>
     </row>
-    <row r="115" spans="1:23" ht="90" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A115" s="6" t="s">
         <v>390</v>
       </c>
@@ -14604,9 +14889,11 @@
       <c r="V115" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W115" s="7"/>
-    </row>
-    <row r="116" spans="1:23" ht="90" x14ac:dyDescent="0.25">
+      <c r="W115" s="7" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="116" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A116" s="6" t="s">
         <v>390</v>
       </c>
@@ -14673,9 +14960,11 @@
       <c r="V116" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W116" s="7"/>
-    </row>
-    <row r="117" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+      <c r="W116" s="7" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="117" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A117" s="6" t="s">
         <v>399</v>
       </c>
@@ -14742,9 +15031,11 @@
       <c r="V117" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W117" s="7"/>
-    </row>
-    <row r="118" spans="1:23" ht="75" x14ac:dyDescent="0.25">
+      <c r="W117" s="7" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="118" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A118" s="6" t="s">
         <v>407</v>
       </c>
@@ -14811,9 +15102,11 @@
       <c r="V118" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W118" s="7"/>
-    </row>
-    <row r="119" spans="1:23" ht="90" x14ac:dyDescent="0.25">
+      <c r="W118" s="7" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="119" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A119" s="6" t="s">
         <v>415</v>
       </c>
@@ -14880,9 +15173,11 @@
       <c r="V119" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W119" s="7"/>
-    </row>
-    <row r="120" spans="1:23" ht="135" x14ac:dyDescent="0.25">
+      <c r="W119" s="7" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="120" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A120" s="6" t="s">
         <v>422</v>
       </c>
@@ -14951,7 +15246,7 @@
       </c>
       <c r="W120" s="7"/>
     </row>
-    <row r="121" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A121" s="6" t="s">
         <v>429</v>
       </c>
@@ -15020,7 +15315,7 @@
       </c>
       <c r="W121" s="7"/>
     </row>
-    <row r="122" spans="1:23" ht="135" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A122" s="6" t="s">
         <v>431</v>
       </c>
@@ -15089,7 +15384,7 @@
       </c>
       <c r="W122" s="7"/>
     </row>
-    <row r="123" spans="1:23" ht="135" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A123" s="6" t="s">
         <v>431</v>
       </c>
@@ -15158,7 +15453,7 @@
       </c>
       <c r="W123" s="7"/>
     </row>
-    <row r="124" spans="1:23" ht="135" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A124" s="6" t="s">
         <v>431</v>
       </c>
@@ -15227,7 +15522,7 @@
       </c>
       <c r="W124" s="7"/>
     </row>
-    <row r="125" spans="1:23" ht="135" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A125" s="6" t="s">
         <v>431</v>
       </c>
@@ -15296,7 +15591,7 @@
       </c>
       <c r="W125" s="7"/>
     </row>
-    <row r="126" spans="1:23" ht="150" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:23" ht="144" x14ac:dyDescent="0.3">
       <c r="A126" s="6" t="s">
         <v>452</v>
       </c>
@@ -15365,7 +15660,7 @@
       </c>
       <c r="W126" s="7"/>
     </row>
-    <row r="127" spans="1:23" ht="150" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:23" ht="144" x14ac:dyDescent="0.3">
       <c r="A127" s="6" t="s">
         <v>452</v>
       </c>
@@ -15434,7 +15729,7 @@
       </c>
       <c r="W127" s="7"/>
     </row>
-    <row r="128" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A128" s="6" t="s">
         <v>529</v>
       </c>
@@ -15503,7 +15798,7 @@
       </c>
       <c r="W128" s="7"/>
     </row>
-    <row r="129" spans="1:23" ht="90" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A129" s="6" t="s">
         <v>531</v>
       </c>
@@ -15572,7 +15867,7 @@
       </c>
       <c r="W129" s="7"/>
     </row>
-    <row r="130" spans="1:23" ht="90" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A130" s="6" t="s">
         <v>542</v>
       </c>
@@ -15641,7 +15936,7 @@
       </c>
       <c r="W130" s="7"/>
     </row>
-    <row r="131" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A131" s="6" t="s">
         <v>568</v>
       </c>
@@ -15710,7 +16005,7 @@
       </c>
       <c r="W131" s="7"/>
     </row>
-    <row r="132" spans="1:23" ht="63" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:23" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A132" s="6" t="s">
         <v>576</v>
       </c>
@@ -15779,7 +16074,7 @@
       </c>
       <c r="W132" s="7"/>
     </row>
-    <row r="133" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A133" s="6" t="s">
         <v>582</v>
       </c>
@@ -15846,9 +16141,11 @@
       <c r="V133" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W133" s="7"/>
-    </row>
-    <row r="134" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+      <c r="W133" s="7" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="134" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A134" s="6" t="s">
         <v>603</v>
       </c>
@@ -15917,7 +16214,7 @@
       </c>
       <c r="W134" s="7"/>
     </row>
-    <row r="135" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:23" ht="81" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="6" t="s">
         <v>611</v>
       </c>
@@ -15984,9 +16281,11 @@
       <c r="V135" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W135" s="7"/>
-    </row>
-    <row r="136" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+      <c r="W135" s="7" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="136" spans="1:23" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="6" t="s">
         <v>611</v>
       </c>
@@ -16053,9 +16352,11 @@
       <c r="V136" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W136" s="7"/>
-    </row>
-    <row r="137" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+      <c r="W136" s="7" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="137" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A137" s="6" t="s">
         <v>622</v>
       </c>
@@ -16124,7 +16425,7 @@
       </c>
       <c r="W137" s="7"/>
     </row>
-    <row r="138" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A138" s="6" t="s">
         <v>630</v>
       </c>
@@ -16193,7 +16494,7 @@
       </c>
       <c r="W138" s="7"/>
     </row>
-    <row r="139" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A139" s="6" t="s">
         <v>637</v>
       </c>
@@ -16262,7 +16563,7 @@
       </c>
       <c r="W139" s="7"/>
     </row>
-    <row r="140" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A140" s="6" t="s">
         <v>638</v>
       </c>
@@ -16331,7 +16632,7 @@
       </c>
       <c r="W140" s="7"/>
     </row>
-    <row r="141" spans="1:23" ht="90" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A141" s="6" t="s">
         <v>639</v>
       </c>
@@ -16400,7 +16701,7 @@
       </c>
       <c r="W141" s="7"/>
     </row>
-    <row r="142" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A142" s="6" t="s">
         <v>648</v>
       </c>
@@ -16469,7 +16770,7 @@
       </c>
       <c r="W142" s="7"/>
     </row>
-    <row r="143" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A143" s="6" t="s">
         <v>653</v>
       </c>
@@ -16538,7 +16839,7 @@
       </c>
       <c r="W143" s="7"/>
     </row>
-    <row r="144" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A144" s="6" t="s">
         <v>653</v>
       </c>
@@ -16607,7 +16908,7 @@
       </c>
       <c r="W144" s="7"/>
     </row>
-    <row r="145" spans="1:23" ht="75" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A145" s="6" t="s">
         <v>661</v>
       </c>
@@ -16676,7 +16977,7 @@
       </c>
       <c r="W145" s="7"/>
     </row>
-    <row r="146" spans="1:23" ht="75" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A146" s="6" t="s">
         <v>661</v>
       </c>
@@ -16745,7 +17046,7 @@
       </c>
       <c r="W146" s="7"/>
     </row>
-    <row r="147" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:23" ht="166.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="6" t="s">
         <v>669</v>
       </c>
@@ -16812,9 +17113,11 @@
       <c r="V147" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W147" s="7"/>
-    </row>
-    <row r="148" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W147" s="7" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="148" spans="1:23" ht="166.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="6" t="s">
         <v>669</v>
       </c>
@@ -16881,9 +17184,11 @@
       <c r="V148" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W148" s="7"/>
-    </row>
-    <row r="149" spans="1:23" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="W148" s="7" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="149" spans="1:23" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A149" s="6" t="s">
         <v>673</v>
       </c>
@@ -16952,7 +17257,7 @@
       </c>
       <c r="W149" s="7"/>
     </row>
-    <row r="150" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A150" s="6" t="s">
         <v>679</v>
       </c>
@@ -17021,7 +17326,7 @@
       </c>
       <c r="W150" s="7"/>
     </row>
-    <row r="151" spans="1:23" ht="90" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A151" s="6" t="s">
         <v>690</v>
       </c>
@@ -17090,7 +17395,7 @@
       </c>
       <c r="W151" s="7"/>
     </row>
-    <row r="152" spans="1:23" ht="90" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A152" s="6" t="s">
         <v>690</v>
       </c>
@@ -17159,7 +17464,7 @@
       </c>
       <c r="W152" s="7"/>
     </row>
-    <row r="153" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A153" s="6" t="s">
         <v>700</v>
       </c>
@@ -17228,7 +17533,7 @@
       </c>
       <c r="W153" s="7"/>
     </row>
-    <row r="154" spans="1:23" ht="135" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:23" ht="129.6" x14ac:dyDescent="0.25">
       <c r="A154" s="6" t="s">
         <v>721</v>
       </c>
@@ -17297,7 +17602,7 @@
       </c>
       <c r="W154" s="7"/>
     </row>
-    <row r="155" spans="1:23" ht="135" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:23" ht="129.6" x14ac:dyDescent="0.25">
       <c r="A155" s="6" t="s">
         <v>721</v>
       </c>
@@ -17366,7 +17671,7 @@
       </c>
       <c r="W155" s="7"/>
     </row>
-    <row r="156" spans="1:23" ht="135" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:23" ht="129.6" x14ac:dyDescent="0.25">
       <c r="A156" s="6" t="s">
         <v>721</v>
       </c>
@@ -17435,7 +17740,7 @@
       </c>
       <c r="W156" s="7"/>
     </row>
-    <row r="157" spans="1:23" ht="135" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:23" ht="129.6" x14ac:dyDescent="0.25">
       <c r="A157" s="6" t="s">
         <v>721</v>
       </c>
@@ -17504,7 +17809,7 @@
       </c>
       <c r="W157" s="7"/>
     </row>
-    <row r="158" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A158" s="6" t="s">
         <v>734</v>
       </c>
@@ -17573,7 +17878,7 @@
       </c>
       <c r="W158" s="7"/>
     </row>
-    <row r="159" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A159" s="6" t="s">
         <v>734</v>
       </c>
@@ -17642,7 +17947,7 @@
       </c>
       <c r="W159" s="7"/>
     </row>
-    <row r="160" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A160" s="6" t="s">
         <v>743</v>
       </c>
@@ -17711,7 +18016,7 @@
       </c>
       <c r="W160" s="7"/>
     </row>
-    <row r="161" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A161" s="6" t="s">
         <v>744</v>
       </c>
@@ -17780,7 +18085,7 @@
       </c>
       <c r="W161" s="7"/>
     </row>
-    <row r="162" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A162" s="6" t="s">
         <v>745</v>
       </c>
@@ -17849,7 +18154,7 @@
       </c>
       <c r="W162" s="7"/>
     </row>
-    <row r="163" spans="1:23" ht="120" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A163" s="6" t="s">
         <v>746</v>
       </c>
@@ -17918,7 +18223,7 @@
       </c>
       <c r="W163" s="7"/>
     </row>
-    <row r="164" spans="1:23" ht="120" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A164" s="6" t="s">
         <v>746</v>
       </c>
@@ -17987,7 +18292,7 @@
       </c>
       <c r="W164" s="7"/>
     </row>
-    <row r="165" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A165" s="6" t="s">
         <v>754</v>
       </c>
@@ -18056,7 +18361,7 @@
       </c>
       <c r="W165" s="7"/>
     </row>
-    <row r="166" spans="1:23" ht="78.75" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:23" ht="78" x14ac:dyDescent="0.25">
       <c r="A166" s="6" t="s">
         <v>762</v>
       </c>
@@ -18125,7 +18430,7 @@
       </c>
       <c r="W166" s="7"/>
     </row>
-    <row r="167" spans="1:23" ht="78.75" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:23" ht="78" x14ac:dyDescent="0.25">
       <c r="A167" s="6" t="s">
         <v>762</v>
       </c>
@@ -18194,7 +18499,7 @@
       </c>
       <c r="W167" s="7"/>
     </row>
-    <row r="168" spans="1:23" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:23" ht="78" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="6" t="s">
         <v>769</v>
       </c>
@@ -18261,9 +18566,11 @@
       <c r="V168" s="10" t="s">
         <v>1287</v>
       </c>
-      <c r="W168" s="7"/>
-    </row>
-    <row r="169" spans="1:23" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W168" s="7" t="s">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="169" spans="1:23" ht="77.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="6" t="s">
         <v>772</v>
       </c>
@@ -18330,9 +18637,11 @@
       <c r="V169" s="10" t="s">
         <v>1285</v>
       </c>
-      <c r="W169" s="7"/>
-    </row>
-    <row r="170" spans="1:23" ht="150" x14ac:dyDescent="0.2">
+      <c r="W169" s="7" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="170" spans="1:23" ht="115.2" x14ac:dyDescent="0.25">
       <c r="A170" s="6" t="s">
         <v>782</v>
       </c>
@@ -18399,9 +18708,11 @@
       <c r="V170" s="10" t="s">
         <v>1225</v>
       </c>
-      <c r="W170" s="7"/>
-    </row>
-    <row r="171" spans="1:23" ht="150" x14ac:dyDescent="0.2">
+      <c r="W170" s="7" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="171" spans="1:23" ht="115.2" x14ac:dyDescent="0.25">
       <c r="A171" s="6" t="s">
         <v>782</v>
       </c>
@@ -18468,9 +18779,11 @@
       <c r="V171" s="10" t="s">
         <v>1225</v>
       </c>
-      <c r="W171" s="7"/>
-    </row>
-    <row r="172" spans="1:23" ht="90" x14ac:dyDescent="0.25">
+      <c r="W171" s="7" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="172" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A172" s="6" t="s">
         <v>787</v>
       </c>
@@ -18539,7 +18852,7 @@
       </c>
       <c r="W172" s="7"/>
     </row>
-    <row r="173" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A173" s="6" t="s">
         <v>795</v>
       </c>
@@ -18608,7 +18921,7 @@
       </c>
       <c r="W173" s="7"/>
     </row>
-    <row r="174" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A174" s="6" t="s">
         <v>796</v>
       </c>
@@ -18675,9 +18988,11 @@
       <c r="V174" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W174" s="7"/>
-    </row>
-    <row r="175" spans="1:23" ht="60" x14ac:dyDescent="0.25">
+      <c r="W174" s="7" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="175" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A175" s="6" t="s">
         <v>804</v>
       </c>
@@ -18746,7 +19061,7 @@
       </c>
       <c r="W175" s="7"/>
     </row>
-    <row r="176" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A176" s="6" t="s">
         <v>811</v>
       </c>
@@ -18815,7 +19130,7 @@
       </c>
       <c r="W176" s="7"/>
     </row>
-    <row r="177" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A177" s="6" t="s">
         <v>812</v>
       </c>
@@ -18884,7 +19199,7 @@
       </c>
       <c r="W177" s="7"/>
     </row>
-    <row r="178" spans="1:23" ht="63" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:23" ht="201.6" x14ac:dyDescent="0.25">
       <c r="A178" s="6" t="s">
         <v>813</v>
       </c>
@@ -18951,9 +19266,11 @@
       <c r="V178" s="10" t="s">
         <v>1291</v>
       </c>
-      <c r="W178" s="7"/>
-    </row>
-    <row r="179" spans="1:23" ht="63" x14ac:dyDescent="0.2">
+      <c r="W178" s="7" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="179" spans="1:23" ht="201.6" x14ac:dyDescent="0.25">
       <c r="A179" s="6" t="s">
         <v>813</v>
       </c>
@@ -19020,9 +19337,11 @@
       <c r="V179" s="10" t="s">
         <v>1291</v>
       </c>
-      <c r="W179" s="7"/>
-    </row>
-    <row r="180" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W179" s="7" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="180" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A180" s="6" t="s">
         <v>822</v>
       </c>
@@ -19091,7 +19410,7 @@
       </c>
       <c r="W180" s="7"/>
     </row>
-    <row r="181" spans="1:23" ht="90" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:23" ht="109.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="6" t="s">
         <v>825</v>
       </c>
@@ -19158,9 +19477,11 @@
       <c r="V181" s="10" t="s">
         <v>1293</v>
       </c>
-      <c r="W181" s="7"/>
-    </row>
-    <row r="182" spans="1:23" ht="90" x14ac:dyDescent="0.2">
+      <c r="W181" s="7" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="182" spans="1:23" ht="86.4" x14ac:dyDescent="0.25">
       <c r="A182" s="6" t="s">
         <v>825</v>
       </c>
@@ -19227,9 +19548,11 @@
       <c r="V182" s="10" t="s">
         <v>1293</v>
       </c>
-      <c r="W182" s="7"/>
-    </row>
-    <row r="183" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+      <c r="W182" s="7" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="183" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A183" s="6" t="s">
         <v>841</v>
       </c>
@@ -19298,7 +19621,7 @@
       </c>
       <c r="W183" s="7"/>
     </row>
-    <row r="184" spans="1:23" ht="105" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A184" s="6" t="s">
         <v>834</v>
       </c>
@@ -19365,9 +19688,11 @@
       <c r="V184" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W184" s="7"/>
-    </row>
-    <row r="185" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W184" s="7" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="185" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A185" s="6" t="s">
         <v>834</v>
       </c>
@@ -19436,7 +19761,7 @@
       </c>
       <c r="W185" s="7"/>
     </row>
-    <row r="186" spans="1:23" ht="75" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A186" s="6" t="s">
         <v>842</v>
       </c>
@@ -19505,7 +19830,7 @@
       </c>
       <c r="W186" s="7"/>
     </row>
-    <row r="187" spans="1:23" ht="75" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A187" s="6" t="s">
         <v>849</v>
       </c>
@@ -19574,7 +19899,7 @@
       </c>
       <c r="W187" s="7"/>
     </row>
-    <row r="188" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A188" s="6" t="s">
         <v>850</v>
       </c>
@@ -19643,7 +19968,7 @@
       </c>
       <c r="W188" s="7"/>
     </row>
-    <row r="189" spans="1:23" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:23" ht="93.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="6" t="s">
         <v>851</v>
       </c>
@@ -19710,9 +20035,11 @@
       <c r="V189" s="10" t="s">
         <v>1295</v>
       </c>
-      <c r="W189" s="7"/>
-    </row>
-    <row r="190" spans="1:23" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="W189" s="7" t="s">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="190" spans="1:23" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A190" s="6" t="s">
         <v>853</v>
       </c>
@@ -19779,9 +20106,11 @@
       <c r="V190" s="10" t="s">
         <v>1296</v>
       </c>
-      <c r="W190" s="7"/>
-    </row>
-    <row r="191" spans="1:23" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="W190" s="7" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="191" spans="1:23" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A191" s="6" t="s">
         <v>860</v>
       </c>
@@ -19850,7 +20179,7 @@
       </c>
       <c r="W191" s="7"/>
     </row>
-    <row r="192" spans="1:23" ht="60" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A192" s="6" t="s">
         <v>861</v>
       </c>
@@ -19919,7 +20248,7 @@
       </c>
       <c r="W192" s="7"/>
     </row>
-    <row r="193" spans="1:23" ht="60" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A193" s="6" t="s">
         <v>861</v>
       </c>
@@ -19986,9 +20315,11 @@
       <c r="V193" s="10" t="s">
         <v>1298</v>
       </c>
-      <c r="W193" s="7"/>
-    </row>
-    <row r="194" spans="1:23" ht="90" x14ac:dyDescent="0.2">
+      <c r="W193" s="7" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="194" spans="1:23" ht="78" x14ac:dyDescent="0.25">
       <c r="A194" s="6" t="s">
         <v>868</v>
       </c>
@@ -20055,9 +20386,11 @@
       <c r="V194" s="10" t="s">
         <v>1300</v>
       </c>
-      <c r="W194" s="7"/>
-    </row>
-    <row r="195" spans="1:23" ht="90" x14ac:dyDescent="0.2">
+      <c r="W194" s="7" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="195" spans="1:23" ht="78" x14ac:dyDescent="0.25">
       <c r="A195" s="6" t="s">
         <v>868</v>
       </c>
@@ -20124,9 +20457,11 @@
       <c r="V195" s="10" t="s">
         <v>1300</v>
       </c>
-      <c r="W195" s="7"/>
-    </row>
-    <row r="196" spans="1:23" ht="78.75" x14ac:dyDescent="0.2">
+      <c r="W195" s="7" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="196" spans="1:23" ht="78" x14ac:dyDescent="0.25">
       <c r="A196" s="6" t="s">
         <v>879</v>
       </c>
@@ -20193,9 +20528,11 @@
       <c r="V196" s="10" t="s">
         <v>1302</v>
       </c>
-      <c r="W196" s="7"/>
-    </row>
-    <row r="197" spans="1:23" ht="78.75" x14ac:dyDescent="0.2">
+      <c r="W196" s="7" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="197" spans="1:23" ht="78" x14ac:dyDescent="0.25">
       <c r="A197" s="6" t="s">
         <v>879</v>
       </c>
@@ -20262,9 +20599,11 @@
       <c r="V197" s="10" t="s">
         <v>1302</v>
       </c>
-      <c r="W197" s="7"/>
-    </row>
-    <row r="198" spans="1:23" ht="60" x14ac:dyDescent="0.25">
+      <c r="W197" s="7" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="198" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A198" s="6" t="s">
         <v>883</v>
       </c>
@@ -20333,7 +20672,7 @@
       </c>
       <c r="W198" s="7"/>
     </row>
-    <row r="199" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A199" s="6" t="s">
         <v>892</v>
       </c>
@@ -20402,7 +20741,7 @@
       </c>
       <c r="W199" s="7"/>
     </row>
-    <row r="200" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A200" s="6" t="s">
         <v>894</v>
       </c>
@@ -20469,9 +20808,11 @@
       <c r="V200" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W200" s="7"/>
-    </row>
-    <row r="201" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+      <c r="W200" s="7" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="201" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A201" s="6" t="s">
         <v>895</v>
       </c>
@@ -20540,7 +20881,7 @@
       </c>
       <c r="W201" s="7"/>
     </row>
-    <row r="202" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A202" s="6" t="s">
         <v>900</v>
       </c>
@@ -20609,7 +20950,7 @@
       </c>
       <c r="W202" s="7"/>
     </row>
-    <row r="203" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A203" s="6" t="s">
         <v>897</v>
       </c>
@@ -20678,7 +21019,7 @@
       </c>
       <c r="W203" s="7"/>
     </row>
-    <row r="204" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A204" s="6" t="s">
         <v>897</v>
       </c>
@@ -20747,7 +21088,7 @@
       </c>
       <c r="W204" s="7"/>
     </row>
-    <row r="205" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A205" s="6" t="s">
         <v>901</v>
       </c>
@@ -20816,7 +21157,7 @@
       </c>
       <c r="W205" s="7"/>
     </row>
-    <row r="206" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:23" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="6" t="s">
         <v>902</v>
       </c>
@@ -20883,9 +21224,11 @@
       <c r="V206" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W206" s="7"/>
-    </row>
-    <row r="207" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+      <c r="W206" s="7" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="207" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A207" s="6" t="s">
         <v>903</v>
       </c>
@@ -20954,7 +21297,7 @@
       </c>
       <c r="W207" s="7"/>
     </row>
-    <row r="208" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A208" s="6" t="s">
         <v>904</v>
       </c>
@@ -21023,7 +21366,7 @@
       </c>
       <c r="W208" s="7"/>
     </row>
-    <row r="209" spans="1:23" ht="90" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A209" s="6" t="s">
         <v>905</v>
       </c>
@@ -21092,7 +21435,7 @@
       </c>
       <c r="W209" s="7"/>
     </row>
-    <row r="210" spans="1:23" ht="90" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A210" s="6" t="s">
         <v>915</v>
       </c>
@@ -21161,7 +21504,7 @@
       </c>
       <c r="W210" s="7"/>
     </row>
-    <row r="211" spans="1:23" ht="195" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:23" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A211" s="6" t="s">
         <v>916</v>
       </c>
@@ -21230,7 +21573,7 @@
       </c>
       <c r="W211" s="7"/>
     </row>
-    <row r="212" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A212" s="6" t="s">
         <v>924</v>
       </c>
@@ -21299,7 +21642,7 @@
       </c>
       <c r="W212" s="7"/>
     </row>
-    <row r="213" spans="1:23" ht="75" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:23" ht="60" x14ac:dyDescent="0.25">
       <c r="A213" s="6" t="s">
         <v>925</v>
       </c>
@@ -21368,7 +21711,7 @@
       </c>
       <c r="W213" s="7"/>
     </row>
-    <row r="214" spans="1:23" ht="60" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:23" ht="60" x14ac:dyDescent="0.25">
       <c r="A214" s="6" t="s">
         <v>932</v>
       </c>
@@ -21437,7 +21780,7 @@
       </c>
       <c r="W214" s="7"/>
     </row>
-    <row r="215" spans="1:23" ht="90" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:23" ht="72" x14ac:dyDescent="0.25">
       <c r="A215" s="6" t="s">
         <v>932</v>
       </c>
@@ -21506,7 +21849,7 @@
       </c>
       <c r="W215" s="7"/>
     </row>
-    <row r="216" spans="1:23" ht="60" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:23" ht="60" x14ac:dyDescent="0.25">
       <c r="A216" s="6" t="s">
         <v>932</v>
       </c>
@@ -21575,7 +21918,7 @@
       </c>
       <c r="W216" s="7"/>
     </row>
-    <row r="217" spans="1:23" ht="90" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A217" s="6" t="s">
         <v>944</v>
       </c>
@@ -21644,7 +21987,7 @@
       </c>
       <c r="W217" s="7"/>
     </row>
-    <row r="218" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A218" s="6" t="s">
         <v>945</v>
       </c>
@@ -21713,7 +22056,7 @@
       </c>
       <c r="W218" s="7"/>
     </row>
-    <row r="219" spans="1:23" ht="150" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:23" ht="144" x14ac:dyDescent="0.3">
       <c r="A219" s="6" t="s">
         <v>953</v>
       </c>
@@ -21782,7 +22125,7 @@
       </c>
       <c r="W219" s="7"/>
     </row>
-    <row r="220" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A220" s="6" t="s">
         <v>963</v>
       </c>
@@ -21851,7 +22194,7 @@
       </c>
       <c r="W220" s="7"/>
     </row>
-    <row r="221" spans="1:23" ht="60" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A221" s="6" t="s">
         <v>1210</v>
       </c>
@@ -21920,7 +22263,7 @@
       </c>
       <c r="W221" s="7"/>
     </row>
-    <row r="222" spans="1:23" ht="60" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A222" s="6" t="s">
         <v>1210</v>
       </c>
@@ -21989,7 +22332,7 @@
       </c>
       <c r="W222" s="7"/>
     </row>
-    <row r="223" spans="1:23" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:23" ht="78" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="6" t="s">
         <v>972</v>
       </c>
@@ -22056,9 +22399,11 @@
       <c r="V223" s="10" t="s">
         <v>1309</v>
       </c>
-      <c r="W223" s="7"/>
-    </row>
-    <row r="224" spans="1:23" ht="75" x14ac:dyDescent="0.25">
+      <c r="W223" s="7" t="s">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="224" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A224" s="6" t="s">
         <v>974</v>
       </c>
@@ -22125,9 +22470,11 @@
       <c r="V224" s="10" t="s">
         <v>1311</v>
       </c>
-      <c r="W224" s="7"/>
-    </row>
-    <row r="225" spans="1:23" ht="75" x14ac:dyDescent="0.25">
+      <c r="W224" s="7" t="s">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="225" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A225" s="6" t="s">
         <v>974</v>
       </c>
@@ -22194,9 +22541,11 @@
       <c r="V225" s="10" t="s">
         <v>1311</v>
       </c>
-      <c r="W225" s="7"/>
-    </row>
-    <row r="226" spans="1:23" ht="75" x14ac:dyDescent="0.25">
+      <c r="W225" s="7" t="s">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="226" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A226" s="6" t="s">
         <v>983</v>
       </c>
@@ -22265,7 +22614,7 @@
       </c>
       <c r="W226" s="7"/>
     </row>
-    <row r="227" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:23" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="6" t="s">
         <v>990</v>
       </c>
@@ -22332,9 +22681,11 @@
       <c r="V227" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W227" s="7"/>
-    </row>
-    <row r="228" spans="1:23" ht="105" x14ac:dyDescent="0.25">
+      <c r="W227" s="7" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="228" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A228" s="6" t="s">
         <v>991</v>
       </c>
@@ -22401,9 +22752,11 @@
       <c r="V228" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W228" s="7"/>
-    </row>
-    <row r="229" spans="1:23" ht="135" x14ac:dyDescent="0.25">
+      <c r="W228" s="7" t="s">
+        <v>1471</v>
+      </c>
+    </row>
+    <row r="229" spans="1:23" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A229" s="6" t="s">
         <v>992</v>
       </c>
@@ -22472,7 +22825,7 @@
       </c>
       <c r="W229" s="7"/>
     </row>
-    <row r="230" spans="1:23" ht="90" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:23" ht="187.2" x14ac:dyDescent="0.25">
       <c r="A230" s="6" t="s">
         <v>993</v>
       </c>
@@ -22539,9 +22892,11 @@
       <c r="V230" s="10" t="s">
         <v>1318</v>
       </c>
-      <c r="W230" s="7"/>
-    </row>
-    <row r="231" spans="1:23" ht="90" x14ac:dyDescent="0.2">
+      <c r="W230" s="7" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="231" spans="1:23" ht="187.2" x14ac:dyDescent="0.25">
       <c r="A231" s="6" t="s">
         <v>1000</v>
       </c>
@@ -22608,9 +22963,11 @@
       <c r="V231" s="10" t="s">
         <v>1318</v>
       </c>
-      <c r="W231" s="7"/>
-    </row>
-    <row r="232" spans="1:23" ht="63" x14ac:dyDescent="0.2">
+      <c r="W231" s="7" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="232" spans="1:23" ht="62.4" x14ac:dyDescent="0.25">
       <c r="A232" s="6" t="s">
         <v>1001</v>
       </c>
@@ -22677,9 +23034,11 @@
       <c r="V232" s="10" t="s">
         <v>1320</v>
       </c>
-      <c r="W232" s="7"/>
-    </row>
-    <row r="233" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+      <c r="W232" s="7" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="233" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A233" s="6" t="s">
         <v>1009</v>
       </c>
@@ -22748,7 +23107,7 @@
       </c>
       <c r="W233" s="7"/>
     </row>
-    <row r="234" spans="1:23" ht="165" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:23" ht="165" x14ac:dyDescent="0.25">
       <c r="A234" s="6" t="s">
         <v>1010</v>
       </c>
@@ -22815,9 +23174,11 @@
       <c r="V234" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W234" s="7"/>
-    </row>
-    <row r="235" spans="1:23" ht="165" x14ac:dyDescent="0.2">
+      <c r="W234" s="7" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="235" spans="1:23" ht="165" x14ac:dyDescent="0.25">
       <c r="A235" s="6" t="s">
         <v>1010</v>
       </c>
@@ -22884,9 +23245,11 @@
       <c r="V235" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W235" s="7"/>
-    </row>
-    <row r="236" spans="1:23" ht="157.5" x14ac:dyDescent="0.25">
+      <c r="W235" s="7" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="236" spans="1:23" ht="156" x14ac:dyDescent="0.3">
       <c r="A236" s="6" t="s">
         <v>1019</v>
       </c>
@@ -22953,9 +23316,11 @@
       <c r="V236" s="10" t="s">
         <v>1322</v>
       </c>
-      <c r="W236" s="7"/>
-    </row>
-    <row r="237" spans="1:23" ht="157.5" x14ac:dyDescent="0.25">
+      <c r="W236" s="7" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="237" spans="1:23" ht="156" x14ac:dyDescent="0.3">
       <c r="A237" s="6" t="s">
         <v>1020</v>
       </c>
@@ -23022,9 +23387,11 @@
       <c r="V237" s="10" t="s">
         <v>1322</v>
       </c>
-      <c r="W237" s="7"/>
-    </row>
-    <row r="238" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+      <c r="W237" s="7" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="238" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A238" s="6" t="s">
         <v>1022</v>
       </c>
@@ -23093,7 +23460,7 @@
       </c>
       <c r="W238" s="7"/>
     </row>
-    <row r="239" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A239" s="6" t="s">
         <v>896</v>
       </c>
@@ -23162,7 +23529,7 @@
       </c>
       <c r="W239" s="7"/>
     </row>
-    <row r="240" spans="1:23" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:23" ht="78" x14ac:dyDescent="0.3">
       <c r="A240" s="6" t="s">
         <v>1023</v>
       </c>
@@ -23231,7 +23598,7 @@
       </c>
       <c r="W240" s="7"/>
     </row>
-    <row r="241" spans="1:23" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:23" ht="78" x14ac:dyDescent="0.3">
       <c r="A241" s="6" t="s">
         <v>1023</v>
       </c>
@@ -23300,7 +23667,7 @@
       </c>
       <c r="W241" s="7"/>
     </row>
-    <row r="242" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A242" s="6" t="s">
         <v>1031</v>
       </c>
@@ -23369,7 +23736,7 @@
       </c>
       <c r="W242" s="7"/>
     </row>
-    <row r="243" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:23" ht="130.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="6" t="s">
         <v>1033</v>
       </c>
@@ -23436,9 +23803,11 @@
       <c r="V243" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W243" s="7"/>
-    </row>
-    <row r="244" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W243" s="7" t="s">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="244" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A244" s="6" t="s">
         <v>1034</v>
       </c>
@@ -23505,9 +23874,11 @@
       <c r="V244" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W244" s="7"/>
-    </row>
-    <row r="245" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+      <c r="W244" s="7" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="245" spans="1:23" ht="103.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="6" t="s">
         <v>1035</v>
       </c>
@@ -23574,9 +23945,11 @@
       <c r="V245" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W245" s="7"/>
-    </row>
-    <row r="246" spans="1:23" ht="75" x14ac:dyDescent="0.25">
+      <c r="W245" s="7" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="246" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A246" s="6" t="s">
         <v>1036</v>
       </c>
@@ -23645,7 +24018,7 @@
       </c>
       <c r="W246" s="7"/>
     </row>
-    <row r="247" spans="1:23" ht="90" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A247" s="6" t="s">
         <v>1037</v>
       </c>
@@ -23714,7 +24087,7 @@
       </c>
       <c r="W247" s="7"/>
     </row>
-    <row r="248" spans="1:23" ht="105" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A248" s="6" t="s">
         <v>1038</v>
       </c>
@@ -23783,7 +24156,7 @@
       </c>
       <c r="W248" s="7"/>
     </row>
-    <row r="249" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A249" s="6" t="s">
         <v>1039</v>
       </c>
@@ -23852,7 +24225,7 @@
       </c>
       <c r="W249" s="7"/>
     </row>
-    <row r="250" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A250" s="6" t="s">
         <v>1040</v>
       </c>
@@ -23921,7 +24294,7 @@
       </c>
       <c r="W250" s="7"/>
     </row>
-    <row r="251" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A251" s="6" t="s">
         <v>1041</v>
       </c>
@@ -23990,7 +24363,7 @@
       </c>
       <c r="W251" s="7"/>
     </row>
-    <row r="252" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A252" s="6" t="s">
         <v>1042</v>
       </c>
@@ -24059,7 +24432,7 @@
       </c>
       <c r="W252" s="7"/>
     </row>
-    <row r="253" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A253" s="6" t="s">
         <v>1043</v>
       </c>
@@ -24128,7 +24501,7 @@
       </c>
       <c r="W253" s="7"/>
     </row>
-    <row r="254" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A254" s="6" t="s">
         <v>1044</v>
       </c>
@@ -24197,7 +24570,7 @@
       </c>
       <c r="W254" s="7"/>
     </row>
-    <row r="255" spans="1:23" ht="63" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A255" s="6" t="s">
         <v>1045</v>
       </c>
@@ -24264,9 +24637,11 @@
       <c r="V255" s="10" t="s">
         <v>1325</v>
       </c>
-      <c r="W255" s="7"/>
-    </row>
-    <row r="256" spans="1:23" ht="63" x14ac:dyDescent="0.25">
+      <c r="W255" s="7" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="256" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A256" s="6" t="s">
         <v>1047</v>
       </c>
@@ -24333,9 +24708,11 @@
       <c r="V256" s="10" t="s">
         <v>1325</v>
       </c>
-      <c r="W256" s="7"/>
-    </row>
-    <row r="257" spans="1:23" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="W256" s="7" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="257" spans="1:23" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A257" s="6" t="s">
         <v>1048</v>
       </c>
@@ -24402,9 +24779,11 @@
       <c r="V257" s="10" t="s">
         <v>1327</v>
       </c>
-      <c r="W257" s="7"/>
-    </row>
-    <row r="258" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W257" s="7" t="s">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="258" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A258" s="6" t="s">
         <v>1052</v>
       </c>
@@ -24473,7 +24852,7 @@
       </c>
       <c r="W258" s="7"/>
     </row>
-    <row r="259" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A259" s="6" t="s">
         <v>1054</v>
       </c>
@@ -24542,7 +24921,7 @@
       </c>
       <c r="W259" s="7"/>
     </row>
-    <row r="260" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A260" s="6" t="s">
         <v>1055</v>
       </c>
@@ -24611,7 +24990,7 @@
       </c>
       <c r="W260" s="7"/>
     </row>
-    <row r="261" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A261" s="6" t="s">
         <v>1056</v>
       </c>
@@ -24680,7 +25059,7 @@
       </c>
       <c r="W261" s="7"/>
     </row>
-    <row r="262" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A262" s="6" t="s">
         <v>1057</v>
       </c>
@@ -24749,7 +25128,7 @@
       </c>
       <c r="W262" s="7"/>
     </row>
-    <row r="263" spans="1:23" ht="120" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A263" s="6" t="s">
         <v>1058</v>
       </c>
@@ -24816,9 +25195,11 @@
       <c r="V263" s="10" t="s">
         <v>1330</v>
       </c>
-      <c r="W263" s="7"/>
-    </row>
-    <row r="264" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W263" s="7" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="264" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A264" s="6" t="s">
         <v>1059</v>
       </c>
@@ -24887,7 +25268,7 @@
       </c>
       <c r="W264" s="7"/>
     </row>
-    <row r="265" spans="1:23" ht="99" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:23" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="6" t="s">
         <v>1060</v>
       </c>
@@ -24956,7 +25337,7 @@
       </c>
       <c r="W265" s="7"/>
     </row>
-    <row r="266" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A266" s="6" t="s">
         <v>1067</v>
       </c>
@@ -25023,9 +25404,11 @@
       <c r="V266" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W266" s="7"/>
-    </row>
-    <row r="267" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+      <c r="W266" s="7" t="s">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="267" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A267" s="6" t="s">
         <v>1071</v>
       </c>
@@ -25092,9 +25475,11 @@
       <c r="V267" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W267" s="7"/>
-    </row>
-    <row r="268" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+      <c r="W267" s="7" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="268" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A268" s="6" t="s">
         <v>1080</v>
       </c>
@@ -25161,9 +25546,11 @@
       <c r="V268" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W268" s="7"/>
-    </row>
-    <row r="269" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W268" s="7" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="269" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A269" s="6" t="s">
         <v>1083</v>
       </c>
@@ -25232,7 +25619,7 @@
       </c>
       <c r="W269" s="7"/>
     </row>
-    <row r="270" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A270" s="6" t="s">
         <v>1091</v>
       </c>
@@ -25301,7 +25688,7 @@
       </c>
       <c r="W270" s="7"/>
     </row>
-    <row r="271" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A271" s="6" t="s">
         <v>1098</v>
       </c>
@@ -25370,7 +25757,7 @@
       </c>
       <c r="W271" s="7"/>
     </row>
-    <row r="272" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A272" s="6" t="s">
         <v>1099</v>
       </c>
@@ -25439,7 +25826,7 @@
       </c>
       <c r="W272" s="7"/>
     </row>
-    <row r="273" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A273" s="6" t="s">
         <v>1105</v>
       </c>
@@ -25508,7 +25895,7 @@
       </c>
       <c r="W273" s="7"/>
     </row>
-    <row r="274" spans="1:23" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:23" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A274" s="6" t="s">
         <v>1109</v>
       </c>
@@ -25577,7 +25964,7 @@
       </c>
       <c r="W274" s="7"/>
     </row>
-    <row r="275" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A275" s="6" t="s">
         <v>1115</v>
       </c>
@@ -25646,7 +26033,7 @@
       </c>
       <c r="W275" s="7"/>
     </row>
-    <row r="276" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A276" s="6" t="s">
         <v>1122</v>
       </c>
@@ -25715,7 +26102,7 @@
       </c>
       <c r="W276" s="7"/>
     </row>
-    <row r="277" spans="1:23" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:23" ht="78" x14ac:dyDescent="0.3">
       <c r="A277" s="6" t="s">
         <v>1128</v>
       </c>
@@ -25784,7 +26171,7 @@
       </c>
       <c r="W277" s="7"/>
     </row>
-    <row r="278" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A278" s="6" t="s">
         <v>1136</v>
       </c>
@@ -25851,9 +26238,11 @@
       <c r="V278" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W278" s="7"/>
-    </row>
-    <row r="279" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W278" s="7" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="279" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A279" s="6" t="s">
         <v>1141</v>
       </c>
@@ -25922,7 +26311,7 @@
       </c>
       <c r="W279" s="7"/>
     </row>
-    <row r="280" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A280" s="6" t="s">
         <v>1137</v>
       </c>
@@ -25989,9 +26378,11 @@
       <c r="V280" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W280" s="7"/>
-    </row>
-    <row r="281" spans="1:23" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="W280" s="7" t="s">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="281" spans="1:23" ht="78" x14ac:dyDescent="0.3">
       <c r="A281" s="6" t="s">
         <v>1142</v>
       </c>
@@ -26058,9 +26449,11 @@
       <c r="V281" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W281" s="7"/>
-    </row>
-    <row r="282" spans="1:23" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="W281" s="7" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="282" spans="1:23" ht="78" x14ac:dyDescent="0.3">
       <c r="A282" s="6" t="s">
         <v>1142</v>
       </c>
@@ -26127,9 +26520,11 @@
       <c r="V282" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W282" s="7"/>
-    </row>
-    <row r="283" spans="1:23" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="W282" s="7" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="283" spans="1:23" ht="78" x14ac:dyDescent="0.3">
       <c r="A283" s="6" t="s">
         <v>1149</v>
       </c>
@@ -26196,9 +26591,11 @@
       <c r="V283" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W283" s="7"/>
-    </row>
-    <row r="284" spans="1:23" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="W283" s="7" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="284" spans="1:23" ht="78" x14ac:dyDescent="0.3">
       <c r="A284" s="6" t="s">
         <v>1149</v>
       </c>
@@ -26265,9 +26662,11 @@
       <c r="V284" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W284" s="7"/>
-    </row>
-    <row r="285" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W284" s="7" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="285" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A285" s="6" t="s">
         <v>1150</v>
       </c>
@@ -26336,7 +26735,7 @@
       </c>
       <c r="W285" s="7"/>
     </row>
-    <row r="286" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A286" s="6" t="s">
         <v>1150</v>
       </c>
@@ -26405,7 +26804,7 @@
       </c>
       <c r="W286" s="7"/>
     </row>
-    <row r="287" spans="1:23" ht="63" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:23" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A287" s="6" t="s">
         <v>1157</v>
       </c>
@@ -26474,7 +26873,7 @@
       </c>
       <c r="W287" s="7"/>
     </row>
-    <row r="288" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A288" s="6" t="s">
         <v>1162</v>
       </c>
@@ -26543,7 +26942,7 @@
       </c>
       <c r="W288" s="7"/>
     </row>
-    <row r="289" spans="1:23" ht="63" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:23" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A289" s="6" t="s">
         <v>1163</v>
       </c>
@@ -26612,7 +27011,7 @@
       </c>
       <c r="W289" s="7"/>
     </row>
-    <row r="290" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:23" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="6" t="s">
         <v>1171</v>
       </c>
@@ -26675,9 +27074,11 @@
       <c r="V290" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W290" s="7"/>
-    </row>
-    <row r="291" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+      <c r="W290" s="7" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="291" spans="1:23" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="6" t="s">
         <v>1172</v>
       </c>
@@ -26746,7 +27147,7 @@
       </c>
       <c r="W291" s="7"/>
     </row>
-    <row r="292" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A292" s="6" t="s">
         <v>1173</v>
       </c>
@@ -26815,7 +27216,7 @@
       </c>
       <c r="W292" s="7"/>
     </row>
-    <row r="293" spans="1:23" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:23" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A293" s="6" t="s">
         <v>1175</v>
       </c>
@@ -26882,9 +27283,11 @@
       <c r="V293" s="10" t="s">
         <v>1346</v>
       </c>
-      <c r="W293" s="7"/>
-    </row>
-    <row r="294" spans="1:23" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="W293" s="7" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="294" spans="1:23" ht="78" x14ac:dyDescent="0.3">
       <c r="A294" s="6" t="s">
         <v>1184</v>
       </c>
@@ -26953,7 +27356,7 @@
       </c>
       <c r="W294" s="7"/>
     </row>
-    <row r="295" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A295" s="6" t="s">
         <v>1193</v>
       </c>
@@ -27022,7 +27425,7 @@
       </c>
       <c r="W295" s="7"/>
     </row>
-    <row r="296" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A296" s="6" t="s">
         <v>1193</v>
       </c>
@@ -27091,7 +27494,7 @@
       </c>
       <c r="W296" s="7"/>
     </row>
-    <row r="297" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A297" s="16" t="s">
         <v>1200</v>
       </c>

--- a/dados_injetaveis.xlsx
+++ b/dados_injetaveis.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ejonh\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ejonh\Desktop\Aplicativo_Injetáveis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3BFBA8B-EFE5-4EF3-B8A4-6D5446BC3C7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF4C6596-54E2-45B1-9E77-025A85DF24B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="18624" windowHeight="10908" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5433,9 +5433,6 @@
     <t>Succinato Sódico de Hidrocortisona: Corticoide que apresenta incompatibilidade físico-química cruzada com sedativos e aminas em Y.  MEDICAMENTOS INCOMPATÍVEIS: Diazepam, Cloridrato de Dobutamina, Cloridrato de Midazolam, Fenitoína Sódica.</t>
   </si>
   <si>
-    <t>Incompatibilidades (Base stabilis.org)</t>
-  </si>
-  <si>
     <t>Imunoglobulina Antitimócito (Coelho): Proteína de alto peso molecular. Pode sofrer agregação ou precipitação física em contato com polímeros fortemente carregados como a heparina. MEDICAMENTOS INCOMPATÍVEIS: Heparina Sódica.</t>
   </si>
   <si>
@@ -5497,6 +5494,9 @@
   </si>
   <si>
     <t>Cloridrato de Vancomicina: Estrutura glicopeptídica complexa ácida. Desenvolve precipitados densos e imediatos em Y ao cruzar com quase todas as cefalosporinas e penicilinas baseadas em sais sódicos alcalinos. MEDICAMENTOS INCOMPATÍVEIS: Anfotericina B, Ampicilina Sódica, Ampicilina+Sulbactam, Aztreonam, Cefazolina Sódica, Cloridrato de Cefepima, Cefotaxima Sódica, Ceftazidima, Ceftriaxona Sódica, Cefuroxima Sódica, Diazepam, Furosemida, Heparina Sódica, Cetoprofeno, Metotrexato Sódico, Succinato Sódico de Metilprednisolona, Omeprazol, Oxacilina Sódica, Fenobarbital Sódico, Fenitoína Sódica, Piperacilina + Tazobactam, Bicarbonato de Sódio.</t>
+  </si>
+  <si>
+    <t>Incompatibilidades</t>
   </si>
 </sst>
 </file>
@@ -6532,7 +6532,7 @@
     <tableColumn id="20" xr3:uid="{3381B897-5F21-4B1A-88C9-CB9C7DFB3FED}" name="OBSERVAÇÕES " dataDxfId="3"/>
     <tableColumn id="21" xr3:uid="{1E22FF74-B6C9-420D-BF9C-1EFEBF09B20F}" name="CONCENTRAÇÃO DE INFUSÃO (Adulto)" dataDxfId="2"/>
     <tableColumn id="22" xr3:uid="{F1DAB99C-AB02-42ED-85FE-4A8DA8E1658D}" name="CONCENTRAÇÃO_ped INFUSÃO" dataDxfId="1"/>
-    <tableColumn id="23" xr3:uid="{3F2D921C-4D7A-4B21-9D59-254332C02760}" name="Incompatibilidades (Base stabilis.org)" dataDxfId="0"/>
+    <tableColumn id="23" xr3:uid="{3F2D921C-4D7A-4B21-9D59-254332C02760}" name="Incompatibilidades" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6916,7 +6916,7 @@
         <v>21</v>
       </c>
       <c r="W1" s="24" t="s">
-        <v>1465</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="158.4" x14ac:dyDescent="0.3">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="W9" s="7"/>
     </row>
-    <row r="10" spans="1:23" ht="115.2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" ht="129.6" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>774</v>
       </c>
@@ -7552,7 +7552,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="115.2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" ht="129.6" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>774</v>
       </c>
@@ -16074,7 +16074,7 @@
       </c>
       <c r="W132" s="7"/>
     </row>
-    <row r="133" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A133" s="6" t="s">
         <v>582</v>
       </c>
@@ -18641,7 +18641,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="170" spans="1:23" ht="115.2" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:23" ht="129.6" x14ac:dyDescent="0.25">
       <c r="A170" s="6" t="s">
         <v>782</v>
       </c>
@@ -18712,7 +18712,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="171" spans="1:23" ht="115.2" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:23" ht="129.6" x14ac:dyDescent="0.25">
       <c r="A171" s="6" t="s">
         <v>782</v>
       </c>
@@ -20809,7 +20809,7 @@
         <v>26</v>
       </c>
       <c r="W200" s="7" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="201" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
@@ -21225,7 +21225,7 @@
         <v>26</v>
       </c>
       <c r="W206" s="7" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="207" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
@@ -22400,7 +22400,7 @@
         <v>1309</v>
       </c>
       <c r="W223" s="7" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="224" spans="1:23" ht="72" x14ac:dyDescent="0.3">
@@ -22471,7 +22471,7 @@
         <v>1311</v>
       </c>
       <c r="W224" s="7" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="225" spans="1:23" ht="72" x14ac:dyDescent="0.3">
@@ -22542,7 +22542,7 @@
         <v>1311</v>
       </c>
       <c r="W225" s="7" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="226" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
@@ -22682,7 +22682,7 @@
         <v>26</v>
       </c>
       <c r="W227" s="7" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="228" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
@@ -22753,7 +22753,7 @@
         <v>26</v>
       </c>
       <c r="W228" s="7" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="229" spans="1:23" ht="93.6" x14ac:dyDescent="0.3">
@@ -22893,7 +22893,7 @@
         <v>1318</v>
       </c>
       <c r="W230" s="7" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="231" spans="1:23" ht="187.2" x14ac:dyDescent="0.25">
@@ -22964,7 +22964,7 @@
         <v>1318</v>
       </c>
       <c r="W231" s="7" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="232" spans="1:23" ht="62.4" x14ac:dyDescent="0.25">
@@ -23035,7 +23035,7 @@
         <v>1320</v>
       </c>
       <c r="W232" s="7" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="233" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
@@ -23107,7 +23107,7 @@
       </c>
       <c r="W233" s="7"/>
     </row>
-    <row r="234" spans="1:23" ht="165" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:23" ht="150" x14ac:dyDescent="0.25">
       <c r="A234" s="6" t="s">
         <v>1010</v>
       </c>
@@ -23175,10 +23175,10 @@
         <v>26</v>
       </c>
       <c r="W234" s="7" t="s">
-        <v>1474</v>
-      </c>
-    </row>
-    <row r="235" spans="1:23" ht="165" x14ac:dyDescent="0.25">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="235" spans="1:23" ht="150" x14ac:dyDescent="0.25">
       <c r="A235" s="6" t="s">
         <v>1010</v>
       </c>
@@ -23246,7 +23246,7 @@
         <v>26</v>
       </c>
       <c r="W235" s="7" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="236" spans="1:23" ht="156" x14ac:dyDescent="0.3">
@@ -23317,7 +23317,7 @@
         <v>1322</v>
       </c>
       <c r="W236" s="7" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="237" spans="1:23" ht="156" x14ac:dyDescent="0.3">
@@ -23388,7 +23388,7 @@
         <v>1322</v>
       </c>
       <c r="W237" s="7" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="238" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
@@ -23804,7 +23804,7 @@
         <v>26</v>
       </c>
       <c r="W243" s="7" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="244" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
@@ -23875,7 +23875,7 @@
         <v>26</v>
       </c>
       <c r="W244" s="7" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="245" spans="1:23" ht="103.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -23946,7 +23946,7 @@
         <v>26</v>
       </c>
       <c r="W245" s="7" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="246" spans="1:23" ht="72" x14ac:dyDescent="0.3">
@@ -24570,7 +24570,7 @@
       </c>
       <c r="W254" s="7"/>
     </row>
-    <row r="255" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A255" s="6" t="s">
         <v>1045</v>
       </c>
@@ -24638,10 +24638,10 @@
         <v>1325</v>
       </c>
       <c r="W255" s="7" t="s">
-        <v>1478</v>
-      </c>
-    </row>
-    <row r="256" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="256" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A256" s="6" t="s">
         <v>1047</v>
       </c>
@@ -24709,7 +24709,7 @@
         <v>1325</v>
       </c>
       <c r="W256" s="7" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="257" spans="1:23" ht="109.2" x14ac:dyDescent="0.3">
@@ -24780,7 +24780,7 @@
         <v>1327</v>
       </c>
       <c r="W257" s="7" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="258" spans="1:23" x14ac:dyDescent="0.3">
@@ -25196,7 +25196,7 @@
         <v>1330</v>
       </c>
       <c r="W263" s="7" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="264" spans="1:23" x14ac:dyDescent="0.3">
@@ -25405,7 +25405,7 @@
         <v>26</v>
       </c>
       <c r="W266" s="7" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="267" spans="1:23" ht="72" x14ac:dyDescent="0.3">
@@ -25476,7 +25476,7 @@
         <v>26</v>
       </c>
       <c r="W267" s="7" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="268" spans="1:23" ht="72" x14ac:dyDescent="0.3">
@@ -25547,7 +25547,7 @@
         <v>26</v>
       </c>
       <c r="W268" s="7" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="269" spans="1:23" x14ac:dyDescent="0.3">
@@ -26239,7 +26239,7 @@
         <v>26</v>
       </c>
       <c r="W278" s="7" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="279" spans="1:23" x14ac:dyDescent="0.3">
@@ -26379,7 +26379,7 @@
         <v>26</v>
       </c>
       <c r="W280" s="7" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="281" spans="1:23" ht="78" x14ac:dyDescent="0.3">
@@ -26450,7 +26450,7 @@
         <v>26</v>
       </c>
       <c r="W281" s="7" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="282" spans="1:23" ht="78" x14ac:dyDescent="0.3">
@@ -26521,7 +26521,7 @@
         <v>26</v>
       </c>
       <c r="W282" s="7" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="283" spans="1:23" ht="78" x14ac:dyDescent="0.3">
@@ -26592,7 +26592,7 @@
         <v>26</v>
       </c>
       <c r="W283" s="7" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="284" spans="1:23" ht="78" x14ac:dyDescent="0.3">
@@ -26663,7 +26663,7 @@
         <v>26</v>
       </c>
       <c r="W284" s="7" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="285" spans="1:23" x14ac:dyDescent="0.3">
@@ -27075,7 +27075,7 @@
         <v>26</v>
       </c>
       <c r="W290" s="7" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="291" spans="1:23" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -27284,7 +27284,7 @@
         <v>1346</v>
       </c>
       <c r="W293" s="7" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="294" spans="1:23" ht="78" x14ac:dyDescent="0.3">

--- a/dados_injetaveis.xlsx
+++ b/dados_injetaveis.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ejonh\Desktop\Aplicativo_Injetáveis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elton.freitas\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF4C6596-54E2-45B1-9E77-025A85DF24B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A5E5A02-2118-4855-AB68-F8A713FFBE30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="732" windowWidth="18624" windowHeight="10908" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6644" uniqueCount="1487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6827" uniqueCount="1487">
   <si>
     <t>MEDICAMENTO</t>
   </si>
@@ -6824,31 +6824,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W297"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="55.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="31.5546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="23.5546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="55.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="31.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" style="1" customWidth="1"/>
     <col min="5" max="5" width="25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.88671875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="23.44140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="55.6640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="54.5546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="126.33203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="131.44140625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="60.88671875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="255.6640625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="155.33203125" style="1" customWidth="1"/>
-    <col min="15" max="19" width="255.6640625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="101.33203125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="37.5546875" style="1" customWidth="1"/>
-    <col min="22" max="22" width="31.109375" style="1" customWidth="1"/>
-    <col min="23" max="23" width="49.88671875" style="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.109375" style="1"/>
+    <col min="6" max="6" width="20.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.42578125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="55.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="54.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="126.28515625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="131.42578125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="60.85546875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="255.7109375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="155.28515625" style="1" customWidth="1"/>
+    <col min="15" max="19" width="255.7109375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="101.28515625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="37.5703125" style="1" customWidth="1"/>
+    <col min="22" max="22" width="31.140625" style="1" customWidth="1"/>
+    <col min="23" max="23" width="49.85546875" style="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -6919,7 +6919,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" ht="165" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>180</v>
       </c>
@@ -6990,7 +6990,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" ht="165" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>180</v>
       </c>
@@ -7061,7 +7061,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="78" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>584</v>
       </c>
@@ -7132,7 +7132,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" ht="120" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>589</v>
       </c>
@@ -7199,9 +7199,11 @@
       <c r="V5" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W5" s="7"/>
-    </row>
-    <row r="6" spans="1:23" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="W5" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="63" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>595</v>
       </c>
@@ -7268,9 +7270,11 @@
       <c r="V6" s="10" t="s">
         <v>1217</v>
       </c>
-      <c r="W6" s="7"/>
-    </row>
-    <row r="7" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="W6" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="135" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>706</v>
       </c>
@@ -7341,7 +7345,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" ht="120" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>711</v>
       </c>
@@ -7412,7 +7416,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="78" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>729</v>
       </c>
@@ -7479,9 +7483,11 @@
       <c r="V9" s="10" t="s">
         <v>1223</v>
       </c>
-      <c r="W9" s="7"/>
-    </row>
-    <row r="10" spans="1:23" ht="129.6" x14ac:dyDescent="0.25">
+      <c r="W9" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="150" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>774</v>
       </c>
@@ -7552,7 +7558,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="129.6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" ht="150" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
         <v>774</v>
       </c>
@@ -7623,7 +7629,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" ht="150" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>188</v>
       </c>
@@ -7690,9 +7696,11 @@
       <c r="V12" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W12" s="7"/>
-    </row>
-    <row r="13" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="W12" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" ht="150" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>188</v>
       </c>
@@ -7759,9 +7767,11 @@
       <c r="V13" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W13" s="7"/>
-    </row>
-    <row r="14" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="W13" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" ht="150" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>188</v>
       </c>
@@ -7828,9 +7838,11 @@
       <c r="V14" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W14" s="7"/>
-    </row>
-    <row r="15" spans="1:23" ht="124.8" x14ac:dyDescent="0.3">
+      <c r="W14" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" ht="126" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>462</v>
       </c>
@@ -7897,9 +7909,11 @@
       <c r="V15" s="10" t="s">
         <v>1228</v>
       </c>
-      <c r="W15" s="7"/>
-    </row>
-    <row r="16" spans="1:23" ht="124.8" x14ac:dyDescent="0.3">
+      <c r="W15" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" ht="126" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>462</v>
       </c>
@@ -7966,9 +7980,11 @@
       <c r="V16" s="10" t="s">
         <v>1228</v>
       </c>
-      <c r="W16" s="7"/>
-    </row>
-    <row r="17" spans="1:23" ht="124.8" x14ac:dyDescent="0.3">
+      <c r="W16" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" ht="126" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>476</v>
       </c>
@@ -8035,9 +8051,11 @@
       <c r="V17" s="10" t="s">
         <v>1228</v>
       </c>
-      <c r="W17" s="7"/>
-    </row>
-    <row r="18" spans="1:23" ht="109.2" x14ac:dyDescent="0.3">
+      <c r="W17" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>480</v>
       </c>
@@ -8104,9 +8122,11 @@
       <c r="V18" s="10" t="s">
         <v>1230</v>
       </c>
-      <c r="W18" s="7"/>
-    </row>
-    <row r="19" spans="1:23" ht="109.2" x14ac:dyDescent="0.3">
+      <c r="W18" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>480</v>
       </c>
@@ -8173,9 +8193,11 @@
       <c r="V19" s="10" t="s">
         <v>1230</v>
       </c>
-      <c r="W19" s="7"/>
-    </row>
-    <row r="20" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="W19" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" ht="150" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>489</v>
       </c>
@@ -8242,9 +8264,11 @@
       <c r="V20" s="10" t="s">
         <v>1232</v>
       </c>
-      <c r="W20" s="7"/>
-    </row>
-    <row r="21" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="W20" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" ht="150" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>489</v>
       </c>
@@ -8311,9 +8335,11 @@
       <c r="V21" s="10" t="s">
         <v>1232</v>
       </c>
-      <c r="W21" s="7"/>
-    </row>
-    <row r="22" spans="1:23" ht="109.2" x14ac:dyDescent="0.3">
+      <c r="W21" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>512</v>
       </c>
@@ -8380,9 +8406,11 @@
       <c r="V22" s="10" t="s">
         <v>1234</v>
       </c>
-      <c r="W22" s="7"/>
-    </row>
-    <row r="23" spans="1:23" ht="109.2" x14ac:dyDescent="0.3">
+      <c r="W22" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>502</v>
       </c>
@@ -8449,9 +8477,11 @@
       <c r="V23" s="10" t="s">
         <v>1236</v>
       </c>
-      <c r="W23" s="7"/>
-    </row>
-    <row r="24" spans="1:23" ht="93.6" x14ac:dyDescent="0.3">
+      <c r="W23" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>513</v>
       </c>
@@ -8518,9 +8548,11 @@
       <c r="V24" s="10" t="s">
         <v>1238</v>
       </c>
-      <c r="W24" s="7"/>
-    </row>
-    <row r="25" spans="1:23" ht="93.6" x14ac:dyDescent="0.3">
+      <c r="W24" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>524</v>
       </c>
@@ -8587,9 +8619,11 @@
       <c r="V25" s="10" t="s">
         <v>1238</v>
       </c>
-      <c r="W25" s="7"/>
-    </row>
-    <row r="26" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="W25" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" ht="120" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>559</v>
       </c>
@@ -8660,7 +8694,7 @@
         <v>1435</v>
       </c>
     </row>
-    <row r="27" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>569</v>
       </c>
@@ -8727,9 +8761,11 @@
       <c r="V27" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W27" s="7"/>
-    </row>
-    <row r="28" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="W27" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" ht="105" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>548</v>
       </c>
@@ -8796,9 +8832,11 @@
       <c r="V28" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W28" s="7"/>
-    </row>
-    <row r="29" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+      <c r="W28" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" ht="75" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>720</v>
       </c>
@@ -8867,7 +8905,7 @@
         <v>1436</v>
       </c>
     </row>
-    <row r="30" spans="1:23" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:23" ht="180" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>22</v>
       </c>
@@ -8934,9 +8972,11 @@
       <c r="V30" s="10" t="s">
         <v>1242</v>
       </c>
-      <c r="W30" s="7"/>
-    </row>
-    <row r="31" spans="1:23" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="W30" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" ht="180" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>22</v>
       </c>
@@ -9003,9 +9043,11 @@
       <c r="V31" s="10" t="s">
         <v>1242</v>
       </c>
-      <c r="W31" s="7"/>
-    </row>
-    <row r="32" spans="1:23" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="W31" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" ht="180" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>22</v>
       </c>
@@ -9072,9 +9114,11 @@
       <c r="V32" s="10" t="s">
         <v>1242</v>
       </c>
-      <c r="W32" s="7"/>
-    </row>
-    <row r="33" spans="1:23" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="W32" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" ht="180" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>22</v>
       </c>
@@ -9141,9 +9185,11 @@
       <c r="V33" s="10" t="s">
         <v>1242</v>
       </c>
-      <c r="W33" s="7"/>
-    </row>
-    <row r="34" spans="1:23" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="W33" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" ht="180" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>22</v>
       </c>
@@ -9210,9 +9256,11 @@
       <c r="V34" s="10" t="s">
         <v>1242</v>
       </c>
-      <c r="W34" s="7"/>
-    </row>
-    <row r="35" spans="1:23" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="W34" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" ht="195" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>22</v>
       </c>
@@ -9279,9 +9327,11 @@
       <c r="V35" s="10" t="s">
         <v>1242</v>
       </c>
-      <c r="W35" s="7"/>
-    </row>
-    <row r="36" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="W35" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" ht="120" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>41</v>
       </c>
@@ -9352,7 +9402,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="37" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:23" ht="120" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>41</v>
       </c>
@@ -9423,7 +9473,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="38" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:23" ht="120" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>41</v>
       </c>
@@ -9494,7 +9544,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="39" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:23" ht="105" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>55</v>
       </c>
@@ -9561,9 +9611,11 @@
       <c r="V39" s="10" t="s">
         <v>1245</v>
       </c>
-      <c r="W39" s="7"/>
-    </row>
-    <row r="40" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="W39" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="90" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
         <v>64</v>
       </c>
@@ -9630,9 +9682,11 @@
       <c r="V40" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W40" s="7"/>
-    </row>
-    <row r="41" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="W40" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="90" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
         <v>64</v>
       </c>
@@ -9699,9 +9753,11 @@
       <c r="V41" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W41" s="7"/>
-    </row>
-    <row r="42" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="W41" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" ht="90" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
         <v>64</v>
       </c>
@@ -9768,9 +9824,11 @@
       <c r="V42" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W42" s="7"/>
-    </row>
-    <row r="43" spans="1:23" ht="144" x14ac:dyDescent="0.3">
+      <c r="W42" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" ht="150" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
         <v>78</v>
       </c>
@@ -9837,9 +9895,11 @@
       <c r="V43" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W43" s="7"/>
-    </row>
-    <row r="44" spans="1:23" ht="144" x14ac:dyDescent="0.3">
+      <c r="W43" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" ht="150" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>78</v>
       </c>
@@ -9906,9 +9966,11 @@
       <c r="V44" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W44" s="7"/>
-    </row>
-    <row r="45" spans="1:23" ht="144" x14ac:dyDescent="0.3">
+      <c r="W44" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" ht="150" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
         <v>78</v>
       </c>
@@ -9975,9 +10037,11 @@
       <c r="V45" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W45" s="7"/>
-    </row>
-    <row r="46" spans="1:23" ht="144" x14ac:dyDescent="0.3">
+      <c r="W45" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" ht="150" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>78</v>
       </c>
@@ -10044,9 +10108,11 @@
       <c r="V46" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W46" s="7"/>
-    </row>
-    <row r="47" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+      <c r="W46" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="75" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
         <v>90</v>
       </c>
@@ -10117,7 +10183,7 @@
         <v>1438</v>
       </c>
     </row>
-    <row r="48" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:23" ht="75" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>90</v>
       </c>
@@ -10188,7 +10254,7 @@
         <v>1438</v>
       </c>
     </row>
-    <row r="49" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>99</v>
       </c>
@@ -10255,9 +10321,11 @@
       <c r="V49" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W49" s="7"/>
-    </row>
-    <row r="50" spans="1:23" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="W49" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" ht="195" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>100</v>
       </c>
@@ -10324,9 +10392,11 @@
       <c r="V50" s="10" t="s">
         <v>1248</v>
       </c>
-      <c r="W50" s="7"/>
-    </row>
-    <row r="51" spans="1:23" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="W50" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" ht="195" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
         <v>100</v>
       </c>
@@ -10393,9 +10463,11 @@
       <c r="V51" s="10" t="s">
         <v>1248</v>
       </c>
-      <c r="W51" s="7"/>
-    </row>
-    <row r="52" spans="1:23" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="W51" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" ht="195" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>100</v>
       </c>
@@ -10462,9 +10534,11 @@
       <c r="V52" s="10" t="s">
         <v>1248</v>
       </c>
-      <c r="W52" s="7"/>
-    </row>
-    <row r="53" spans="1:23" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="W52" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" ht="195" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
         <v>100</v>
       </c>
@@ -10531,9 +10605,11 @@
       <c r="V53" s="10" t="s">
         <v>1248</v>
       </c>
-      <c r="W53" s="7"/>
-    </row>
-    <row r="54" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="W53" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
         <v>123</v>
       </c>
@@ -10600,9 +10676,11 @@
       <c r="V54" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="W54" s="7"/>
-    </row>
-    <row r="55" spans="1:23" ht="144" x14ac:dyDescent="0.3">
+      <c r="W54" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" ht="150" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>112</v>
       </c>
@@ -10673,7 +10751,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="56" spans="1:23" ht="144" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:23" ht="150" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
         <v>112</v>
       </c>
@@ -10744,7 +10822,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="57" spans="1:23" ht="119.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:23" ht="119.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
         <v>124</v>
       </c>
@@ -10811,9 +10889,11 @@
       <c r="V57" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="W57" s="7"/>
-    </row>
-    <row r="58" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="W57" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23" ht="90" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
         <v>139</v>
       </c>
@@ -10880,9 +10960,11 @@
       <c r="V58" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="W58" s="7"/>
-    </row>
-    <row r="59" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="W58" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" ht="90" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
         <v>139</v>
       </c>
@@ -10949,9 +11031,11 @@
       <c r="V59" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="W59" s="7"/>
-    </row>
-    <row r="60" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="W59" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" ht="90" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
         <v>139</v>
       </c>
@@ -11018,9 +11102,11 @@
       <c r="V60" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="W60" s="7"/>
-    </row>
-    <row r="61" spans="1:23" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="W60" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" ht="165" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
         <v>149</v>
       </c>
@@ -11087,9 +11173,11 @@
       <c r="V61" s="10" t="s">
         <v>1253</v>
       </c>
-      <c r="W61" s="7"/>
-    </row>
-    <row r="62" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="W61" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" ht="120" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
         <v>162</v>
       </c>
@@ -11160,7 +11248,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="63" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:23" ht="120" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
         <v>162</v>
       </c>
@@ -11231,7 +11319,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="64" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:23" ht="120" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
         <v>162</v>
       </c>
@@ -11302,7 +11390,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="65" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:23" ht="120" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
         <v>162</v>
       </c>
@@ -11373,7 +11461,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="66" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:23" ht="120" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
         <v>162</v>
       </c>
@@ -11444,7 +11532,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="67" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:23" ht="120" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
         <v>162</v>
       </c>
@@ -11515,7 +11603,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="68" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
         <v>172</v>
       </c>
@@ -11582,9 +11670,11 @@
       <c r="V68" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W68" s="7"/>
-    </row>
-    <row r="69" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="W68" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
         <v>173</v>
       </c>
@@ -11651,9 +11741,11 @@
       <c r="V69" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W69" s="7"/>
-    </row>
-    <row r="70" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="W69" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" ht="135" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
         <v>174</v>
       </c>
@@ -11724,7 +11816,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="71" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:23" ht="135" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
         <v>174</v>
       </c>
@@ -11795,7 +11887,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="72" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:23" ht="135" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
         <v>174</v>
       </c>
@@ -11866,7 +11958,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="73" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:23" ht="135" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
         <v>174</v>
       </c>
@@ -11937,7 +12029,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="74" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:23" ht="135" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
         <v>205</v>
       </c>
@@ -12008,7 +12100,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="75" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:23" ht="135" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
         <v>205</v>
       </c>
@@ -12079,7 +12171,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="76" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:23" ht="135" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
         <v>205</v>
       </c>
@@ -12150,7 +12242,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="77" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:23" ht="135" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
         <v>205</v>
       </c>
@@ -12221,7 +12313,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="78" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:23" ht="135" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
         <v>221</v>
       </c>
@@ -12292,7 +12384,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="79" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:23" ht="135" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
         <v>221</v>
       </c>
@@ -12363,7 +12455,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="80" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:23" ht="120" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
         <v>223</v>
       </c>
@@ -12434,7 +12526,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="81" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:23" ht="120" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
         <v>223</v>
       </c>
@@ -12505,7 +12597,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="82" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:23" ht="120" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
         <v>223</v>
       </c>
@@ -12576,7 +12668,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="83" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:23" ht="120" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
         <v>223</v>
       </c>
@@ -12647,7 +12739,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="84" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:23" ht="120" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
         <v>223</v>
       </c>
@@ -12718,7 +12810,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="85" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:23" ht="120" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
         <v>223</v>
       </c>
@@ -12789,7 +12881,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="86" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:23" ht="120" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
         <v>223</v>
       </c>
@@ -12860,7 +12952,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="87" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:23" ht="120" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
         <v>223</v>
       </c>
@@ -12931,7 +13023,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="88" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:23" ht="120" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
         <v>263</v>
       </c>
@@ -13002,7 +13094,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="89" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:23" ht="120" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
         <v>252</v>
       </c>
@@ -13073,7 +13165,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="90" spans="1:23" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:23" ht="172.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
         <v>239</v>
       </c>
@@ -13144,7 +13236,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="91" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:23" ht="90" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
         <v>273</v>
       </c>
@@ -13211,9 +13303,11 @@
       <c r="V91" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W91" s="7"/>
-    </row>
-    <row r="92" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="W91" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="92" spans="1:23" ht="90" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
         <v>273</v>
       </c>
@@ -13280,9 +13374,11 @@
       <c r="V92" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W92" s="7"/>
-    </row>
-    <row r="93" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="W92" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="93" spans="1:23" ht="90" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
         <v>286</v>
       </c>
@@ -13349,9 +13445,11 @@
       <c r="V93" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W93" s="7"/>
-    </row>
-    <row r="94" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+      <c r="W93" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="94" spans="1:23" ht="75" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
         <v>290</v>
       </c>
@@ -13422,7 +13520,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="95" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:23" ht="75" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
         <v>290</v>
       </c>
@@ -13493,7 +13591,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="96" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:23" ht="75" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
         <v>290</v>
       </c>
@@ -13564,7 +13662,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="97" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:23" ht="75" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
         <v>300</v>
       </c>
@@ -13635,7 +13733,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="98" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:23" ht="75" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
         <v>300</v>
       </c>
@@ -13706,7 +13804,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="99" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:23" ht="75" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
         <v>300</v>
       </c>
@@ -13777,7 +13875,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="100" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:23" ht="75" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
         <v>300</v>
       </c>
@@ -13848,7 +13946,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="101" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:23" ht="60" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
         <v>308</v>
       </c>
@@ -13919,7 +14017,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="102" spans="1:23" ht="165.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:23" ht="165.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
         <v>308</v>
       </c>
@@ -13990,7 +14088,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="103" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:23" ht="75" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
         <v>322</v>
       </c>
@@ -14061,7 +14159,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="104" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:23" ht="75" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
         <v>322</v>
       </c>
@@ -14132,7 +14230,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="105" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
         <v>338</v>
       </c>
@@ -14199,9 +14297,11 @@
       <c r="V105" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W105" s="7"/>
-    </row>
-    <row r="106" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="W105" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="106" spans="1:23" ht="60" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
         <v>338</v>
       </c>
@@ -14268,9 +14368,11 @@
       <c r="V106" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W106" s="7"/>
-    </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="W106" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="107" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A107" s="6" t="s">
         <v>347</v>
       </c>
@@ -14337,9 +14439,11 @@
       <c r="V107" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W107" s="7"/>
-    </row>
-    <row r="108" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="W107" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="108" spans="1:23" ht="90" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
         <v>348</v>
       </c>
@@ -14406,9 +14510,11 @@
       <c r="V108" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W108" s="7"/>
-    </row>
-    <row r="109" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="W108" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="109" spans="1:23" ht="90" x14ac:dyDescent="0.25">
       <c r="A109" s="6" t="s">
         <v>348</v>
       </c>
@@ -14475,9 +14581,11 @@
       <c r="V109" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W109" s="7"/>
-    </row>
-    <row r="110" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="W109" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="110" spans="1:23" ht="135" x14ac:dyDescent="0.25">
       <c r="A110" s="6" t="s">
         <v>365</v>
       </c>
@@ -14544,9 +14652,11 @@
       <c r="V110" s="10" t="s">
         <v>1268</v>
       </c>
-      <c r="W110" s="7"/>
-    </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="W110" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="111" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A111" s="6" t="s">
         <v>378</v>
       </c>
@@ -14613,9 +14723,11 @@
       <c r="V111" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W111" s="7"/>
-    </row>
-    <row r="112" spans="1:23" ht="78" x14ac:dyDescent="0.3">
+      <c r="W111" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="112" spans="1:23" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A112" s="6" t="s">
         <v>379</v>
       </c>
@@ -14682,9 +14794,11 @@
       <c r="V112" s="10" t="s">
         <v>1271</v>
       </c>
-      <c r="W112" s="7"/>
-    </row>
-    <row r="113" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="W112" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="113" spans="1:23" ht="60" x14ac:dyDescent="0.25">
       <c r="A113" s="6" t="s">
         <v>382</v>
       </c>
@@ -14751,9 +14865,11 @@
       <c r="V113" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W113" s="7"/>
-    </row>
-    <row r="114" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="W113" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="114" spans="1:23" ht="60" x14ac:dyDescent="0.25">
       <c r="A114" s="6" t="s">
         <v>382</v>
       </c>
@@ -14820,9 +14936,11 @@
       <c r="V114" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W114" s="7"/>
-    </row>
-    <row r="115" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="W114" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="115" spans="1:23" ht="90" x14ac:dyDescent="0.25">
       <c r="A115" s="6" t="s">
         <v>390</v>
       </c>
@@ -14893,7 +15011,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="116" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:23" ht="90" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
         <v>390</v>
       </c>
@@ -14964,7 +15082,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="117" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:23" ht="75" x14ac:dyDescent="0.25">
       <c r="A117" s="6" t="s">
         <v>399</v>
       </c>
@@ -15035,7 +15153,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="118" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:23" ht="75" x14ac:dyDescent="0.25">
       <c r="A118" s="6" t="s">
         <v>407</v>
       </c>
@@ -15106,7 +15224,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="119" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:23" ht="90" x14ac:dyDescent="0.25">
       <c r="A119" s="6" t="s">
         <v>415</v>
       </c>
@@ -15177,7 +15295,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="120" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:23" ht="135" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
         <v>422</v>
       </c>
@@ -15244,9 +15362,11 @@
       <c r="V120" s="10" t="s">
         <v>1272</v>
       </c>
-      <c r="W120" s="7"/>
-    </row>
-    <row r="121" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="W120" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="121" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A121" s="6" t="s">
         <v>429</v>
       </c>
@@ -15313,9 +15433,11 @@
       <c r="V121" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W121" s="7"/>
-    </row>
-    <row r="122" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="W121" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="122" spans="1:23" ht="135" x14ac:dyDescent="0.25">
       <c r="A122" s="6" t="s">
         <v>431</v>
       </c>
@@ -15382,9 +15504,11 @@
       <c r="V122" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W122" s="7"/>
-    </row>
-    <row r="123" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="W122" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="123" spans="1:23" ht="135" x14ac:dyDescent="0.25">
       <c r="A123" s="6" t="s">
         <v>431</v>
       </c>
@@ -15451,9 +15575,11 @@
       <c r="V123" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W123" s="7"/>
-    </row>
-    <row r="124" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="W123" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="124" spans="1:23" ht="135" x14ac:dyDescent="0.25">
       <c r="A124" s="6" t="s">
         <v>431</v>
       </c>
@@ -15520,9 +15646,11 @@
       <c r="V124" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W124" s="7"/>
-    </row>
-    <row r="125" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="W124" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="125" spans="1:23" ht="135" x14ac:dyDescent="0.25">
       <c r="A125" s="6" t="s">
         <v>431</v>
       </c>
@@ -15589,9 +15717,11 @@
       <c r="V125" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W125" s="7"/>
-    </row>
-    <row r="126" spans="1:23" ht="144" x14ac:dyDescent="0.3">
+      <c r="W125" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="126" spans="1:23" ht="150" x14ac:dyDescent="0.25">
       <c r="A126" s="6" t="s">
         <v>452</v>
       </c>
@@ -15658,9 +15788,11 @@
       <c r="V126" s="10" t="s">
         <v>1276</v>
       </c>
-      <c r="W126" s="7"/>
-    </row>
-    <row r="127" spans="1:23" ht="144" x14ac:dyDescent="0.3">
+      <c r="W126" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="127" spans="1:23" ht="150" x14ac:dyDescent="0.25">
       <c r="A127" s="6" t="s">
         <v>452</v>
       </c>
@@ -15727,9 +15859,11 @@
       <c r="V127" s="10" t="s">
         <v>1277</v>
       </c>
-      <c r="W127" s="7"/>
-    </row>
-    <row r="128" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="W127" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="128" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
         <v>529</v>
       </c>
@@ -15796,9 +15930,11 @@
       <c r="V128" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W128" s="7"/>
-    </row>
-    <row r="129" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="W128" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="129" spans="1:23" ht="90" x14ac:dyDescent="0.25">
       <c r="A129" s="6" t="s">
         <v>531</v>
       </c>
@@ -15865,9 +16001,11 @@
       <c r="V129" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W129" s="7"/>
-    </row>
-    <row r="130" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="W129" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="130" spans="1:23" ht="90" x14ac:dyDescent="0.25">
       <c r="A130" s="6" t="s">
         <v>542</v>
       </c>
@@ -15934,9 +16072,11 @@
       <c r="V130" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W130" s="7"/>
-    </row>
-    <row r="131" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="W130" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="131" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A131" s="6" t="s">
         <v>568</v>
       </c>
@@ -16003,9 +16143,11 @@
       <c r="V131" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W131" s="7"/>
-    </row>
-    <row r="132" spans="1:23" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="W131" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="132" spans="1:23" ht="63" x14ac:dyDescent="0.25">
       <c r="A132" s="6" t="s">
         <v>576</v>
       </c>
@@ -16072,9 +16214,11 @@
       <c r="V132" s="10" t="s">
         <v>1353</v>
       </c>
-      <c r="W132" s="7"/>
-    </row>
-    <row r="133" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="W132" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="133" spans="1:23" ht="75" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
         <v>582</v>
       </c>
@@ -16145,7 +16289,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="134" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A134" s="6" t="s">
         <v>603</v>
       </c>
@@ -16212,9 +16356,11 @@
       <c r="V134" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W134" s="7"/>
-    </row>
-    <row r="135" spans="1:23" ht="81" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="W134" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="135" spans="1:23" ht="81" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="6" t="s">
         <v>611</v>
       </c>
@@ -16285,7 +16431,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="136" spans="1:23" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:23" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="6" t="s">
         <v>611</v>
       </c>
@@ -16356,7 +16502,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="137" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A137" s="6" t="s">
         <v>622</v>
       </c>
@@ -16423,9 +16569,11 @@
       <c r="V137" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W137" s="7"/>
-    </row>
-    <row r="138" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="W137" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="138" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A138" s="6" t="s">
         <v>630</v>
       </c>
@@ -16492,9 +16640,11 @@
       <c r="V138" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W138" s="7"/>
-    </row>
-    <row r="139" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="W138" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="139" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A139" s="6" t="s">
         <v>637</v>
       </c>
@@ -16561,9 +16711,11 @@
       <c r="V139" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W139" s="7"/>
-    </row>
-    <row r="140" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="W139" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="140" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A140" s="6" t="s">
         <v>638</v>
       </c>
@@ -16630,9 +16782,11 @@
       <c r="V140" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W140" s="7"/>
-    </row>
-    <row r="141" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="W140" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="141" spans="1:23" ht="90" x14ac:dyDescent="0.25">
       <c r="A141" s="6" t="s">
         <v>639</v>
       </c>
@@ -16699,9 +16853,11 @@
       <c r="V141" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W141" s="7"/>
-    </row>
-    <row r="142" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="W141" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="142" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A142" s="6" t="s">
         <v>648</v>
       </c>
@@ -16768,9 +16924,11 @@
       <c r="V142" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W142" s="7"/>
-    </row>
-    <row r="143" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="W142" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="143" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A143" s="6" t="s">
         <v>653</v>
       </c>
@@ -16837,9 +16995,11 @@
       <c r="V143" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W143" s="7"/>
-    </row>
-    <row r="144" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="W143" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="144" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A144" s="6" t="s">
         <v>653</v>
       </c>
@@ -16906,9 +17066,11 @@
       <c r="V144" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W144" s="7"/>
-    </row>
-    <row r="145" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+      <c r="W144" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="145" spans="1:23" ht="75" x14ac:dyDescent="0.25">
       <c r="A145" s="6" t="s">
         <v>661</v>
       </c>
@@ -16975,9 +17137,11 @@
       <c r="V145" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W145" s="7"/>
-    </row>
-    <row r="146" spans="1:23" ht="72" x14ac:dyDescent="0.25">
+      <c r="W145" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="146" spans="1:23" ht="75" x14ac:dyDescent="0.2">
       <c r="A146" s="6" t="s">
         <v>661</v>
       </c>
@@ -17044,9 +17208,11 @@
       <c r="V146" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W146" s="7"/>
-    </row>
-    <row r="147" spans="1:23" ht="166.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="W146" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="147" spans="1:23" ht="166.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="6" t="s">
         <v>669</v>
       </c>
@@ -17117,7 +17283,7 @@
         <v>1453</v>
       </c>
     </row>
-    <row r="148" spans="1:23" ht="166.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:23" ht="166.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="6" t="s">
         <v>669</v>
       </c>
@@ -17188,7 +17354,7 @@
         <v>1453</v>
       </c>
     </row>
-    <row r="149" spans="1:23" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:23" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A149" s="6" t="s">
         <v>673</v>
       </c>
@@ -17255,9 +17421,11 @@
       <c r="V149" s="10" t="s">
         <v>1281</v>
       </c>
-      <c r="W149" s="7"/>
-    </row>
-    <row r="150" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="W149" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="150" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
         <v>679</v>
       </c>
@@ -17324,9 +17492,11 @@
       <c r="V150" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W150" s="7"/>
-    </row>
-    <row r="151" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="W150" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="151" spans="1:23" ht="90" x14ac:dyDescent="0.25">
       <c r="A151" s="6" t="s">
         <v>690</v>
       </c>
@@ -17393,9 +17563,11 @@
       <c r="V151" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W151" s="7"/>
-    </row>
-    <row r="152" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="W151" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="152" spans="1:23" ht="90" x14ac:dyDescent="0.25">
       <c r="A152" s="6" t="s">
         <v>690</v>
       </c>
@@ -17462,9 +17634,11 @@
       <c r="V152" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W152" s="7"/>
-    </row>
-    <row r="153" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="W152" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="153" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A153" s="6" t="s">
         <v>700</v>
       </c>
@@ -17531,9 +17705,11 @@
       <c r="V153" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W153" s="7"/>
-    </row>
-    <row r="154" spans="1:23" ht="129.6" x14ac:dyDescent="0.25">
+      <c r="W153" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="154" spans="1:23" ht="135" x14ac:dyDescent="0.2">
       <c r="A154" s="6" t="s">
         <v>721</v>
       </c>
@@ -17600,9 +17776,11 @@
       <c r="V154" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W154" s="7"/>
-    </row>
-    <row r="155" spans="1:23" ht="129.6" x14ac:dyDescent="0.25">
+      <c r="W154" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="155" spans="1:23" ht="135" x14ac:dyDescent="0.2">
       <c r="A155" s="6" t="s">
         <v>721</v>
       </c>
@@ -17669,9 +17847,11 @@
       <c r="V155" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W155" s="7"/>
-    </row>
-    <row r="156" spans="1:23" ht="129.6" x14ac:dyDescent="0.25">
+      <c r="W155" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="156" spans="1:23" ht="135" x14ac:dyDescent="0.2">
       <c r="A156" s="6" t="s">
         <v>721</v>
       </c>
@@ -17738,9 +17918,11 @@
       <c r="V156" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W156" s="7"/>
-    </row>
-    <row r="157" spans="1:23" ht="129.6" x14ac:dyDescent="0.25">
+      <c r="W156" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="157" spans="1:23" ht="135" x14ac:dyDescent="0.2">
       <c r="A157" s="6" t="s">
         <v>721</v>
       </c>
@@ -17807,9 +17989,11 @@
       <c r="V157" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W157" s="7"/>
-    </row>
-    <row r="158" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="W157" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="158" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A158" s="6" t="s">
         <v>734</v>
       </c>
@@ -17876,9 +18060,11 @@
       <c r="V158" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W158" s="7"/>
-    </row>
-    <row r="159" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="W158" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="159" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A159" s="6" t="s">
         <v>734</v>
       </c>
@@ -17945,9 +18131,11 @@
       <c r="V159" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W159" s="7"/>
-    </row>
-    <row r="160" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="W159" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="160" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A160" s="6" t="s">
         <v>743</v>
       </c>
@@ -18014,9 +18202,11 @@
       <c r="V160" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W160" s="7"/>
-    </row>
-    <row r="161" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="W160" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="161" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A161" s="6" t="s">
         <v>744</v>
       </c>
@@ -18083,9 +18273,11 @@
       <c r="V161" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W161" s="7"/>
-    </row>
-    <row r="162" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="W161" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="162" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A162" s="6" t="s">
         <v>745</v>
       </c>
@@ -18152,9 +18344,11 @@
       <c r="V162" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W162" s="7"/>
-    </row>
-    <row r="163" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="W162" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="163" spans="1:23" ht="120" x14ac:dyDescent="0.25">
       <c r="A163" s="6" t="s">
         <v>746</v>
       </c>
@@ -18221,9 +18415,11 @@
       <c r="V163" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W163" s="7"/>
-    </row>
-    <row r="164" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="W163" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="164" spans="1:23" ht="120" x14ac:dyDescent="0.25">
       <c r="A164" s="6" t="s">
         <v>746</v>
       </c>
@@ -18290,9 +18486,11 @@
       <c r="V164" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W164" s="7"/>
-    </row>
-    <row r="165" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="W164" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="165" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A165" s="6" t="s">
         <v>754</v>
       </c>
@@ -18359,9 +18557,11 @@
       <c r="V165" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W165" s="7"/>
-    </row>
-    <row r="166" spans="1:23" ht="78" x14ac:dyDescent="0.25">
+      <c r="W165" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="166" spans="1:23" ht="78.75" x14ac:dyDescent="0.2">
       <c r="A166" s="6" t="s">
         <v>762</v>
       </c>
@@ -18428,9 +18628,11 @@
       <c r="V166" s="10" t="s">
         <v>1284</v>
       </c>
-      <c r="W166" s="7"/>
-    </row>
-    <row r="167" spans="1:23" ht="78" x14ac:dyDescent="0.25">
+      <c r="W166" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="167" spans="1:23" ht="78.75" x14ac:dyDescent="0.2">
       <c r="A167" s="6" t="s">
         <v>762</v>
       </c>
@@ -18497,9 +18699,11 @@
       <c r="V167" s="10" t="s">
         <v>1284</v>
       </c>
-      <c r="W167" s="7"/>
-    </row>
-    <row r="168" spans="1:23" ht="78" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="W167" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="168" spans="1:23" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
         <v>769</v>
       </c>
@@ -18570,7 +18774,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="169" spans="1:23" ht="77.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:23" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="6" t="s">
         <v>772</v>
       </c>
@@ -18641,7 +18845,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="170" spans="1:23" ht="129.6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:23" ht="150" x14ac:dyDescent="0.2">
       <c r="A170" s="6" t="s">
         <v>782</v>
       </c>
@@ -18712,7 +18916,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="171" spans="1:23" ht="129.6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:23" ht="150" x14ac:dyDescent="0.2">
       <c r="A171" s="6" t="s">
         <v>782</v>
       </c>
@@ -18783,7 +18987,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="172" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:23" ht="90" x14ac:dyDescent="0.25">
       <c r="A172" s="6" t="s">
         <v>787</v>
       </c>
@@ -18850,9 +19054,11 @@
       <c r="V172" s="10" t="s">
         <v>1289</v>
       </c>
-      <c r="W172" s="7"/>
-    </row>
-    <row r="173" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="W172" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="173" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A173" s="6" t="s">
         <v>795</v>
       </c>
@@ -18919,9 +19125,11 @@
       <c r="V173" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W173" s="7"/>
-    </row>
-    <row r="174" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="W173" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="174" spans="1:23" ht="105" x14ac:dyDescent="0.25">
       <c r="A174" s="6" t="s">
         <v>796</v>
       </c>
@@ -18992,7 +19200,7 @@
         <v>1457</v>
       </c>
     </row>
-    <row r="175" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:23" ht="60" x14ac:dyDescent="0.25">
       <c r="A175" s="6" t="s">
         <v>804</v>
       </c>
@@ -19059,9 +19267,11 @@
       <c r="V175" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W175" s="7"/>
-    </row>
-    <row r="176" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="W175" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="176" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A176" s="6" t="s">
         <v>811</v>
       </c>
@@ -19128,9 +19338,11 @@
       <c r="V176" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W176" s="7"/>
-    </row>
-    <row r="177" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="W176" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="177" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A177" s="6" t="s">
         <v>812</v>
       </c>
@@ -19197,9 +19409,11 @@
       <c r="V177" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W177" s="7"/>
-    </row>
-    <row r="178" spans="1:23" ht="201.6" x14ac:dyDescent="0.25">
+      <c r="W177" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="178" spans="1:23" ht="225" x14ac:dyDescent="0.2">
       <c r="A178" s="6" t="s">
         <v>813</v>
       </c>
@@ -19270,7 +19484,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="179" spans="1:23" ht="201.6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:23" ht="225" x14ac:dyDescent="0.2">
       <c r="A179" s="6" t="s">
         <v>813</v>
       </c>
@@ -19341,7 +19555,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="180" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A180" s="6" t="s">
         <v>822</v>
       </c>
@@ -19408,9 +19622,11 @@
       <c r="V180" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W180" s="7"/>
-    </row>
-    <row r="181" spans="1:23" ht="109.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W180" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="181" spans="1:23" ht="109.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="6" t="s">
         <v>825</v>
       </c>
@@ -19481,7 +19697,7 @@
         <v>1459</v>
       </c>
     </row>
-    <row r="182" spans="1:23" ht="86.4" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:23" ht="105" x14ac:dyDescent="0.2">
       <c r="A182" s="6" t="s">
         <v>825</v>
       </c>
@@ -19552,7 +19768,7 @@
         <v>1459</v>
       </c>
     </row>
-    <row r="183" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A183" s="6" t="s">
         <v>841</v>
       </c>
@@ -19619,9 +19835,11 @@
       <c r="V183" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W183" s="7"/>
-    </row>
-    <row r="184" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="W183" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="184" spans="1:23" ht="120" x14ac:dyDescent="0.25">
       <c r="A184" s="6" t="s">
         <v>834</v>
       </c>
@@ -19692,7 +19910,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="185" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
         <v>834</v>
       </c>
@@ -19759,9 +19977,11 @@
       <c r="V185" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W185" s="7"/>
-    </row>
-    <row r="186" spans="1:23" ht="72" x14ac:dyDescent="0.25">
+      <c r="W185" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="186" spans="1:23" ht="75" x14ac:dyDescent="0.2">
       <c r="A186" s="6" t="s">
         <v>842</v>
       </c>
@@ -19828,9 +20048,11 @@
       <c r="V186" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W186" s="7"/>
-    </row>
-    <row r="187" spans="1:23" ht="72" x14ac:dyDescent="0.25">
+      <c r="W186" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="187" spans="1:23" ht="75" x14ac:dyDescent="0.2">
       <c r="A187" s="6" t="s">
         <v>849</v>
       </c>
@@ -19897,9 +20119,11 @@
       <c r="V187" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W187" s="7"/>
-    </row>
-    <row r="188" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="W187" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="188" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A188" s="6" t="s">
         <v>850</v>
       </c>
@@ -19966,9 +20190,11 @@
       <c r="V188" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W188" s="7"/>
-    </row>
-    <row r="189" spans="1:23" ht="93.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="W188" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="189" spans="1:23" ht="93.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="6" t="s">
         <v>851</v>
       </c>
@@ -20039,7 +20265,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="190" spans="1:23" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:23" ht="180" x14ac:dyDescent="0.25">
       <c r="A190" s="6" t="s">
         <v>853</v>
       </c>
@@ -20110,7 +20336,7 @@
         <v>1462</v>
       </c>
     </row>
-    <row r="191" spans="1:23" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:23" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A191" s="6" t="s">
         <v>860</v>
       </c>
@@ -20177,9 +20403,11 @@
       <c r="V191" s="10" t="s">
         <v>1297</v>
       </c>
-      <c r="W191" s="7"/>
-    </row>
-    <row r="192" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="W191" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="192" spans="1:23" ht="60" x14ac:dyDescent="0.25">
       <c r="A192" s="6" t="s">
         <v>861</v>
       </c>
@@ -20246,9 +20474,11 @@
       <c r="V192" s="10" t="s">
         <v>1298</v>
       </c>
-      <c r="W192" s="7"/>
-    </row>
-    <row r="193" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+      <c r="W192" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="193" spans="1:23" ht="75" x14ac:dyDescent="0.25">
       <c r="A193" s="6" t="s">
         <v>861</v>
       </c>
@@ -20319,7 +20549,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="194" spans="1:23" ht="78" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:23" ht="90" x14ac:dyDescent="0.2">
       <c r="A194" s="6" t="s">
         <v>868</v>
       </c>
@@ -20390,7 +20620,7 @@
         <v>1464</v>
       </c>
     </row>
-    <row r="195" spans="1:23" ht="78" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:23" ht="90" x14ac:dyDescent="0.2">
       <c r="A195" s="6" t="s">
         <v>868</v>
       </c>
@@ -20461,7 +20691,7 @@
         <v>1464</v>
       </c>
     </row>
-    <row r="196" spans="1:23" ht="78" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:23" ht="90" x14ac:dyDescent="0.2">
       <c r="A196" s="6" t="s">
         <v>879</v>
       </c>
@@ -20532,7 +20762,7 @@
         <v>1464</v>
       </c>
     </row>
-    <row r="197" spans="1:23" ht="78" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:23" ht="90" x14ac:dyDescent="0.2">
       <c r="A197" s="6" t="s">
         <v>879</v>
       </c>
@@ -20603,7 +20833,7 @@
         <v>1464</v>
       </c>
     </row>
-    <row r="198" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:23" ht="60" x14ac:dyDescent="0.25">
       <c r="A198" s="6" t="s">
         <v>883</v>
       </c>
@@ -20670,9 +20900,11 @@
       <c r="V198" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W198" s="7"/>
-    </row>
-    <row r="199" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="W198" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="199" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A199" s="6" t="s">
         <v>892</v>
       </c>
@@ -20739,9 +20971,11 @@
       <c r="V199" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W199" s="7"/>
-    </row>
-    <row r="200" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+      <c r="W199" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="200" spans="1:23" ht="75" x14ac:dyDescent="0.25">
       <c r="A200" s="6" t="s">
         <v>894</v>
       </c>
@@ -20812,7 +21046,7 @@
         <v>1465</v>
       </c>
     </row>
-    <row r="201" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
         <v>895</v>
       </c>
@@ -20879,9 +21113,11 @@
       <c r="V201" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W201" s="7"/>
-    </row>
-    <row r="202" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="W201" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="202" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A202" s="6" t="s">
         <v>900</v>
       </c>
@@ -20948,9 +21184,11 @@
       <c r="V202" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W202" s="7"/>
-    </row>
-    <row r="203" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="W202" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="203" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A203" s="6" t="s">
         <v>897</v>
       </c>
@@ -21017,9 +21255,11 @@
       <c r="V203" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W203" s="7"/>
-    </row>
-    <row r="204" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="W203" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="204" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A204" s="6" t="s">
         <v>897</v>
       </c>
@@ -21086,9 +21326,11 @@
       <c r="V204" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W204" s="7"/>
-    </row>
-    <row r="205" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="W204" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="205" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A205" s="6" t="s">
         <v>901</v>
       </c>
@@ -21155,9 +21397,11 @@
       <c r="V205" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W205" s="7"/>
-    </row>
-    <row r="206" spans="1:23" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="W205" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="206" spans="1:23" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="6" t="s">
         <v>902</v>
       </c>
@@ -21228,7 +21472,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="207" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A207" s="6" t="s">
         <v>903</v>
       </c>
@@ -21295,9 +21539,11 @@
       <c r="V207" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W207" s="7"/>
-    </row>
-    <row r="208" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="W207" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="208" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A208" s="6" t="s">
         <v>904</v>
       </c>
@@ -21364,9 +21610,11 @@
       <c r="V208" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W208" s="7"/>
-    </row>
-    <row r="209" spans="1:23" ht="72" x14ac:dyDescent="0.25">
+      <c r="W208" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="209" spans="1:23" ht="90" x14ac:dyDescent="0.2">
       <c r="A209" s="6" t="s">
         <v>905</v>
       </c>
@@ -21433,9 +21681,11 @@
       <c r="V209" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W209" s="7"/>
-    </row>
-    <row r="210" spans="1:23" ht="72" x14ac:dyDescent="0.25">
+      <c r="W209" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="210" spans="1:23" ht="90" x14ac:dyDescent="0.2">
       <c r="A210" s="6" t="s">
         <v>915</v>
       </c>
@@ -21502,9 +21752,11 @@
       <c r="V210" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W210" s="7"/>
-    </row>
-    <row r="211" spans="1:23" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="W210" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="211" spans="1:23" ht="195" x14ac:dyDescent="0.25">
       <c r="A211" s="6" t="s">
         <v>916</v>
       </c>
@@ -21571,9 +21823,11 @@
       <c r="V211" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W211" s="7"/>
-    </row>
-    <row r="212" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="W211" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="212" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A212" s="6" t="s">
         <v>924</v>
       </c>
@@ -21640,9 +21894,11 @@
       <c r="V212" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W212" s="7"/>
-    </row>
-    <row r="213" spans="1:23" ht="60" x14ac:dyDescent="0.25">
+      <c r="W212" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="213" spans="1:23" ht="75" x14ac:dyDescent="0.2">
       <c r="A213" s="6" t="s">
         <v>925</v>
       </c>
@@ -21709,9 +21965,11 @@
       <c r="V213" s="10" t="s">
         <v>1305</v>
       </c>
-      <c r="W213" s="7"/>
-    </row>
-    <row r="214" spans="1:23" ht="60" x14ac:dyDescent="0.25">
+      <c r="W213" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="214" spans="1:23" ht="60" x14ac:dyDescent="0.2">
       <c r="A214" s="6" t="s">
         <v>932</v>
       </c>
@@ -21778,9 +22036,11 @@
       <c r="V214" s="10" t="s">
         <v>1305</v>
       </c>
-      <c r="W214" s="7"/>
-    </row>
-    <row r="215" spans="1:23" ht="72" x14ac:dyDescent="0.25">
+      <c r="W214" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="215" spans="1:23" ht="90" x14ac:dyDescent="0.2">
       <c r="A215" s="6" t="s">
         <v>932</v>
       </c>
@@ -21847,9 +22107,11 @@
       <c r="V215" s="10" t="s">
         <v>1305</v>
       </c>
-      <c r="W215" s="7"/>
-    </row>
-    <row r="216" spans="1:23" ht="60" x14ac:dyDescent="0.25">
+      <c r="W215" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="216" spans="1:23" ht="60" x14ac:dyDescent="0.2">
       <c r="A216" s="6" t="s">
         <v>932</v>
       </c>
@@ -21916,9 +22178,11 @@
       <c r="V216" s="10" t="s">
         <v>1305</v>
       </c>
-      <c r="W216" s="7"/>
-    </row>
-    <row r="217" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+      <c r="W216" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="217" spans="1:23" ht="90" x14ac:dyDescent="0.25">
       <c r="A217" s="6" t="s">
         <v>944</v>
       </c>
@@ -21985,9 +22249,11 @@
       <c r="V217" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W217" s="7"/>
-    </row>
-    <row r="218" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="W217" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="218" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A218" s="6" t="s">
         <v>945</v>
       </c>
@@ -22054,9 +22320,11 @@
       <c r="V218" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W218" s="7"/>
-    </row>
-    <row r="219" spans="1:23" ht="144" x14ac:dyDescent="0.3">
+      <c r="W218" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="219" spans="1:23" ht="150" x14ac:dyDescent="0.25">
       <c r="A219" s="6" t="s">
         <v>953</v>
       </c>
@@ -22123,9 +22391,11 @@
       <c r="V219" s="10" t="s">
         <v>1307</v>
       </c>
-      <c r="W219" s="7"/>
-    </row>
-    <row r="220" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="W219" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="220" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
         <v>963</v>
       </c>
@@ -22192,9 +22462,11 @@
       <c r="V220" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W220" s="7"/>
-    </row>
-    <row r="221" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="W220" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="221" spans="1:23" ht="60" x14ac:dyDescent="0.25">
       <c r="A221" s="6" t="s">
         <v>1210</v>
       </c>
@@ -22261,9 +22533,11 @@
       <c r="V221" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W221" s="7"/>
-    </row>
-    <row r="222" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="W221" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="222" spans="1:23" ht="60" x14ac:dyDescent="0.25">
       <c r="A222" s="6" t="s">
         <v>1210</v>
       </c>
@@ -22330,9 +22604,11 @@
       <c r="V222" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W222" s="7"/>
-    </row>
-    <row r="223" spans="1:23" ht="78" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="W222" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="223" spans="1:23" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="6" t="s">
         <v>972</v>
       </c>
@@ -22403,7 +22679,7 @@
         <v>1468</v>
       </c>
     </row>
-    <row r="224" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:23" ht="75" x14ac:dyDescent="0.25">
       <c r="A224" s="6" t="s">
         <v>974</v>
       </c>
@@ -22474,7 +22750,7 @@
         <v>1468</v>
       </c>
     </row>
-    <row r="225" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:23" ht="75" x14ac:dyDescent="0.25">
       <c r="A225" s="6" t="s">
         <v>974</v>
       </c>
@@ -22545,7 +22821,7 @@
         <v>1468</v>
       </c>
     </row>
-    <row r="226" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:23" ht="75" x14ac:dyDescent="0.25">
       <c r="A226" s="6" t="s">
         <v>983</v>
       </c>
@@ -22612,9 +22888,11 @@
       <c r="V226" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W226" s="7"/>
-    </row>
-    <row r="227" spans="1:23" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="W226" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="227" spans="1:23" ht="82.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="6" t="s">
         <v>990</v>
       </c>
@@ -22685,7 +22963,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="228" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:23" ht="105" x14ac:dyDescent="0.25">
       <c r="A228" s="6" t="s">
         <v>991</v>
       </c>
@@ -22756,7 +23034,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="229" spans="1:23" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:23" ht="135" x14ac:dyDescent="0.25">
       <c r="A229" s="6" t="s">
         <v>992</v>
       </c>
@@ -22823,9 +23101,11 @@
       <c r="V229" s="10" t="s">
         <v>1314</v>
       </c>
-      <c r="W229" s="7"/>
-    </row>
-    <row r="230" spans="1:23" ht="187.2" x14ac:dyDescent="0.25">
+      <c r="W229" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="230" spans="1:23" ht="210" x14ac:dyDescent="0.2">
       <c r="A230" s="6" t="s">
         <v>993</v>
       </c>
@@ -22896,7 +23176,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="231" spans="1:23" ht="187.2" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:23" ht="210" x14ac:dyDescent="0.2">
       <c r="A231" s="6" t="s">
         <v>1000</v>
       </c>
@@ -22967,7 +23247,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="232" spans="1:23" ht="62.4" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:23" ht="63" x14ac:dyDescent="0.2">
       <c r="A232" s="6" t="s">
         <v>1001</v>
       </c>
@@ -23038,7 +23318,7 @@
         <v>1472</v>
       </c>
     </row>
-    <row r="233" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A233" s="6" t="s">
         <v>1009</v>
       </c>
@@ -23105,9 +23385,11 @@
       <c r="V233" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W233" s="7"/>
-    </row>
-    <row r="234" spans="1:23" ht="150" x14ac:dyDescent="0.25">
+      <c r="W233" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="234" spans="1:23" ht="165" x14ac:dyDescent="0.2">
       <c r="A234" s="6" t="s">
         <v>1010</v>
       </c>
@@ -23178,7 +23460,7 @@
         <v>1473</v>
       </c>
     </row>
-    <row r="235" spans="1:23" ht="150" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:23" ht="165" x14ac:dyDescent="0.2">
       <c r="A235" s="6" t="s">
         <v>1010</v>
       </c>
@@ -23249,7 +23531,7 @@
         <v>1473</v>
       </c>
     </row>
-    <row r="236" spans="1:23" ht="156" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:23" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A236" s="6" t="s">
         <v>1019</v>
       </c>
@@ -23320,7 +23602,7 @@
         <v>1473</v>
       </c>
     </row>
-    <row r="237" spans="1:23" ht="156" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:23" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
         <v>1020</v>
       </c>
@@ -23391,7 +23673,7 @@
         <v>1473</v>
       </c>
     </row>
-    <row r="238" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A238" s="6" t="s">
         <v>1022</v>
       </c>
@@ -23458,9 +23740,11 @@
       <c r="V238" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W238" s="7"/>
-    </row>
-    <row r="239" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="W238" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="239" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A239" s="6" t="s">
         <v>896</v>
       </c>
@@ -23527,9 +23811,11 @@
       <c r="V239" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W239" s="7"/>
-    </row>
-    <row r="240" spans="1:23" ht="78" x14ac:dyDescent="0.3">
+      <c r="W239" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="240" spans="1:23" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A240" s="6" t="s">
         <v>1023</v>
       </c>
@@ -23596,9 +23882,11 @@
       <c r="V240" s="10" t="s">
         <v>1324</v>
       </c>
-      <c r="W240" s="7"/>
-    </row>
-    <row r="241" spans="1:23" ht="78" x14ac:dyDescent="0.3">
+      <c r="W240" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="241" spans="1:23" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A241" s="6" t="s">
         <v>1023</v>
       </c>
@@ -23665,9 +23953,11 @@
       <c r="V241" s="10" t="s">
         <v>1324</v>
       </c>
-      <c r="W241" s="7"/>
-    </row>
-    <row r="242" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="W241" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="242" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A242" s="6" t="s">
         <v>1031</v>
       </c>
@@ -23734,9 +24024,11 @@
       <c r="V242" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W242" s="7"/>
-    </row>
-    <row r="243" spans="1:23" ht="130.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="W242" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="243" spans="1:23" ht="130.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="6" t="s">
         <v>1033</v>
       </c>
@@ -23807,7 +24099,7 @@
         <v>1474</v>
       </c>
     </row>
-    <row r="244" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A244" s="6" t="s">
         <v>1034</v>
       </c>
@@ -23878,7 +24170,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="245" spans="1:23" ht="103.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:23" ht="103.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="6" t="s">
         <v>1035</v>
       </c>
@@ -23949,7 +24241,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="246" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:23" ht="75" x14ac:dyDescent="0.25">
       <c r="A246" s="6" t="s">
         <v>1036</v>
       </c>
@@ -24016,9 +24308,11 @@
       <c r="V246" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W246" s="7"/>
-    </row>
-    <row r="247" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="W246" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="247" spans="1:23" ht="90" x14ac:dyDescent="0.25">
       <c r="A247" s="6" t="s">
         <v>1037</v>
       </c>
@@ -24085,9 +24379,11 @@
       <c r="V247" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W247" s="7"/>
-    </row>
-    <row r="248" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="W247" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="248" spans="1:23" ht="105" x14ac:dyDescent="0.25">
       <c r="A248" s="6" t="s">
         <v>1038</v>
       </c>
@@ -24154,9 +24450,11 @@
       <c r="V248" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W248" s="7"/>
-    </row>
-    <row r="249" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="W248" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="249" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A249" s="6" t="s">
         <v>1039</v>
       </c>
@@ -24223,9 +24521,11 @@
       <c r="V249" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W249" s="7"/>
-    </row>
-    <row r="250" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="W249" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="250" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A250" s="6" t="s">
         <v>1040</v>
       </c>
@@ -24292,9 +24592,11 @@
       <c r="V250" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W250" s="7"/>
-    </row>
-    <row r="251" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="W250" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="251" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A251" s="6" t="s">
         <v>1041</v>
       </c>
@@ -24361,9 +24663,11 @@
       <c r="V251" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W251" s="7"/>
-    </row>
-    <row r="252" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="W251" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="252" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A252" s="6" t="s">
         <v>1042</v>
       </c>
@@ -24430,9 +24734,11 @@
       <c r="V252" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W252" s="7"/>
-    </row>
-    <row r="253" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="W252" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="253" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A253" s="6" t="s">
         <v>1043</v>
       </c>
@@ -24499,9 +24805,11 @@
       <c r="V253" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W253" s="7"/>
-    </row>
-    <row r="254" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="W253" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="254" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A254" s="6" t="s">
         <v>1044</v>
       </c>
@@ -24568,9 +24876,11 @@
       <c r="V254" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W254" s="7"/>
-    </row>
-    <row r="255" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+      <c r="W254" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="255" spans="1:23" ht="90" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
         <v>1045</v>
       </c>
@@ -24641,7 +24951,7 @@
         <v>1477</v>
       </c>
     </row>
-    <row r="256" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:23" ht="90" x14ac:dyDescent="0.25">
       <c r="A256" s="6" t="s">
         <v>1047</v>
       </c>
@@ -24712,7 +25022,7 @@
         <v>1477</v>
       </c>
     </row>
-    <row r="257" spans="1:23" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:23" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A257" s="6" t="s">
         <v>1048</v>
       </c>
@@ -24783,7 +25093,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="258" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A258" s="6" t="s">
         <v>1052</v>
       </c>
@@ -24850,9 +25160,11 @@
       <c r="V258" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W258" s="7"/>
-    </row>
-    <row r="259" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="W258" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="259" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A259" s="6" t="s">
         <v>1054</v>
       </c>
@@ -24919,9 +25231,11 @@
       <c r="V259" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W259" s="7"/>
-    </row>
-    <row r="260" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="W259" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="260" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A260" s="6" t="s">
         <v>1055</v>
       </c>
@@ -24988,9 +25302,11 @@
       <c r="V260" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W260" s="7"/>
-    </row>
-    <row r="261" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="W260" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="261" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A261" s="6" t="s">
         <v>1056</v>
       </c>
@@ -25057,9 +25373,11 @@
       <c r="V261" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W261" s="7"/>
-    </row>
-    <row r="262" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="W261" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="262" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A262" s="6" t="s">
         <v>1057</v>
       </c>
@@ -25126,9 +25444,11 @@
       <c r="V262" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W262" s="7"/>
-    </row>
-    <row r="263" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="W262" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="263" spans="1:23" ht="135" x14ac:dyDescent="0.25">
       <c r="A263" s="6" t="s">
         <v>1058</v>
       </c>
@@ -25199,7 +25519,7 @@
         <v>1479</v>
       </c>
     </row>
-    <row r="264" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A264" s="6" t="s">
         <v>1059</v>
       </c>
@@ -25266,9 +25586,11 @@
       <c r="V264" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W264" s="7"/>
-    </row>
-    <row r="265" spans="1:23" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="W264" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="265" spans="1:23" ht="99" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="6" t="s">
         <v>1060</v>
       </c>
@@ -25335,9 +25657,11 @@
       <c r="V265" s="10" t="s">
         <v>1332</v>
       </c>
-      <c r="W265" s="7"/>
-    </row>
-    <row r="266" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="W265" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="266" spans="1:23" ht="90" x14ac:dyDescent="0.25">
       <c r="A266" s="6" t="s">
         <v>1067</v>
       </c>
@@ -25408,7 +25732,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="267" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:23" ht="90" x14ac:dyDescent="0.25">
       <c r="A267" s="6" t="s">
         <v>1071</v>
       </c>
@@ -25479,7 +25803,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="268" spans="1:23" ht="72" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:23" ht="90" x14ac:dyDescent="0.25">
       <c r="A268" s="6" t="s">
         <v>1080</v>
       </c>
@@ -25550,7 +25874,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="269" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A269" s="6" t="s">
         <v>1083</v>
       </c>
@@ -25617,9 +25941,11 @@
       <c r="V269" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W269" s="7"/>
-    </row>
-    <row r="270" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="W269" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="270" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A270" s="6" t="s">
         <v>1091</v>
       </c>
@@ -25686,9 +26012,11 @@
       <c r="V270" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W270" s="7"/>
-    </row>
-    <row r="271" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="W270" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="271" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A271" s="6" t="s">
         <v>1098</v>
       </c>
@@ -25755,9 +26083,11 @@
       <c r="V271" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W271" s="7"/>
-    </row>
-    <row r="272" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="W271" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="272" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A272" s="6" t="s">
         <v>1099</v>
       </c>
@@ -25824,9 +26154,11 @@
       <c r="V272" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W272" s="7"/>
-    </row>
-    <row r="273" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="W272" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="273" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A273" s="6" t="s">
         <v>1105</v>
       </c>
@@ -25893,9 +26225,11 @@
       <c r="V273" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W273" s="7"/>
-    </row>
-    <row r="274" spans="1:23" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="W273" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="274" spans="1:23" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
         <v>1109</v>
       </c>
@@ -25962,9 +26296,11 @@
       <c r="V274" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W274" s="7"/>
-    </row>
-    <row r="275" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="W274" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="275" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A275" s="6" t="s">
         <v>1115</v>
       </c>
@@ -26031,9 +26367,11 @@
       <c r="V275" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W275" s="7"/>
-    </row>
-    <row r="276" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="W275" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="276" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A276" s="6" t="s">
         <v>1122</v>
       </c>
@@ -26100,9 +26438,11 @@
       <c r="V276" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W276" s="7"/>
-    </row>
-    <row r="277" spans="1:23" ht="78" x14ac:dyDescent="0.3">
+      <c r="W276" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="277" spans="1:23" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A277" s="6" t="s">
         <v>1128</v>
       </c>
@@ -26169,9 +26509,11 @@
       <c r="V277" s="10" t="s">
         <v>1340</v>
       </c>
-      <c r="W277" s="7"/>
-    </row>
-    <row r="278" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="W277" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="278" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A278" s="6" t="s">
         <v>1136</v>
       </c>
@@ -26242,7 +26584,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="279" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A279" s="6" t="s">
         <v>1141</v>
       </c>
@@ -26309,9 +26651,11 @@
       <c r="V279" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W279" s="7"/>
-    </row>
-    <row r="280" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="W279" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="280" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A280" s="6" t="s">
         <v>1137</v>
       </c>
@@ -26382,7 +26726,7 @@
         <v>1482</v>
       </c>
     </row>
-    <row r="281" spans="1:23" ht="78" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:23" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A281" s="6" t="s">
         <v>1142</v>
       </c>
@@ -26453,7 +26797,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="282" spans="1:23" ht="78" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:23" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A282" s="6" t="s">
         <v>1142</v>
       </c>
@@ -26524,7 +26868,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="283" spans="1:23" ht="78" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:23" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A283" s="6" t="s">
         <v>1149</v>
       </c>
@@ -26595,7 +26939,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="284" spans="1:23" ht="78" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:23" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A284" s="6" t="s">
         <v>1149</v>
       </c>
@@ -26666,7 +27010,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="285" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A285" s="6" t="s">
         <v>1150</v>
       </c>
@@ -26733,9 +27077,11 @@
       <c r="V285" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W285" s="7"/>
-    </row>
-    <row r="286" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="W285" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="286" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A286" s="6" t="s">
         <v>1150</v>
       </c>
@@ -26802,9 +27148,11 @@
       <c r="V286" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W286" s="7"/>
-    </row>
-    <row r="287" spans="1:23" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="W286" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="287" spans="1:23" ht="63" x14ac:dyDescent="0.25">
       <c r="A287" s="6" t="s">
         <v>1157</v>
       </c>
@@ -26871,9 +27219,11 @@
       <c r="V287" s="10" t="s">
         <v>1342</v>
       </c>
-      <c r="W287" s="7"/>
-    </row>
-    <row r="288" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="W287" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="288" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A288" s="6" t="s">
         <v>1162</v>
       </c>
@@ -26940,9 +27290,11 @@
       <c r="V288" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W288" s="7"/>
-    </row>
-    <row r="289" spans="1:23" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="W288" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="289" spans="1:23" ht="63" x14ac:dyDescent="0.25">
       <c r="A289" s="6" t="s">
         <v>1163</v>
       </c>
@@ -27009,9 +27361,11 @@
       <c r="V289" s="10" t="s">
         <v>1344</v>
       </c>
-      <c r="W289" s="7"/>
-    </row>
-    <row r="290" spans="1:23" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="W289" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="290" spans="1:23" ht="64.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="6" t="s">
         <v>1171</v>
       </c>
@@ -27078,7 +27432,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="291" spans="1:23" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:23" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="6" t="s">
         <v>1172</v>
       </c>
@@ -27145,9 +27499,11 @@
       <c r="V291" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W291" s="7"/>
-    </row>
-    <row r="292" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="W291" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="292" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A292" s="6" t="s">
         <v>1173</v>
       </c>
@@ -27214,9 +27570,11 @@
       <c r="V292" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W292" s="7"/>
-    </row>
-    <row r="293" spans="1:23" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="W292" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="293" spans="1:23" ht="210" x14ac:dyDescent="0.25">
       <c r="A293" s="6" t="s">
         <v>1175</v>
       </c>
@@ -27287,7 +27645,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="294" spans="1:23" ht="78" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:23" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A294" s="6" t="s">
         <v>1184</v>
       </c>
@@ -27354,9 +27712,11 @@
       <c r="V294" s="10" t="s">
         <v>1348</v>
       </c>
-      <c r="W294" s="7"/>
-    </row>
-    <row r="295" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="W294" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="295" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A295" s="6" t="s">
         <v>1193</v>
       </c>
@@ -27423,9 +27783,11 @@
       <c r="V295" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W295" s="7"/>
-    </row>
-    <row r="296" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="W295" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="296" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A296" s="6" t="s">
         <v>1193</v>
       </c>
@@ -27492,9 +27854,11 @@
       <c r="V296" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="W296" s="7"/>
-    </row>
-    <row r="297" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="W296" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="297" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A297" s="16" t="s">
         <v>1200</v>
       </c>
@@ -27561,7 +27925,9 @@
       <c r="V297" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="W297" s="17"/>
+      <c r="W297" s="17" t="s">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/dados_injetaveis.xlsx
+++ b/dados_injetaveis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elton.freitas\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{948D8AD9-FF84-4FB4-9BC7-64A59080E4B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B4B75C-5424-48F0-9B25-FC2E876DBD3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6873" uniqueCount="1488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6873" uniqueCount="1498">
   <si>
     <t>MEDICAMENTO</t>
   </si>
@@ -4066,9 +4066,6 @@
   </si>
   <si>
     <t>TEICOPLANINA 200MG PÓ LIÓFILO PARA INJETÁVEL</t>
-  </si>
-  <si>
-    <t>TEIPLAN®</t>
   </si>
   <si>
     <t>66,6 mg/mL</t>
@@ -5156,9 +5153,6 @@
     <t>25 mL de Cloreto de Sódio 0,9% ou Soro Glicosado 5% para cada mL  Bac-Sulfitrin®</t>
   </si>
   <si>
-    <t>20 a 200mL Cloreto de Sódio 0,9% ou Soro Glicosado 5%</t>
-  </si>
-  <si>
     <t>100 mL Cloreto de Sódio 0,9% ou Soro Glicosado 5%</t>
   </si>
   <si>
@@ -5505,6 +5499,45 @@
   </si>
   <si>
     <t>Pacientes com insuficiência hepática devem ser cuidadosamente monitorados e mantidos com a menor dose eficaz diária.</t>
+  </si>
+  <si>
+    <t>48 H</t>
+  </si>
+  <si>
+    <t>11  dias</t>
+  </si>
+  <si>
+    <t>Diluentes gerais 48 h ; Ringer lactato 7 dias</t>
+  </si>
+  <si>
+    <t>3,2ml</t>
+  </si>
+  <si>
+    <t>Acima de 2 meses: Ataque de 10 mg/kg a cada 12h (3 doses); Manutenção de 6 a 10 mg/kg/dia.  ;                       Recém-nascidos: Ataque de 16 mg/kg (dose única no 1º dia); Manutenção de 8 mg/kg/dia.</t>
+  </si>
+  <si>
+    <t>Até o 4º dia: Não ajustar (manter ataque).
+A partir do 5º dia:
+ClCr 40-60 mL/min: Reduzir a dose à metade (dose usual a cada 48h ou meia dose/dia).
+ClCr &lt; 40 mL/min ou Hemodiálise: Reduzir a dose a um terço (dose usual a cada 72h ou 1/3 da dose/dia).</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 50 mL a 100 mL Cloreto de Sódio 0,9% ; Soro Glicosado 5%; Ringer; Ringer lactato; </t>
+  </si>
+  <si>
+    <t>Se o paciente tiver peso superior a 85 kg, a dose deve ser calculada estritamente por mg/kg em vez de usar o frasco fixo de 400 mg.</t>
+  </si>
+  <si>
+    <t>Bactomax®</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7 dias</t>
+  </si>
+  <si>
+    <t>24 horas</t>
+  </si>
+  <si>
+    <t>50 mL a 100 mL Soro Fisiológico 0,9%, Soro Glicosado 5% o</t>
   </si>
 </sst>
 </file>
@@ -6925,7 +6958,7 @@
         <v>21</v>
       </c>
       <c r="W1" s="23" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
@@ -6957,7 +6990,7 @@
         <v>26</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="K2" s="6" t="s">
         <v>147</v>
@@ -6990,13 +7023,13 @@
         <v>186</v>
       </c>
       <c r="U2" s="8" t="s">
+        <v>1198</v>
+      </c>
+      <c r="V2" s="9" t="s">
         <v>1199</v>
       </c>
-      <c r="V2" s="9" t="s">
-        <v>1200</v>
-      </c>
       <c r="W2" s="22" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
@@ -7028,7 +7061,7 @@
         <v>26</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>147</v>
@@ -7061,13 +7094,13 @@
         <v>186</v>
       </c>
       <c r="U3" s="8" t="s">
+        <v>1198</v>
+      </c>
+      <c r="V3" s="9" t="s">
         <v>1199</v>
       </c>
-      <c r="V3" s="9" t="s">
-        <v>1200</v>
-      </c>
       <c r="W3" s="22" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="105" x14ac:dyDescent="0.25">
@@ -7099,7 +7132,7 @@
         <v>26</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="K4" s="6" t="s">
         <v>26</v>
@@ -7132,13 +7165,13 @@
         <v>26</v>
       </c>
       <c r="U4" s="8" t="s">
+        <v>1200</v>
+      </c>
+      <c r="V4" s="9" t="s">
         <v>1201</v>
       </c>
-      <c r="V4" s="9" t="s">
-        <v>1202</v>
-      </c>
       <c r="W4" s="6" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="240" x14ac:dyDescent="0.25">
@@ -7170,7 +7203,7 @@
         <v>26</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K5" s="6" t="s">
         <v>35</v>
@@ -7241,7 +7274,7 @@
         <v>26</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="K6" s="6" t="s">
         <v>147</v>
@@ -7274,10 +7307,10 @@
         <v>591</v>
       </c>
       <c r="U6" s="8" t="s">
+        <v>1202</v>
+      </c>
+      <c r="V6" s="9" t="s">
         <v>1203</v>
-      </c>
-      <c r="V6" s="9" t="s">
-        <v>1204</v>
       </c>
       <c r="W6" s="6" t="s">
         <v>26</v>
@@ -7312,7 +7345,7 @@
         <v>26</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="K7" s="6" t="s">
         <v>147</v>
@@ -7345,13 +7378,13 @@
         <v>698</v>
       </c>
       <c r="U7" s="8" t="s">
+        <v>1204</v>
+      </c>
+      <c r="V7" s="9" t="s">
         <v>1205</v>
       </c>
-      <c r="V7" s="9" t="s">
-        <v>1206</v>
-      </c>
       <c r="W7" s="6" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="150" x14ac:dyDescent="0.25">
@@ -7383,7 +7416,7 @@
         <v>26</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K8" s="6" t="s">
         <v>35</v>
@@ -7416,13 +7449,13 @@
         <v>707</v>
       </c>
       <c r="U8" s="8" t="s">
+        <v>1206</v>
+      </c>
+      <c r="V8" s="9" t="s">
         <v>1207</v>
       </c>
-      <c r="V8" s="9" t="s">
-        <v>1208</v>
-      </c>
       <c r="W8" s="6" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="63" x14ac:dyDescent="0.25">
@@ -7487,10 +7520,10 @@
         <v>721</v>
       </c>
       <c r="U9" s="8" t="s">
+        <v>1208</v>
+      </c>
+      <c r="V9" s="9" t="s">
         <v>1209</v>
-      </c>
-      <c r="V9" s="9" t="s">
-        <v>1210</v>
       </c>
       <c r="W9" s="6" t="s">
         <v>26</v>
@@ -7525,7 +7558,7 @@
         <v>26</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K10" s="6" t="s">
         <v>35</v>
@@ -7558,13 +7591,13 @@
         <v>768</v>
       </c>
       <c r="U10" s="11" t="s">
+        <v>1210</v>
+      </c>
+      <c r="V10" s="9" t="s">
         <v>1211</v>
       </c>
-      <c r="V10" s="9" t="s">
-        <v>1212</v>
-      </c>
       <c r="W10" s="6" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="330" x14ac:dyDescent="0.2">
@@ -7629,13 +7662,13 @@
         <v>768</v>
       </c>
       <c r="U11" s="11" t="s">
+        <v>1210</v>
+      </c>
+      <c r="V11" s="9" t="s">
         <v>1211</v>
       </c>
-      <c r="V11" s="9" t="s">
-        <v>1212</v>
-      </c>
       <c r="W11" s="6" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="150" x14ac:dyDescent="0.25">
@@ -7667,7 +7700,7 @@
         <v>194</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="K12" s="6" t="s">
         <v>195</v>
@@ -7700,7 +7733,7 @@
         <v>202</v>
       </c>
       <c r="U12" s="8" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="V12" s="10" t="s">
         <v>26</v>
@@ -7738,7 +7771,7 @@
         <v>194</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>195</v>
@@ -7771,7 +7804,7 @@
         <v>202</v>
       </c>
       <c r="U13" s="8" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="V13" s="10" t="s">
         <v>26</v>
@@ -7809,7 +7842,7 @@
         <v>194</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="K14" s="6" t="s">
         <v>195</v>
@@ -7842,7 +7875,7 @@
         <v>202</v>
       </c>
       <c r="U14" s="8" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="V14" s="10" t="s">
         <v>26</v>
@@ -7859,13 +7892,13 @@
         <v>26</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>76</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>472</v>
@@ -7874,43 +7907,43 @@
         <v>473</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>147</v>
+        <v>211</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>438</v>
+        <v>211</v>
       </c>
       <c r="J15" s="6" t="s">
         <v>26</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>26</v>
+        <v>211</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>26</v>
+        <v>211</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>469</v>
       </c>
       <c r="P15" s="6" t="s">
+        <v>1476</v>
+      </c>
+      <c r="Q15" s="6" t="s">
+        <v>1477</v>
+      </c>
+      <c r="R15" s="6" t="s">
         <v>1478</v>
-      </c>
-      <c r="Q15" s="6" t="s">
-        <v>1479</v>
-      </c>
-      <c r="R15" s="6" t="s">
-        <v>1480</v>
       </c>
       <c r="S15" s="6" t="s">
         <v>51</v>
       </c>
       <c r="T15" s="6" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="U15" s="6" t="s">
         <v>26</v>
@@ -7930,13 +7963,13 @@
         <v>26</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>464</v>
@@ -7945,52 +7978,52 @@
         <v>465</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>147</v>
+        <v>211</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>438</v>
+        <v>211</v>
       </c>
       <c r="J16" s="6" t="s">
+        <v>1473</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>1474</v>
+      </c>
+      <c r="N16" s="6" t="s">
         <v>1475</v>
-      </c>
-      <c r="K16" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="L16" s="6" t="s">
-        <v>438</v>
-      </c>
-      <c r="M16" s="6" t="s">
-        <v>1476</v>
-      </c>
-      <c r="N16" s="6" t="s">
-        <v>1477</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>469</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="Q16" s="6" t="s">
         <v>470</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="S16" s="6" t="s">
         <v>51</v>
       </c>
       <c r="T16" s="6" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="U16" s="8" t="s">
+        <v>1213</v>
+      </c>
+      <c r="V16" s="9" t="s">
         <v>1214</v>
       </c>
-      <c r="V16" s="9" t="s">
-        <v>1215</v>
-      </c>
       <c r="W16" s="6" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="17" spans="1:23" ht="135" x14ac:dyDescent="0.25">
@@ -8007,7 +8040,7 @@
         <v>25</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>464</v>
@@ -8022,7 +8055,7 @@
         <v>466</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="K17" s="6" t="s">
         <v>436</v>
@@ -8052,16 +8085,16 @@
         <v>51</v>
       </c>
       <c r="T17" s="6" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="U17" s="8" t="s">
+        <v>1213</v>
+      </c>
+      <c r="V17" s="9" t="s">
         <v>1214</v>
       </c>
-      <c r="V17" s="9" t="s">
-        <v>1215</v>
-      </c>
       <c r="W17" s="6" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="18" spans="1:23" ht="60" x14ac:dyDescent="0.25">
@@ -8078,7 +8111,7 @@
         <v>76</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>472</v>
@@ -8114,7 +8147,7 @@
         <v>474</v>
       </c>
       <c r="Q18" s="6" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>471</v>
@@ -8123,7 +8156,7 @@
         <v>51</v>
       </c>
       <c r="T18" s="6" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="U18" s="6" t="s">
         <v>26</v>
@@ -8149,7 +8182,7 @@
         <v>25</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>476</v>
@@ -8164,7 +8197,7 @@
         <v>466</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="K19" s="6" t="s">
         <v>436</v>
@@ -8194,16 +8227,16 @@
         <v>51</v>
       </c>
       <c r="T19" s="6" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="U19" s="8" t="s">
+        <v>1213</v>
+      </c>
+      <c r="V19" s="9" t="s">
         <v>1214</v>
       </c>
-      <c r="V19" s="9" t="s">
-        <v>1215</v>
-      </c>
       <c r="W19" s="6" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="20" spans="1:23" ht="94.5" x14ac:dyDescent="0.25">
@@ -8220,7 +8253,7 @@
         <v>25</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>481</v>
@@ -8235,7 +8268,7 @@
         <v>26</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>211</v>
@@ -8268,10 +8301,10 @@
         <v>486</v>
       </c>
       <c r="U20" s="8" t="s">
+        <v>1215</v>
+      </c>
+      <c r="V20" s="9" t="s">
         <v>1216</v>
-      </c>
-      <c r="V20" s="9" t="s">
-        <v>1217</v>
       </c>
       <c r="W20" s="6" t="s">
         <v>26</v>
@@ -8377,7 +8410,7 @@
         <v>449</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>493</v>
@@ -8410,10 +8443,10 @@
         <v>498</v>
       </c>
       <c r="U22" s="8" t="s">
+        <v>1217</v>
+      </c>
+      <c r="V22" s="9" t="s">
         <v>1218</v>
-      </c>
-      <c r="V22" s="9" t="s">
-        <v>1219</v>
       </c>
       <c r="W22" s="6" t="s">
         <v>26</v>
@@ -8448,7 +8481,7 @@
         <v>26</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>26</v>
@@ -8481,10 +8514,10 @@
         <v>498</v>
       </c>
       <c r="U23" s="8" t="s">
+        <v>1217</v>
+      </c>
+      <c r="V23" s="9" t="s">
         <v>1218</v>
-      </c>
-      <c r="V23" s="9" t="s">
-        <v>1219</v>
       </c>
       <c r="W23" s="6" t="s">
         <v>26</v>
@@ -8495,7 +8528,7 @@
         <v>511</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>38</v>
@@ -8552,10 +8585,10 @@
         <v>26</v>
       </c>
       <c r="U24" s="8" t="s">
+        <v>1219</v>
+      </c>
+      <c r="V24" s="9" t="s">
         <v>1220</v>
-      </c>
-      <c r="V24" s="9" t="s">
-        <v>1221</v>
       </c>
       <c r="W24" s="6" t="s">
         <v>26</v>
@@ -8590,7 +8623,7 @@
         <v>211</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K25" s="6" t="s">
         <v>504</v>
@@ -8623,10 +8656,10 @@
         <v>510</v>
       </c>
       <c r="U25" s="8" t="s">
+        <v>1221</v>
+      </c>
+      <c r="V25" s="9" t="s">
         <v>1222</v>
-      </c>
-      <c r="V25" s="9" t="s">
-        <v>1223</v>
       </c>
       <c r="W25" s="6" t="s">
         <v>26</v>
@@ -8652,7 +8685,7 @@
         <v>514</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>211</v>
@@ -8670,10 +8703,10 @@
         <v>26</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>515</v>
@@ -8732,7 +8765,7 @@
         <v>147</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>26</v>
@@ -8741,10 +8774,10 @@
         <v>26</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>515</v>
@@ -8765,10 +8798,10 @@
         <v>522</v>
       </c>
       <c r="U27" s="8" t="s">
+        <v>1223</v>
+      </c>
+      <c r="V27" s="9" t="s">
         <v>1224</v>
-      </c>
-      <c r="V27" s="9" t="s">
-        <v>1225</v>
       </c>
       <c r="W27" s="6" t="s">
         <v>26</v>
@@ -8788,7 +8821,7 @@
         <v>25</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -8803,7 +8836,7 @@
         <v>26</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>26</v>
@@ -8836,13 +8869,13 @@
         <v>556</v>
       </c>
       <c r="U28" s="8" t="s">
+        <v>1225</v>
+      </c>
+      <c r="V28" s="9" t="s">
         <v>1226</v>
       </c>
-      <c r="V28" s="9" t="s">
-        <v>1227</v>
-      </c>
       <c r="W28" s="6" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="29" spans="1:23" ht="45" x14ac:dyDescent="0.25">
@@ -8874,7 +8907,7 @@
         <v>449</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>449</v>
@@ -8907,7 +8940,7 @@
         <v>26</v>
       </c>
       <c r="U29" s="8" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="V29" s="10" t="s">
         <v>26</v>
@@ -8930,7 +8963,7 @@
         <v>25</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>540</v>
@@ -8945,7 +8978,7 @@
         <v>541</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>26</v>
@@ -9053,7 +9086,7 @@
         <v>26</v>
       </c>
       <c r="W31" s="6" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="32" spans="1:23" ht="225" x14ac:dyDescent="0.25">
@@ -9085,7 +9118,7 @@
         <v>26</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>27</v>
@@ -9115,13 +9148,13 @@
         <v>31</v>
       </c>
       <c r="T32" s="6" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="U32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="V32" s="9" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="W32" s="6" t="s">
         <v>26</v>
@@ -9156,7 +9189,7 @@
         <v>26</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>27</v>
@@ -9186,13 +9219,13 @@
         <v>31</v>
       </c>
       <c r="T33" s="6" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="U33" s="6" t="s">
         <v>26</v>
       </c>
       <c r="V33" s="9" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="W33" s="6" t="s">
         <v>26</v>
@@ -9227,7 +9260,7 @@
         <v>26</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>27</v>
@@ -9257,13 +9290,13 @@
         <v>31</v>
       </c>
       <c r="T34" s="6" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="U34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="V34" s="9" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="W34" s="6" t="s">
         <v>26</v>
@@ -9298,7 +9331,7 @@
         <v>26</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>27</v>
@@ -9328,13 +9361,13 @@
         <v>31</v>
       </c>
       <c r="T35" s="6" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="U35" s="6" t="s">
         <v>26</v>
       </c>
       <c r="V35" s="9" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="W35" s="6" t="s">
         <v>26</v>
@@ -9369,7 +9402,7 @@
         <v>26</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>27</v>
@@ -9399,13 +9432,13 @@
         <v>31</v>
       </c>
       <c r="T36" s="6" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="U36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="V36" s="9" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="W36" s="6" t="s">
         <v>26</v>
@@ -9440,7 +9473,7 @@
         <v>26</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>27</v>
@@ -9476,7 +9509,7 @@
         <v>26</v>
       </c>
       <c r="V37" s="9" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="W37" s="6" t="s">
         <v>26</v>
@@ -9496,7 +9529,7 @@
         <v>25</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -9511,7 +9544,7 @@
         <v>46</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>45</v>
@@ -9544,13 +9577,13 @@
         <v>52</v>
       </c>
       <c r="U38" s="8" t="s">
+        <v>1229</v>
+      </c>
+      <c r="V38" s="9" t="s">
         <v>1230</v>
       </c>
-      <c r="V38" s="9" t="s">
-        <v>1231</v>
-      </c>
       <c r="W38" s="6" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="39" spans="1:23" ht="210" x14ac:dyDescent="0.25">
@@ -9567,7 +9600,7 @@
         <v>25</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="F39" s="6" t="s">
         <v>26</v>
@@ -9582,7 +9615,7 @@
         <v>46</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>45</v>
@@ -9615,13 +9648,13 @@
         <v>52</v>
       </c>
       <c r="U39" s="8" t="s">
+        <v>1229</v>
+      </c>
+      <c r="V39" s="9" t="s">
         <v>1230</v>
       </c>
-      <c r="V39" s="9" t="s">
-        <v>1231</v>
-      </c>
       <c r="W39" s="6" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="40" spans="1:23" ht="210" x14ac:dyDescent="0.25">
@@ -9638,7 +9671,7 @@
         <v>25</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
@@ -9653,7 +9686,7 @@
         <v>46</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>45</v>
@@ -9686,13 +9719,13 @@
         <v>52</v>
       </c>
       <c r="U40" s="8" t="s">
+        <v>1229</v>
+      </c>
+      <c r="V40" s="9" t="s">
         <v>1230</v>
       </c>
-      <c r="V40" s="9" t="s">
-        <v>1231</v>
-      </c>
       <c r="W40" s="6" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="225" x14ac:dyDescent="0.25">
@@ -9724,7 +9757,7 @@
         <v>26</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>27</v>
@@ -9760,7 +9793,7 @@
         <v>312</v>
       </c>
       <c r="V41" s="9" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="W41" s="6" t="s">
         <v>26</v>
@@ -9795,7 +9828,7 @@
         <v>26</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>66</v>
@@ -9828,7 +9861,7 @@
         <v>73</v>
       </c>
       <c r="U42" s="8" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="V42" s="10" t="s">
         <v>26</v>
@@ -9866,7 +9899,7 @@
         <v>26</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>66</v>
@@ -9899,7 +9932,7 @@
         <v>73</v>
       </c>
       <c r="U43" s="8" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="V43" s="10" t="s">
         <v>26</v>
@@ -10008,7 +10041,7 @@
         <v>26</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>27</v>
@@ -10079,7 +10112,7 @@
         <v>26</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>88</v>
@@ -10150,7 +10183,7 @@
         <v>26</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>27</v>
@@ -10221,7 +10254,7 @@
         <v>26</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>27</v>
@@ -10328,10 +10361,10 @@
         <v>26</v>
       </c>
       <c r="V49" s="9" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="W49" s="6" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="50" spans="1:23" ht="225" x14ac:dyDescent="0.25">
@@ -10399,10 +10432,10 @@
         <v>26</v>
       </c>
       <c r="V50" s="9" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="W50" s="6" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="51" spans="1:23" ht="45" x14ac:dyDescent="0.25">
@@ -10505,7 +10538,7 @@
         <v>26</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="K52" s="6" t="s">
         <v>27</v>
@@ -10538,10 +10571,10 @@
         <v>106</v>
       </c>
       <c r="U52" s="8" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="V52" s="9" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="W52" s="6" t="s">
         <v>26</v>
@@ -10576,7 +10609,7 @@
         <v>26</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>27</v>
@@ -10609,10 +10642,10 @@
         <v>106</v>
       </c>
       <c r="U53" s="8" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="V53" s="9" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="W53" s="6" t="s">
         <v>26</v>
@@ -10647,7 +10680,7 @@
         <v>26</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>27</v>
@@ -10680,10 +10713,10 @@
         <v>106</v>
       </c>
       <c r="U54" s="8" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="V54" s="9" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="W54" s="6" t="s">
         <v>26</v>
@@ -10718,7 +10751,7 @@
         <v>26</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="K55" s="6" t="s">
         <v>27</v>
@@ -10751,10 +10784,10 @@
         <v>106</v>
       </c>
       <c r="U55" s="8" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="V55" s="9" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="W55" s="6" t="s">
         <v>26</v>
@@ -10860,7 +10893,7 @@
         <v>26</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="K57" s="6" t="s">
         <v>27</v>
@@ -10899,7 +10932,7 @@
         <v>26</v>
       </c>
       <c r="W57" s="6" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="58" spans="1:23" ht="225" x14ac:dyDescent="0.25">
@@ -10910,7 +10943,7 @@
         <v>121</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>25</v>
@@ -10931,7 +10964,7 @@
         <v>26</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>27</v>
@@ -10970,7 +11003,7 @@
         <v>26</v>
       </c>
       <c r="W58" s="6" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="59" spans="1:23" ht="119.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11002,7 +11035,7 @@
         <v>26</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="K59" s="6" t="s">
         <v>130</v>
@@ -11035,7 +11068,7 @@
         <v>138</v>
       </c>
       <c r="U59" s="12" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="V59" s="19" t="s">
         <v>26</v>
@@ -11073,7 +11106,7 @@
         <v>26</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>142</v>
@@ -11106,7 +11139,7 @@
         <v>145</v>
       </c>
       <c r="U60" s="13" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="V60" s="19" t="s">
         <v>26</v>
@@ -11144,7 +11177,7 @@
         <v>26</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>147</v>
@@ -11177,7 +11210,7 @@
         <v>145</v>
       </c>
       <c r="U61" s="8" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="V61" s="19" t="s">
         <v>26</v>
@@ -11215,7 +11248,7 @@
         <v>26</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>147</v>
@@ -11248,7 +11281,7 @@
         <v>145</v>
       </c>
       <c r="U62" s="8" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="V62" s="19" t="s">
         <v>26</v>
@@ -11286,7 +11319,7 @@
         <v>35</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="K63" s="6" t="s">
         <v>155</v>
@@ -11319,10 +11352,10 @@
         <v>161</v>
       </c>
       <c r="U63" s="8" t="s">
+        <v>1238</v>
+      </c>
+      <c r="V63" s="9" t="s">
         <v>1239</v>
-      </c>
-      <c r="V63" s="9" t="s">
-        <v>1240</v>
       </c>
       <c r="W63" s="6" t="s">
         <v>26</v>
@@ -11357,7 +11390,7 @@
         <v>26</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>163</v>
@@ -11390,13 +11423,13 @@
         <v>169</v>
       </c>
       <c r="U64" s="8" t="s">
+        <v>1240</v>
+      </c>
+      <c r="V64" s="9" t="s">
         <v>1241</v>
       </c>
-      <c r="V64" s="9" t="s">
-        <v>1242</v>
-      </c>
       <c r="W64" s="6" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="65" spans="1:23" ht="195" x14ac:dyDescent="0.25">
@@ -11428,7 +11461,7 @@
         <v>26</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="K65" s="6" t="s">
         <v>27</v>
@@ -11461,13 +11494,13 @@
         <v>169</v>
       </c>
       <c r="U65" s="8" t="s">
+        <v>1240</v>
+      </c>
+      <c r="V65" s="9" t="s">
         <v>1241</v>
       </c>
-      <c r="V65" s="9" t="s">
-        <v>1242</v>
-      </c>
       <c r="W65" s="6" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="66" spans="1:23" ht="195" x14ac:dyDescent="0.25">
@@ -11499,7 +11532,7 @@
         <v>26</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="K66" s="6" t="s">
         <v>27</v>
@@ -11532,13 +11565,13 @@
         <v>169</v>
       </c>
       <c r="U66" s="8" t="s">
+        <v>1240</v>
+      </c>
+      <c r="V66" s="9" t="s">
         <v>1241</v>
       </c>
-      <c r="V66" s="9" t="s">
-        <v>1242</v>
-      </c>
       <c r="W66" s="6" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="67" spans="1:23" ht="195" x14ac:dyDescent="0.25">
@@ -11925,7 +11958,7 @@
         <v>26</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>147</v>
@@ -11961,10 +11994,10 @@
         <v>26</v>
       </c>
       <c r="V72" s="9" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="W72" s="6" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="73" spans="1:23" ht="345" x14ac:dyDescent="0.25">
@@ -11996,7 +12029,7 @@
         <v>26</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="K73" s="6" t="s">
         <v>147</v>
@@ -12032,10 +12065,10 @@
         <v>26</v>
       </c>
       <c r="V73" s="9" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="W73" s="6" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="74" spans="1:23" ht="345" x14ac:dyDescent="0.25">
@@ -12067,7 +12100,7 @@
         <v>26</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>147</v>
@@ -12103,10 +12136,10 @@
         <v>26</v>
       </c>
       <c r="V74" s="9" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="W74" s="6" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="75" spans="1:23" ht="345" x14ac:dyDescent="0.25">
@@ -12138,7 +12171,7 @@
         <v>26</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="K75" s="6" t="s">
         <v>147</v>
@@ -12174,10 +12207,10 @@
         <v>26</v>
       </c>
       <c r="V75" s="9" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="W75" s="6" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="76" spans="1:23" ht="135" x14ac:dyDescent="0.25">
@@ -12242,13 +12275,13 @@
         <v>218</v>
       </c>
       <c r="U76" s="8" t="s">
+        <v>1243</v>
+      </c>
+      <c r="V76" s="9" t="s">
         <v>1244</v>
       </c>
-      <c r="V76" s="9" t="s">
-        <v>1245</v>
-      </c>
       <c r="W76" s="6" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="77" spans="1:23" ht="135" x14ac:dyDescent="0.25">
@@ -12384,13 +12417,13 @@
         <v>218</v>
       </c>
       <c r="U78" s="8" t="s">
+        <v>1243</v>
+      </c>
+      <c r="V78" s="9" t="s">
         <v>1244</v>
       </c>
-      <c r="V78" s="9" t="s">
-        <v>1245</v>
-      </c>
       <c r="W78" s="6" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="79" spans="1:23" ht="135" x14ac:dyDescent="0.25">
@@ -12526,13 +12559,13 @@
         <v>218</v>
       </c>
       <c r="U80" s="8" t="s">
+        <v>1243</v>
+      </c>
+      <c r="V80" s="9" t="s">
         <v>1244</v>
       </c>
-      <c r="V80" s="9" t="s">
-        <v>1245</v>
-      </c>
       <c r="W80" s="6" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="81" spans="1:23" ht="135" x14ac:dyDescent="0.25">
@@ -12635,13 +12668,13 @@
         <v>26</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K82" s="6" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="M82" s="6" t="s">
         <v>228</v>
@@ -12653,7 +12686,7 @@
         <v>230</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="Q82" s="6" t="s">
         <v>231</v>
@@ -12668,13 +12701,13 @@
         <v>238</v>
       </c>
       <c r="U82" s="8" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="V82" s="9" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="W82" s="6" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="83" spans="1:23" ht="135" x14ac:dyDescent="0.25">
@@ -12706,13 +12739,13 @@
         <v>26</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="K83" s="6" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="L83" s="6" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="M83" s="6" t="s">
         <v>228</v>
@@ -12724,7 +12757,7 @@
         <v>230</v>
       </c>
       <c r="P83" s="6" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="Q83" s="6" t="s">
         <v>231</v>
@@ -12739,13 +12772,13 @@
         <v>233</v>
       </c>
       <c r="U83" s="8" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="V83" s="9" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="W83" s="6" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="84" spans="1:23" ht="135" x14ac:dyDescent="0.25">
@@ -12777,13 +12810,13 @@
         <v>26</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="K84" s="6" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="M84" s="6" t="s">
         <v>228</v>
@@ -12795,7 +12828,7 @@
         <v>230</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="Q84" s="6" t="s">
         <v>231</v>
@@ -12810,13 +12843,13 @@
         <v>233</v>
       </c>
       <c r="U84" s="8" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="V84" s="9" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="W84" s="6" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="85" spans="1:23" ht="135" x14ac:dyDescent="0.25">
@@ -12848,13 +12881,13 @@
         <v>26</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="K85" s="6" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="L85" s="6" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="M85" s="6" t="s">
         <v>228</v>
@@ -12866,7 +12899,7 @@
         <v>230</v>
       </c>
       <c r="P85" s="6" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="Q85" s="6" t="s">
         <v>231</v>
@@ -12881,13 +12914,13 @@
         <v>233</v>
       </c>
       <c r="U85" s="8" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="V85" s="9" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="W85" s="6" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="86" spans="1:23" ht="135" x14ac:dyDescent="0.25">
@@ -13203,7 +13236,7 @@
         <v>26</v>
       </c>
       <c r="J90" s="6" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="K90" s="6" t="s">
         <v>26</v>
@@ -13242,7 +13275,7 @@
         <v>26</v>
       </c>
       <c r="W90" s="6" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="91" spans="1:23" ht="135" x14ac:dyDescent="0.25">
@@ -13274,7 +13307,7 @@
         <v>35</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="K91" s="6" t="s">
         <v>27</v>
@@ -13307,13 +13340,13 @@
         <v>262</v>
       </c>
       <c r="U91" s="8" t="s">
+        <v>1246</v>
+      </c>
+      <c r="V91" s="9" t="s">
         <v>1247</v>
       </c>
-      <c r="V91" s="9" t="s">
-        <v>1248</v>
-      </c>
       <c r="W91" s="6" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="92" spans="1:23" ht="172.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -13345,7 +13378,7 @@
         <v>26</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="K92" s="6" t="s">
         <v>211</v>
@@ -13378,13 +13411,13 @@
         <v>251</v>
       </c>
       <c r="U92" s="8" t="s">
+        <v>1248</v>
+      </c>
+      <c r="V92" s="9" t="s">
         <v>1249</v>
       </c>
-      <c r="V92" s="9" t="s">
-        <v>1250</v>
-      </c>
       <c r="W92" s="6" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="93" spans="1:23" ht="195" x14ac:dyDescent="0.25">
@@ -13416,7 +13449,7 @@
         <v>278</v>
       </c>
       <c r="J93" s="6" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="K93" s="6" t="s">
         <v>26</v>
@@ -13449,7 +13482,7 @@
         <v>284</v>
       </c>
       <c r="U93" s="8" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="V93" s="10" t="s">
         <v>26</v>
@@ -13487,7 +13520,7 @@
         <v>278</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="K94" s="6" t="s">
         <v>26</v>
@@ -13520,7 +13553,7 @@
         <v>284</v>
       </c>
       <c r="U94" s="8" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="V94" s="10" t="s">
         <v>26</v>
@@ -13558,7 +13591,7 @@
         <v>278</v>
       </c>
       <c r="J95" s="6" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="K95" s="6" t="s">
         <v>26</v>
@@ -13591,7 +13624,7 @@
         <v>284</v>
       </c>
       <c r="U95" s="8" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="V95" s="10" t="s">
         <v>26</v>
@@ -13629,7 +13662,7 @@
         <v>26</v>
       </c>
       <c r="J96" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K96" s="6" t="s">
         <v>293</v>
@@ -13668,7 +13701,7 @@
         <v>26</v>
       </c>
       <c r="W96" s="6" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="97" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
@@ -13700,10 +13733,10 @@
         <v>26</v>
       </c>
       <c r="J97" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K97" s="6" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="L97" s="6" t="s">
         <v>26</v>
@@ -13739,7 +13772,7 @@
         <v>26</v>
       </c>
       <c r="W97" s="6" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="98" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
@@ -13771,10 +13804,10 @@
         <v>26</v>
       </c>
       <c r="J98" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K98" s="6" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="L98" s="6" t="s">
         <v>26</v>
@@ -13810,7 +13843,7 @@
         <v>26</v>
       </c>
       <c r="W98" s="6" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="99" spans="1:23" ht="240" x14ac:dyDescent="0.25">
@@ -13881,7 +13914,7 @@
         <v>26</v>
       </c>
       <c r="W99" s="6" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="100" spans="1:23" ht="240" x14ac:dyDescent="0.25">
@@ -14023,7 +14056,7 @@
         <v>26</v>
       </c>
       <c r="W101" s="6" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="102" spans="1:23" ht="240" x14ac:dyDescent="0.25">
@@ -14126,7 +14159,7 @@
         <v>26</v>
       </c>
       <c r="J103" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K103" s="6" t="s">
         <v>147</v>
@@ -14159,13 +14192,13 @@
         <v>320</v>
       </c>
       <c r="U103" s="8" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="V103" s="9" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="W103" s="6" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="104" spans="1:23" ht="165.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14197,7 +14230,7 @@
         <v>26</v>
       </c>
       <c r="J104" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K104" s="6" t="s">
         <v>147</v>
@@ -14230,13 +14263,13 @@
         <v>320</v>
       </c>
       <c r="U104" s="8" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="V104" s="9" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="W104" s="6" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="105" spans="1:23" ht="75" x14ac:dyDescent="0.25">
@@ -14268,13 +14301,13 @@
         <v>328</v>
       </c>
       <c r="J105" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K105" s="6" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="L105" s="6" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="M105" s="6" t="s">
         <v>329</v>
@@ -14301,13 +14334,13 @@
         <v>333</v>
       </c>
       <c r="U105" s="8" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="V105" s="9" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="W105" s="6" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="106" spans="1:23" ht="60" x14ac:dyDescent="0.25">
@@ -14528,10 +14561,10 @@
         <v>347</v>
       </c>
       <c r="B109" s="6" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C109" s="7" t="s">
         <v>1339</v>
-      </c>
-      <c r="C109" s="7" t="s">
-        <v>1340</v>
       </c>
       <c r="D109" s="6" t="s">
         <v>26</v>
@@ -14765,7 +14798,7 @@
         <v>26</v>
       </c>
       <c r="J112" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K112" s="6" t="s">
         <v>26</v>
@@ -14798,10 +14831,10 @@
         <v>377</v>
       </c>
       <c r="U112" s="8" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="V112" s="9" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="W112" s="6" t="s">
         <v>26</v>
@@ -14940,10 +14973,10 @@
         <v>381</v>
       </c>
       <c r="U114" s="8" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="V114" s="9" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="W114" s="6" t="s">
         <v>26</v>
@@ -14978,7 +15011,7 @@
         <v>26</v>
       </c>
       <c r="J115" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K115" s="6" t="s">
         <v>26</v>
@@ -15011,7 +15044,7 @@
         <v>388</v>
       </c>
       <c r="U115" s="8" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="V115" s="10" t="s">
         <v>26</v>
@@ -15159,7 +15192,7 @@
         <v>26</v>
       </c>
       <c r="W117" s="6" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="118" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
@@ -15230,7 +15263,7 @@
         <v>26</v>
       </c>
       <c r="W118" s="6" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="119" spans="1:23" ht="75" x14ac:dyDescent="0.25">
@@ -15262,7 +15295,7 @@
         <v>26</v>
       </c>
       <c r="J119" s="6" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="K119" s="6" t="s">
         <v>26</v>
@@ -15301,7 +15334,7 @@
         <v>26</v>
       </c>
       <c r="W119" s="6" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="120" spans="1:23" ht="315" x14ac:dyDescent="0.25">
@@ -15372,7 +15405,7 @@
         <v>26</v>
       </c>
       <c r="W120" s="6" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="121" spans="1:23" ht="225" x14ac:dyDescent="0.25">
@@ -15443,7 +15476,7 @@
         <v>26</v>
       </c>
       <c r="W121" s="6" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="122" spans="1:23" ht="225" x14ac:dyDescent="0.25">
@@ -15475,7 +15508,7 @@
         <v>26</v>
       </c>
       <c r="J122" s="6" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="K122" s="6" t="s">
         <v>211</v>
@@ -15511,7 +15544,7 @@
         <v>26</v>
       </c>
       <c r="V122" s="9" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="W122" s="6" t="s">
         <v>26</v>
@@ -15525,7 +15558,7 @@
         <v>26</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="D123" s="6" t="s">
         <v>26</v>
@@ -15617,7 +15650,7 @@
         <v>437</v>
       </c>
       <c r="J124" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K124" s="6" t="s">
         <v>436</v>
@@ -15650,7 +15683,7 @@
         <v>444</v>
       </c>
       <c r="U124" s="8" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="V124" s="10" t="s">
         <v>26</v>
@@ -15688,7 +15721,7 @@
         <v>449</v>
       </c>
       <c r="J125" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K125" s="6" t="s">
         <v>448</v>
@@ -15721,7 +15754,7 @@
         <v>444</v>
       </c>
       <c r="U125" s="8" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="V125" s="10" t="s">
         <v>26</v>
@@ -15901,7 +15934,7 @@
         <v>147</v>
       </c>
       <c r="J128" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K128" s="6" t="s">
         <v>436</v>
@@ -15934,10 +15967,10 @@
         <v>460</v>
       </c>
       <c r="U128" s="8" t="s">
+        <v>1260</v>
+      </c>
+      <c r="V128" s="9" t="s">
         <v>1261</v>
-      </c>
-      <c r="V128" s="9" t="s">
-        <v>1262</v>
       </c>
       <c r="W128" s="6" t="s">
         <v>26</v>
@@ -16099,7 +16132,7 @@
         <v>25</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="F131" s="6" t="s">
         <v>26</v>
@@ -16114,7 +16147,7 @@
         <v>211</v>
       </c>
       <c r="J131" s="6" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="K131" s="6" t="s">
         <v>26</v>
@@ -16138,10 +16171,10 @@
         <v>529</v>
       </c>
       <c r="R131" s="6" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="S131" s="6" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="T131" s="6" t="s">
         <v>530</v>
@@ -16327,7 +16360,7 @@
         <v>26</v>
       </c>
       <c r="J134" s="6" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="K134" s="6" t="s">
         <v>147</v>
@@ -16360,10 +16393,10 @@
         <v>570</v>
       </c>
       <c r="U134" s="8" t="s">
+        <v>1334</v>
+      </c>
+      <c r="V134" s="9" t="s">
         <v>1335</v>
-      </c>
-      <c r="V134" s="9" t="s">
-        <v>1336</v>
       </c>
       <c r="W134" s="6" t="s">
         <v>26</v>
@@ -16398,7 +16431,7 @@
         <v>26</v>
       </c>
       <c r="J135" s="6" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="K135" s="6" t="s">
         <v>147</v>
@@ -16437,7 +16470,7 @@
         <v>26</v>
       </c>
       <c r="W135" s="6" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="136" spans="1:23" ht="30" x14ac:dyDescent="0.25">
@@ -16469,7 +16502,7 @@
         <v>26</v>
       </c>
       <c r="J136" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K136" s="6" t="s">
         <v>593</v>
@@ -16502,7 +16535,7 @@
         <v>26</v>
       </c>
       <c r="U136" s="8" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="V136" s="10" t="s">
         <v>26</v>
@@ -16540,7 +16573,7 @@
         <v>26</v>
       </c>
       <c r="J137" s="6" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="K137" s="6" t="s">
         <v>26</v>
@@ -16573,13 +16606,13 @@
         <v>26</v>
       </c>
       <c r="U137" s="8" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="V137" s="10" t="s">
         <v>26</v>
       </c>
       <c r="W137" s="6" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="138" spans="1:23" ht="60" x14ac:dyDescent="0.25">
@@ -16999,7 +17032,7 @@
         <v>636</v>
       </c>
       <c r="U143" s="8" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="V143" s="10" t="s">
         <v>26</v>
@@ -17037,7 +17070,7 @@
         <v>26</v>
       </c>
       <c r="J144" s="6" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="K144" s="6" t="s">
         <v>638</v>
@@ -17108,7 +17141,7 @@
         <v>26</v>
       </c>
       <c r="J145" s="6" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="K145" s="6" t="s">
         <v>644</v>
@@ -17250,7 +17283,7 @@
         <v>26</v>
       </c>
       <c r="J147" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K147" s="6" t="s">
         <v>26</v>
@@ -17392,7 +17425,7 @@
         <v>26</v>
       </c>
       <c r="J149" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K149" s="6" t="s">
         <v>147</v>
@@ -17431,7 +17464,7 @@
         <v>26</v>
       </c>
       <c r="W149" s="6" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="150" spans="1:23" ht="30" x14ac:dyDescent="0.25">
@@ -17534,7 +17567,7 @@
         <v>26</v>
       </c>
       <c r="J151" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K151" s="6" t="s">
         <v>663</v>
@@ -17567,10 +17600,10 @@
         <v>26</v>
       </c>
       <c r="U151" s="8" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="V151" s="9" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="W151" s="6" t="s">
         <v>26</v>
@@ -17605,7 +17638,7 @@
         <v>26</v>
       </c>
       <c r="J152" s="6" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="K152" s="6" t="s">
         <v>638</v>
@@ -17676,7 +17709,7 @@
         <v>26</v>
       </c>
       <c r="J153" s="6" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="K153" s="6" t="s">
         <v>638</v>
@@ -17889,7 +17922,7 @@
         <v>26</v>
       </c>
       <c r="J156" s="6" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="K156" s="6" t="s">
         <v>26</v>
@@ -17922,7 +17955,7 @@
         <v>715</v>
       </c>
       <c r="U156" s="11" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="V156" s="10" t="s">
         <v>26</v>
@@ -17960,7 +17993,7 @@
         <v>26</v>
       </c>
       <c r="J157" s="6" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="K157" s="6" t="s">
         <v>26</v>
@@ -17993,7 +18026,7 @@
         <v>715</v>
       </c>
       <c r="U157" s="11" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="V157" s="10" t="s">
         <v>26</v>
@@ -18173,7 +18206,7 @@
         <v>26</v>
       </c>
       <c r="J160" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K160" s="6" t="s">
         <v>147</v>
@@ -18528,7 +18561,7 @@
         <v>26</v>
       </c>
       <c r="J165" s="6" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="K165" s="6" t="s">
         <v>211</v>
@@ -18741,7 +18774,7 @@
         <v>26</v>
       </c>
       <c r="J168" s="6" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="K168" s="6" t="s">
         <v>211</v>
@@ -18774,10 +18807,10 @@
         <v>756</v>
       </c>
       <c r="U168" s="11" t="s">
+        <v>1266</v>
+      </c>
+      <c r="V168" s="9" t="s">
         <v>1267</v>
-      </c>
-      <c r="V168" s="9" t="s">
-        <v>1268</v>
       </c>
       <c r="W168" s="6" t="s">
         <v>26</v>
@@ -18883,7 +18916,7 @@
         <v>26</v>
       </c>
       <c r="J170" s="6" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="K170" s="6" t="s">
         <v>211</v>
@@ -18916,13 +18949,13 @@
         <v>759</v>
       </c>
       <c r="U170" s="8" t="s">
+        <v>1269</v>
+      </c>
+      <c r="V170" s="9" t="s">
         <v>1270</v>
       </c>
-      <c r="V170" s="9" t="s">
-        <v>1271</v>
-      </c>
       <c r="W170" s="6" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="171" spans="1:23" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -18987,13 +19020,13 @@
         <v>26</v>
       </c>
       <c r="U171" s="8" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="V171" s="9" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="W171" s="6" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="172" spans="1:23" ht="180" x14ac:dyDescent="0.2">
@@ -19025,7 +19058,7 @@
         <v>26</v>
       </c>
       <c r="J172" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K172" s="6" t="s">
         <v>35</v>
@@ -19058,13 +19091,13 @@
         <v>768</v>
       </c>
       <c r="U172" s="11" t="s">
+        <v>1210</v>
+      </c>
+      <c r="V172" s="9" t="s">
         <v>1211</v>
       </c>
-      <c r="V172" s="9" t="s">
-        <v>1212</v>
-      </c>
       <c r="W172" s="6" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="173" spans="1:23" ht="180" x14ac:dyDescent="0.2">
@@ -19129,13 +19162,13 @@
         <v>768</v>
       </c>
       <c r="U173" s="11" t="s">
+        <v>1210</v>
+      </c>
+      <c r="V173" s="9" t="s">
         <v>1211</v>
       </c>
-      <c r="V173" s="9" t="s">
-        <v>1212</v>
-      </c>
       <c r="W173" s="6" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="174" spans="1:23" ht="255" x14ac:dyDescent="0.25">
@@ -19167,7 +19200,7 @@
         <v>26</v>
       </c>
       <c r="J174" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K174" s="6" t="s">
         <v>35</v>
@@ -19203,7 +19236,7 @@
         <v>26</v>
       </c>
       <c r="V174" s="9" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="W174" s="6" t="s">
         <v>26</v>
@@ -19348,7 +19381,7 @@
         <v>26</v>
       </c>
       <c r="W176" s="6" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="177" spans="1:23" ht="210" x14ac:dyDescent="0.25">
@@ -19380,7 +19413,7 @@
         <v>26</v>
       </c>
       <c r="J177" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K177" s="6" t="s">
         <v>35</v>
@@ -19593,7 +19626,7 @@
         <v>26</v>
       </c>
       <c r="J180" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K180" s="6" t="s">
         <v>35</v>
@@ -19626,13 +19659,13 @@
         <v>809</v>
       </c>
       <c r="U180" s="11" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V180" s="9" t="s">
         <v>1274</v>
       </c>
-      <c r="V180" s="9" t="s">
-        <v>1275</v>
-      </c>
       <c r="W180" s="6" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="181" spans="1:23" ht="315" x14ac:dyDescent="0.25">
@@ -19806,7 +19839,7 @@
         <v>26</v>
       </c>
       <c r="J183" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K183" s="6" t="s">
         <v>211</v>
@@ -19839,13 +19872,13 @@
         <v>820</v>
       </c>
       <c r="U183" s="11" t="s">
+        <v>1275</v>
+      </c>
+      <c r="V183" s="9" t="s">
         <v>1276</v>
       </c>
-      <c r="V183" s="9" t="s">
-        <v>1277</v>
-      </c>
       <c r="W183" s="6" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="184" spans="1:23" ht="120" x14ac:dyDescent="0.2">
@@ -19910,13 +19943,13 @@
         <v>820</v>
       </c>
       <c r="U184" s="11" t="s">
+        <v>1275</v>
+      </c>
+      <c r="V184" s="9" t="s">
         <v>1276</v>
       </c>
-      <c r="V184" s="9" t="s">
-        <v>1277</v>
-      </c>
       <c r="W184" s="6" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="185" spans="1:23" ht="45" x14ac:dyDescent="0.25">
@@ -20019,7 +20052,7 @@
         <v>26</v>
       </c>
       <c r="J186" s="6" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="K186" s="6" t="s">
         <v>26</v>
@@ -20058,7 +20091,7 @@
         <v>26</v>
       </c>
       <c r="W186" s="6" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="187" spans="1:23" x14ac:dyDescent="0.25">
@@ -20161,7 +20194,7 @@
         <v>26</v>
       </c>
       <c r="J188" s="6" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="K188" s="6" t="s">
         <v>211</v>
@@ -20194,7 +20227,7 @@
         <v>836</v>
       </c>
       <c r="U188" s="11" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="V188" s="10" t="s">
         <v>26</v>
@@ -20232,7 +20265,7 @@
         <v>26</v>
       </c>
       <c r="J189" s="6" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="K189" s="6" t="s">
         <v>211</v>
@@ -20265,7 +20298,7 @@
         <v>836</v>
       </c>
       <c r="U189" s="11" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="V189" s="10" t="s">
         <v>26</v>
@@ -20407,13 +20440,13 @@
         <v>26</v>
       </c>
       <c r="U191" s="8" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="V191" s="9" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="W191" s="6" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="192" spans="1:23" ht="345" x14ac:dyDescent="0.25">
@@ -20445,7 +20478,7 @@
         <v>26</v>
       </c>
       <c r="J192" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K192" s="6" t="s">
         <v>211</v>
@@ -20481,10 +20514,10 @@
         <v>26</v>
       </c>
       <c r="V192" s="9" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="W192" s="6" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="193" spans="1:23" ht="30" x14ac:dyDescent="0.25">
@@ -20549,10 +20582,10 @@
         <v>26</v>
       </c>
       <c r="U193" s="8" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="V193" s="9" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="W193" s="6" t="s">
         <v>26</v>
@@ -20587,7 +20620,7 @@
         <v>26</v>
       </c>
       <c r="J194" s="6" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="K194" s="6" t="s">
         <v>211</v>
@@ -20620,10 +20653,10 @@
         <v>855</v>
       </c>
       <c r="U194" s="12" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="V194" s="9" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="W194" s="6" t="s">
         <v>26</v>
@@ -20729,7 +20762,7 @@
         <v>26</v>
       </c>
       <c r="J196" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K196" s="6" t="s">
         <v>26</v>
@@ -20762,13 +20795,13 @@
         <v>866</v>
       </c>
       <c r="U196" s="11" t="s">
+        <v>1282</v>
+      </c>
+      <c r="V196" s="9" t="s">
         <v>1283</v>
       </c>
-      <c r="V196" s="9" t="s">
-        <v>1284</v>
-      </c>
       <c r="W196" s="6" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="197" spans="1:23" ht="225" x14ac:dyDescent="0.25">
@@ -20871,7 +20904,7 @@
         <v>466</v>
       </c>
       <c r="J198" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K198" s="6" t="s">
         <v>26</v>
@@ -20904,13 +20937,13 @@
         <v>866</v>
       </c>
       <c r="U198" s="11" t="s">
+        <v>1284</v>
+      </c>
+      <c r="V198" s="9" t="s">
         <v>1285</v>
       </c>
-      <c r="V198" s="9" t="s">
-        <v>1286</v>
-      </c>
       <c r="W198" s="6" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="199" spans="1:23" ht="225" x14ac:dyDescent="0.25">
@@ -21013,7 +21046,7 @@
         <v>26</v>
       </c>
       <c r="J200" s="6" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="K200" s="6" t="s">
         <v>211</v>
@@ -21131,11 +21164,11 @@
         <v>882</v>
       </c>
       <c r="B202" s="6" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C202" s="7" t="s">
         <v>1343</v>
       </c>
-      <c r="C202" s="7" t="s">
-        <v>1344</v>
-      </c>
       <c r="D202" s="6" t="s">
         <v>26</v>
       </c>
@@ -21194,7 +21227,7 @@
         <v>26</v>
       </c>
       <c r="W202" s="6" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="203" spans="1:23" ht="30" x14ac:dyDescent="0.25">
@@ -21202,10 +21235,10 @@
         <v>883</v>
       </c>
       <c r="B203" s="6" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C203" s="7" t="s">
         <v>1343</v>
-      </c>
-      <c r="C203" s="7" t="s">
-        <v>1344</v>
       </c>
       <c r="D203" s="6" t="s">
         <v>26</v>
@@ -21620,7 +21653,7 @@
         <v>26</v>
       </c>
       <c r="W208" s="6" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="209" spans="1:23" ht="30" x14ac:dyDescent="0.25">
@@ -21827,7 +21860,7 @@
         <v>902</v>
       </c>
       <c r="U211" s="11" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="V211" s="10" t="s">
         <v>26</v>
@@ -21898,7 +21931,7 @@
         <v>902</v>
       </c>
       <c r="U212" s="11" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="V212" s="10" t="s">
         <v>26</v>
@@ -22111,10 +22144,10 @@
         <v>919</v>
       </c>
       <c r="U215" s="11" t="s">
+        <v>1287</v>
+      </c>
+      <c r="V215" s="9" t="s">
         <v>1288</v>
-      </c>
-      <c r="V215" s="9" t="s">
-        <v>1289</v>
       </c>
       <c r="W215" s="6" t="s">
         <v>26</v>
@@ -22149,7 +22182,7 @@
         <v>26</v>
       </c>
       <c r="J216" s="6" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="K216" s="6" t="s">
         <v>926</v>
@@ -22182,10 +22215,10 @@
         <v>931</v>
       </c>
       <c r="U216" s="11" t="s">
+        <v>1287</v>
+      </c>
+      <c r="V216" s="9" t="s">
         <v>1288</v>
-      </c>
-      <c r="V216" s="9" t="s">
-        <v>1289</v>
       </c>
       <c r="W216" s="6" t="s">
         <v>26</v>
@@ -22253,10 +22286,10 @@
         <v>902</v>
       </c>
       <c r="U217" s="11" t="s">
+        <v>1287</v>
+      </c>
+      <c r="V217" s="9" t="s">
         <v>1288</v>
-      </c>
-      <c r="V217" s="9" t="s">
-        <v>1289</v>
       </c>
       <c r="W217" s="6" t="s">
         <v>26</v>
@@ -22504,7 +22537,7 @@
         <v>436</v>
       </c>
       <c r="J221" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K221" s="6" t="s">
         <v>943</v>
@@ -22537,10 +22570,10 @@
         <v>950</v>
       </c>
       <c r="U221" s="8" t="s">
+        <v>1289</v>
+      </c>
+      <c r="V221" s="9" t="s">
         <v>1290</v>
-      </c>
-      <c r="V221" s="9" t="s">
-        <v>1291</v>
       </c>
       <c r="W221" s="6" t="s">
         <v>26</v>
@@ -22575,7 +22608,7 @@
         <v>26</v>
       </c>
       <c r="J222" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K222" s="6" t="s">
         <v>147</v>
@@ -22619,7 +22652,7 @@
     </row>
     <row r="223" spans="1:23" ht="405" x14ac:dyDescent="0.25">
       <c r="A223" s="5" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="B223" s="6" t="s">
         <v>954</v>
@@ -22690,7 +22723,7 @@
     </row>
     <row r="224" spans="1:23" ht="405" x14ac:dyDescent="0.25">
       <c r="A224" s="5" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="B224" s="6" t="s">
         <v>954</v>
@@ -22821,13 +22854,13 @@
         <v>26</v>
       </c>
       <c r="U225" s="8" t="s">
+        <v>1291</v>
+      </c>
+      <c r="V225" s="9" t="s">
         <v>1292</v>
       </c>
-      <c r="V225" s="9" t="s">
-        <v>1293</v>
-      </c>
       <c r="W225" s="6" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="226" spans="1:23" ht="255" x14ac:dyDescent="0.25">
@@ -22859,7 +22892,7 @@
         <v>211</v>
       </c>
       <c r="J226" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K226" s="6" t="s">
         <v>211</v>
@@ -22892,13 +22925,13 @@
         <v>969</v>
       </c>
       <c r="U226" s="8" t="s">
+        <v>1293</v>
+      </c>
+      <c r="V226" s="9" t="s">
         <v>1294</v>
       </c>
-      <c r="V226" s="9" t="s">
-        <v>1295</v>
-      </c>
       <c r="W226" s="6" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="227" spans="1:23" ht="255" x14ac:dyDescent="0.25">
@@ -23001,7 +23034,7 @@
         <v>26</v>
       </c>
       <c r="J228" s="6" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="K228" s="6" t="s">
         <v>26</v>
@@ -23034,7 +23067,7 @@
         <v>977</v>
       </c>
       <c r="U228" s="8" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="V228" s="10" t="s">
         <v>26</v>
@@ -23111,7 +23144,7 @@
         <v>26</v>
       </c>
       <c r="W229" s="6" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="230" spans="1:23" ht="120" x14ac:dyDescent="0.25">
@@ -23173,7 +23206,7 @@
         <v>26</v>
       </c>
       <c r="T230" s="6" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="U230" s="6" t="s">
         <v>26</v>
@@ -23182,7 +23215,7 @@
         <v>26</v>
       </c>
       <c r="W230" s="6" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="231" spans="1:23" ht="150" x14ac:dyDescent="0.25">
@@ -23190,7 +23223,7 @@
         <v>980</v>
       </c>
       <c r="B231" s="6" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="C231" s="7" t="s">
         <v>114</v>
@@ -23244,13 +23277,13 @@
         <v>26</v>
       </c>
       <c r="T231" s="6" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="U231" s="8" t="s">
+        <v>1296</v>
+      </c>
+      <c r="V231" s="9" t="s">
         <v>1297</v>
-      </c>
-      <c r="V231" s="9" t="s">
-        <v>1298</v>
       </c>
       <c r="W231" s="6" t="s">
         <v>26</v>
@@ -23318,13 +23351,13 @@
         <v>987</v>
       </c>
       <c r="U232" s="11" t="s">
+        <v>1300</v>
+      </c>
+      <c r="V232" s="9" t="s">
         <v>1301</v>
       </c>
-      <c r="V232" s="9" t="s">
-        <v>1302</v>
-      </c>
       <c r="W232" s="6" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="233" spans="1:23" ht="210" x14ac:dyDescent="0.2">
@@ -23389,13 +23422,13 @@
         <v>987</v>
       </c>
       <c r="U233" s="11" t="s">
+        <v>1300</v>
+      </c>
+      <c r="V233" s="9" t="s">
         <v>1301</v>
       </c>
-      <c r="V233" s="9" t="s">
-        <v>1302</v>
-      </c>
       <c r="W233" s="6" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="234" spans="1:23" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -23427,7 +23460,7 @@
         <v>26</v>
       </c>
       <c r="J234" s="6" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="K234" s="6" t="s">
         <v>147</v>
@@ -23460,13 +23493,13 @@
         <v>996</v>
       </c>
       <c r="U234" s="14" t="s">
+        <v>1302</v>
+      </c>
+      <c r="V234" s="9" t="s">
         <v>1303</v>
       </c>
-      <c r="V234" s="9" t="s">
-        <v>1304</v>
-      </c>
       <c r="W234" s="6" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="235" spans="1:23" ht="30" x14ac:dyDescent="0.25">
@@ -23569,7 +23602,7 @@
         <v>26</v>
       </c>
       <c r="J236" s="6" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="K236" s="6" t="s">
         <v>211</v>
@@ -23602,13 +23635,13 @@
         <v>1005</v>
       </c>
       <c r="U236" s="11" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="V236" s="10" t="s">
         <v>26</v>
       </c>
       <c r="W236" s="6" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="237" spans="1:23" ht="240" x14ac:dyDescent="0.2">
@@ -23673,13 +23706,13 @@
         <v>1005</v>
       </c>
       <c r="U237" s="11" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="V237" s="10" t="s">
         <v>26</v>
       </c>
       <c r="W237" s="6" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="238" spans="1:23" ht="240" x14ac:dyDescent="0.25">
@@ -23711,7 +23744,7 @@
         <v>26</v>
       </c>
       <c r="J238" s="6" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="K238" s="6" t="s">
         <v>211</v>
@@ -23744,13 +23777,13 @@
         <v>1005</v>
       </c>
       <c r="U238" s="8" t="s">
+        <v>1304</v>
+      </c>
+      <c r="V238" s="9" t="s">
         <v>1305</v>
       </c>
-      <c r="V238" s="9" t="s">
-        <v>1306</v>
-      </c>
       <c r="W238" s="6" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="239" spans="1:23" ht="240" x14ac:dyDescent="0.25">
@@ -23815,13 +23848,13 @@
         <v>1005</v>
       </c>
       <c r="U239" s="8" t="s">
+        <v>1304</v>
+      </c>
+      <c r="V239" s="9" t="s">
         <v>1305</v>
       </c>
-      <c r="V239" s="9" t="s">
-        <v>1306</v>
-      </c>
       <c r="W239" s="6" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="240" spans="1:23" ht="30" x14ac:dyDescent="0.25">
@@ -23995,7 +24028,7 @@
         <v>26</v>
       </c>
       <c r="J242" s="6" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="K242" s="6" t="s">
         <v>35</v>
@@ -24028,10 +24061,10 @@
         <v>1017</v>
       </c>
       <c r="U242" s="8" t="s">
+        <v>1306</v>
+      </c>
+      <c r="V242" s="9" t="s">
         <v>1307</v>
-      </c>
-      <c r="V242" s="9" t="s">
-        <v>1308</v>
       </c>
       <c r="W242" s="6" t="s">
         <v>26</v>
@@ -24099,10 +24132,10 @@
         <v>1017</v>
       </c>
       <c r="U243" s="8" t="s">
+        <v>1306</v>
+      </c>
+      <c r="V243" s="9" t="s">
         <v>1307</v>
-      </c>
-      <c r="V243" s="9" t="s">
-        <v>1308</v>
       </c>
       <c r="W243" s="6" t="s">
         <v>26</v>
@@ -24184,7 +24217,7 @@
         <v>1021</v>
       </c>
       <c r="B245" s="6" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="C245" s="7" t="s">
         <v>701</v>
@@ -24247,7 +24280,7 @@
         <v>26</v>
       </c>
       <c r="W245" s="6" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="246" spans="1:23" ht="45" x14ac:dyDescent="0.25">
@@ -24255,7 +24288,7 @@
         <v>1022</v>
       </c>
       <c r="B246" s="6" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="C246" s="7" t="s">
         <v>701</v>
@@ -24318,7 +24351,7 @@
         <v>26</v>
       </c>
       <c r="W246" s="6" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="247" spans="1:23" ht="103.9" customHeight="1" x14ac:dyDescent="0.25">
@@ -24326,7 +24359,7 @@
         <v>1023</v>
       </c>
       <c r="B247" s="6" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="C247" s="7" t="s">
         <v>74</v>
@@ -24389,7 +24422,7 @@
         <v>26</v>
       </c>
       <c r="W247" s="6" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="248" spans="1:23" ht="75" x14ac:dyDescent="0.25">
@@ -24610,7 +24643,7 @@
         <v>1027</v>
       </c>
       <c r="B251" s="6" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="C251" s="7" t="s">
         <v>54</v>
@@ -24681,10 +24714,10 @@
         <v>1028</v>
       </c>
       <c r="B252" s="6" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="C252" s="7" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D252" s="6" t="s">
         <v>26</v>
@@ -24752,10 +24785,10 @@
         <v>1029</v>
       </c>
       <c r="B253" s="6" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="C253" s="7" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="D253" s="6" t="s">
         <v>26</v>
@@ -25096,10 +25129,10 @@
         <v>26</v>
       </c>
       <c r="V257" s="9" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="W257" s="6" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="258" spans="1:23" ht="90" x14ac:dyDescent="0.25">
@@ -25167,10 +25200,10 @@
         <v>26</v>
       </c>
       <c r="V258" s="9" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="W258" s="6" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="259" spans="1:23" ht="94.5" x14ac:dyDescent="0.25">
@@ -25202,7 +25235,7 @@
         <v>492</v>
       </c>
       <c r="J259" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K259" s="6" t="s">
         <v>26</v>
@@ -25235,13 +25268,13 @@
         <v>26</v>
       </c>
       <c r="U259" s="8" t="s">
+        <v>1309</v>
+      </c>
+      <c r="V259" s="9" t="s">
         <v>1310</v>
       </c>
-      <c r="V259" s="9" t="s">
-        <v>1311</v>
-      </c>
       <c r="W259" s="6" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="260" spans="1:23" x14ac:dyDescent="0.25">
@@ -25462,10 +25495,10 @@
         <v>1044</v>
       </c>
       <c r="B263" s="6" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C263" s="6" t="s">
         <v>1351</v>
-      </c>
-      <c r="C263" s="6" t="s">
-        <v>1352</v>
       </c>
       <c r="D263" s="6" t="s">
         <v>26</v>
@@ -25658,16 +25691,16 @@
         <v>26</v>
       </c>
       <c r="T265" s="6" t="s">
+        <v>1311</v>
+      </c>
+      <c r="U265" s="8" t="s">
         <v>1312</v>
       </c>
-      <c r="U265" s="8" t="s">
+      <c r="V265" s="9" t="s">
         <v>1313</v>
       </c>
-      <c r="V265" s="9" t="s">
-        <v>1314</v>
-      </c>
       <c r="W265" s="6" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="266" spans="1:23" x14ac:dyDescent="0.25">
@@ -25770,7 +25803,7 @@
         <v>1052</v>
       </c>
       <c r="J267" s="6" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="K267" s="6" t="s">
         <v>147</v>
@@ -25800,13 +25833,13 @@
         <v>26</v>
       </c>
       <c r="T267" s="6" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="U267" s="8" t="s">
+        <v>1314</v>
+      </c>
+      <c r="V267" s="9" t="s">
         <v>1315</v>
-      </c>
-      <c r="V267" s="9" t="s">
-        <v>1316</v>
       </c>
       <c r="W267" s="6" t="s">
         <v>26</v>
@@ -25871,7 +25904,7 @@
         <v>26</v>
       </c>
       <c r="T268" s="6" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="U268" s="6" t="s">
         <v>26</v>
@@ -25912,7 +25945,7 @@
         <v>26</v>
       </c>
       <c r="J269" s="6" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="K269" s="6" t="s">
         <v>1061</v>
@@ -25945,13 +25978,13 @@
         <v>1067</v>
       </c>
       <c r="U269" s="8" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="V269" s="10" t="s">
         <v>26</v>
       </c>
       <c r="W269" s="6" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="270" spans="1:23" ht="195" x14ac:dyDescent="0.25">
@@ -25983,7 +26016,7 @@
         <v>26</v>
       </c>
       <c r="J270" s="6" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="K270" s="6" t="s">
         <v>1061</v>
@@ -26016,13 +26049,13 @@
         <v>1067</v>
       </c>
       <c r="U270" s="8" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="V270" s="10" t="s">
         <v>26</v>
       </c>
       <c r="W270" s="6" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="271" spans="1:23" ht="45" x14ac:dyDescent="0.25">
@@ -26125,7 +26158,7 @@
         <v>26</v>
       </c>
       <c r="J272" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K272" s="6" t="s">
         <v>147</v>
@@ -26158,7 +26191,7 @@
         <v>26</v>
       </c>
       <c r="U272" s="8" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="V272" s="10" t="s">
         <v>26</v>
@@ -26267,7 +26300,7 @@
         <v>26</v>
       </c>
       <c r="J274" s="6" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="K274" s="6" t="s">
         <v>147</v>
@@ -26338,7 +26371,7 @@
         <v>26</v>
       </c>
       <c r="J275" s="6" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="K275" s="6" t="s">
         <v>147</v>
@@ -26409,7 +26442,7 @@
         <v>26</v>
       </c>
       <c r="J276" s="6" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="K276" s="6" t="s">
         <v>1098</v>
@@ -26442,7 +26475,7 @@
         <v>26</v>
       </c>
       <c r="U276" s="8" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="V276" s="10" t="s">
         <v>26</v>
@@ -26513,7 +26546,7 @@
         <v>26</v>
       </c>
       <c r="U277" s="8" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="V277" s="10" t="s">
         <v>26</v>
@@ -26551,7 +26584,7 @@
         <v>26</v>
       </c>
       <c r="J278" s="6" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="K278" s="6" t="s">
         <v>1111</v>
@@ -26581,10 +26614,10 @@
         <v>1115</v>
       </c>
       <c r="T278" s="6" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="U278" s="8" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="V278" s="10" t="s">
         <v>26</v>
@@ -26622,7 +26655,7 @@
         <v>26</v>
       </c>
       <c r="J279" s="6" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="K279" s="6" t="s">
         <v>492</v>
@@ -26640,7 +26673,7 @@
         <v>1120</v>
       </c>
       <c r="P279" s="6" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="Q279" s="6" t="s">
         <v>1121</v>
@@ -26655,10 +26688,10 @@
         <v>26</v>
       </c>
       <c r="U279" s="8" t="s">
+        <v>1322</v>
+      </c>
+      <c r="V279" s="9" t="s">
         <v>1323</v>
-      </c>
-      <c r="V279" s="9" t="s">
-        <v>1324</v>
       </c>
       <c r="W279" s="6" t="s">
         <v>26</v>
@@ -26732,7 +26765,7 @@
         <v>26</v>
       </c>
       <c r="W280" s="6" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="281" spans="1:23" ht="30" x14ac:dyDescent="0.25">
@@ -26874,7 +26907,7 @@
         <v>26</v>
       </c>
       <c r="W282" s="6" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="283" spans="1:23" ht="90" x14ac:dyDescent="0.25">
@@ -26882,10 +26915,10 @@
         <v>1129</v>
       </c>
       <c r="B283" s="6" t="s">
-        <v>1130</v>
+        <v>1494</v>
       </c>
       <c r="C283" s="7" t="s">
-        <v>54</v>
+        <v>241</v>
       </c>
       <c r="D283" s="6" t="s">
         <v>25</v>
@@ -26894,69 +26927,69 @@
         <v>224</v>
       </c>
       <c r="F283" s="6" t="s">
-        <v>26</v>
+        <v>1489</v>
       </c>
       <c r="G283" s="6" t="s">
+        <v>1130</v>
+      </c>
+      <c r="H283" s="6" t="s">
+        <v>1486</v>
+      </c>
+      <c r="I283" s="6" t="s">
+        <v>1495</v>
+      </c>
+      <c r="J283" s="6" t="s">
+        <v>1497</v>
+      </c>
+      <c r="K283" s="6" t="s">
+        <v>1496</v>
+      </c>
+      <c r="L283" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="M283" s="6" t="s">
         <v>1131</v>
       </c>
-      <c r="H283" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I283" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="J283" s="6" t="s">
-        <v>1384</v>
-      </c>
-      <c r="K283" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L283" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M283" s="6" t="s">
+      <c r="N283" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O283" s="6" t="s">
         <v>1132</v>
       </c>
-      <c r="N283" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O283" s="6" t="s">
+      <c r="P283" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q283" s="6" t="s">
         <v>1133</v>
       </c>
-      <c r="P283" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q283" s="6" t="s">
+      <c r="R283" s="6" t="s">
         <v>1134</v>
       </c>
-      <c r="R283" s="6" t="s">
-        <v>1135</v>
-      </c>
       <c r="S283" s="6" t="s">
         <v>26</v>
       </c>
       <c r="T283" s="6" t="s">
-        <v>26</v>
+        <v>1493</v>
       </c>
       <c r="U283" s="8" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="V283" s="10" t="s">
         <v>26</v>
       </c>
       <c r="W283" s="6" t="s">
-        <v>1463</v>
-      </c>
-    </row>
-    <row r="284" spans="1:23" x14ac:dyDescent="0.25">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="284" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A284" s="5" t="s">
         <v>1129</v>
       </c>
       <c r="B284" s="6" t="s">
-        <v>1130</v>
+        <v>1494</v>
       </c>
       <c r="C284" s="7" t="s">
-        <v>54</v>
+        <v>241</v>
       </c>
       <c r="D284" s="6" t="s">
         <v>76</v>
@@ -26965,10 +26998,10 @@
         <v>224</v>
       </c>
       <c r="F284" s="6" t="s">
-        <v>26</v>
+        <v>1489</v>
       </c>
       <c r="G284" s="6" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H284" s="6" t="s">
         <v>26</v>
@@ -27007,7 +27040,7 @@
         <v>26</v>
       </c>
       <c r="T284" s="6" t="s">
-        <v>26</v>
+        <v>1493</v>
       </c>
       <c r="U284" s="6" t="s">
         <v>26</v>
@@ -27019,15 +27052,15 @@
         <v>26</v>
       </c>
     </row>
-    <row r="285" spans="1:23" ht="63" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:23" ht="90" x14ac:dyDescent="0.25">
       <c r="A285" s="5" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B285" s="6" t="s">
-        <v>1130</v>
+        <v>26</v>
       </c>
       <c r="C285" s="7" t="s">
-        <v>54</v>
+        <v>952</v>
       </c>
       <c r="D285" s="6" t="s">
         <v>25</v>
@@ -27036,69 +27069,69 @@
         <v>224</v>
       </c>
       <c r="F285" s="6" t="s">
-        <v>26</v>
+        <v>1489</v>
       </c>
       <c r="G285" s="6" t="s">
-        <v>26</v>
+        <v>1130</v>
       </c>
       <c r="H285" s="6" t="s">
-        <v>26</v>
+        <v>1486</v>
       </c>
       <c r="I285" s="6" t="s">
-        <v>26</v>
+        <v>1487</v>
       </c>
       <c r="J285" s="6" t="s">
-        <v>26</v>
+        <v>1492</v>
       </c>
       <c r="K285" s="6" t="s">
-        <v>26</v>
+        <v>449</v>
       </c>
       <c r="L285" s="6" t="s">
-        <v>26</v>
+        <v>1488</v>
       </c>
       <c r="M285" s="6" t="s">
-        <v>26</v>
+        <v>1490</v>
       </c>
       <c r="N285" s="6" t="s">
         <v>26</v>
       </c>
       <c r="O285" s="6" t="s">
-        <v>26</v>
+        <v>1132</v>
       </c>
       <c r="P285" s="6" t="s">
         <v>26</v>
       </c>
       <c r="Q285" s="6" t="s">
-        <v>26</v>
+        <v>1133</v>
       </c>
       <c r="R285" s="6" t="s">
-        <v>26</v>
+        <v>1491</v>
       </c>
       <c r="S285" s="6" t="s">
         <v>26</v>
       </c>
       <c r="T285" s="6" t="s">
-        <v>26</v>
+        <v>1493</v>
       </c>
       <c r="U285" s="8" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="V285" s="10" t="s">
         <v>26</v>
       </c>
       <c r="W285" s="6" t="s">
-        <v>1463</v>
-      </c>
-    </row>
-    <row r="286" spans="1:23" x14ac:dyDescent="0.25">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="286" spans="1:23" ht="90" x14ac:dyDescent="0.25">
       <c r="A286" s="5" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B286" s="6" t="s">
-        <v>1130</v>
+        <v>26</v>
       </c>
       <c r="C286" s="7" t="s">
-        <v>54</v>
+        <v>952</v>
       </c>
       <c r="D286" s="6" t="s">
         <v>76</v>
@@ -27107,10 +27140,10 @@
         <v>224</v>
       </c>
       <c r="F286" s="6" t="s">
-        <v>26</v>
+        <v>1489</v>
       </c>
       <c r="G286" s="6" t="s">
-        <v>26</v>
+        <v>1130</v>
       </c>
       <c r="H286" s="6" t="s">
         <v>26</v>
@@ -27134,7 +27167,7 @@
         <v>26</v>
       </c>
       <c r="O286" s="6" t="s">
-        <v>26</v>
+        <v>1132</v>
       </c>
       <c r="P286" s="6" t="s">
         <v>26</v>
@@ -27149,7 +27182,7 @@
         <v>26</v>
       </c>
       <c r="T286" s="6" t="s">
-        <v>26</v>
+        <v>1493</v>
       </c>
       <c r="U286" s="6" t="s">
         <v>26</v>
@@ -27163,7 +27196,7 @@
     </row>
     <row r="287" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A287" s="5" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="B287" s="6" t="s">
         <v>26</v>
@@ -27181,7 +27214,7 @@
         <v>26</v>
       </c>
       <c r="G287" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H287" s="6" t="s">
         <v>638</v>
@@ -27199,19 +27232,19 @@
         <v>26</v>
       </c>
       <c r="M287" s="6" t="s">
+        <v>1138</v>
+      </c>
+      <c r="N287" s="6" t="s">
+        <v>1138</v>
+      </c>
+      <c r="O287" s="6" t="s">
         <v>1139</v>
       </c>
-      <c r="N287" s="6" t="s">
-        <v>1139</v>
-      </c>
-      <c r="O287" s="6" t="s">
+      <c r="P287" s="6" t="s">
         <v>1140</v>
       </c>
-      <c r="P287" s="6" t="s">
+      <c r="Q287" s="6" t="s">
         <v>1141</v>
-      </c>
-      <c r="Q287" s="6" t="s">
-        <v>1142</v>
       </c>
       <c r="R287" s="6" t="s">
         <v>51</v>
@@ -27220,7 +27253,7 @@
         <v>51</v>
       </c>
       <c r="T287" s="6" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="U287" s="6" t="s">
         <v>26</v>
@@ -27234,7 +27267,7 @@
     </row>
     <row r="288" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A288" s="5" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="B288" s="6" t="s">
         <v>26</v>
@@ -27252,7 +27285,7 @@
         <v>26</v>
       </c>
       <c r="G288" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H288" s="6" t="s">
         <v>638</v>
@@ -27270,16 +27303,16 @@
         <v>26</v>
       </c>
       <c r="M288" s="6" t="s">
+        <v>1138</v>
+      </c>
+      <c r="N288" s="6" t="s">
+        <v>1138</v>
+      </c>
+      <c r="O288" s="6" t="s">
         <v>1139</v>
       </c>
-      <c r="N288" s="6" t="s">
-        <v>1139</v>
-      </c>
-      <c r="O288" s="6" t="s">
+      <c r="P288" s="6" t="s">
         <v>1140</v>
-      </c>
-      <c r="P288" s="6" t="s">
-        <v>1141</v>
       </c>
       <c r="Q288" s="6" t="s">
         <v>26</v>
@@ -27291,7 +27324,7 @@
         <v>51</v>
       </c>
       <c r="T288" s="6" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="U288" s="6" t="s">
         <v>26</v>
@@ -27305,7 +27338,7 @@
     </row>
     <row r="289" spans="1:23" ht="63" x14ac:dyDescent="0.25">
       <c r="A289" s="5" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B289" s="6" t="s">
         <v>26</v>
@@ -27332,7 +27365,7 @@
         <v>26</v>
       </c>
       <c r="J289" s="6" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="K289" s="6" t="s">
         <v>436</v>
@@ -27347,17 +27380,17 @@
         <v>26</v>
       </c>
       <c r="O289" s="6" t="s">
+        <v>1144</v>
+      </c>
+      <c r="P289" s="6" t="s">
         <v>1145</v>
       </c>
-      <c r="P289" s="6" t="s">
+      <c r="Q289" s="6" t="s">
         <v>1146</v>
       </c>
-      <c r="Q289" s="6" t="s">
+      <c r="R289" s="6" t="s">
         <v>1147</v>
       </c>
-      <c r="R289" s="6" t="s">
-        <v>1148</v>
-      </c>
       <c r="S289" s="6" t="s">
         <v>26</v>
       </c>
@@ -27365,10 +27398,10 @@
         <v>26</v>
       </c>
       <c r="U289" s="8" t="s">
+        <v>1324</v>
+      </c>
+      <c r="V289" s="9" t="s">
         <v>1325</v>
-      </c>
-      <c r="V289" s="9" t="s">
-        <v>1326</v>
       </c>
       <c r="W289" s="6" t="s">
         <v>26</v>
@@ -27376,7 +27409,7 @@
     </row>
     <row r="290" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A290" s="5" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="B290" s="6" t="s">
         <v>26</v>
@@ -27447,10 +27480,10 @@
     </row>
     <row r="291" spans="1:23" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A291" s="5" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B291" s="6" t="s">
         <v>1150</v>
-      </c>
-      <c r="B291" s="6" t="s">
-        <v>1151</v>
       </c>
       <c r="C291" s="7" t="s">
         <v>1049</v>
@@ -27459,13 +27492,13 @@
         <v>25</v>
       </c>
       <c r="E291" s="6" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="F291" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G291" s="6" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H291" s="6" t="s">
         <v>638</v>
@@ -27474,7 +27507,7 @@
         <v>638</v>
       </c>
       <c r="J291" s="6" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="K291" s="6" t="s">
         <v>26</v>
@@ -27483,16 +27516,16 @@
         <v>26</v>
       </c>
       <c r="M291" s="6" t="s">
+        <v>1152</v>
+      </c>
+      <c r="N291" s="6" t="s">
+        <v>1138</v>
+      </c>
+      <c r="O291" s="6" t="s">
         <v>1153</v>
       </c>
-      <c r="N291" s="6" t="s">
-        <v>1139</v>
-      </c>
-      <c r="O291" s="6" t="s">
+      <c r="P291" s="6" t="s">
         <v>1154</v>
-      </c>
-      <c r="P291" s="6" t="s">
-        <v>1155</v>
       </c>
       <c r="Q291" s="6" t="s">
         <v>598</v>
@@ -27501,16 +27534,16 @@
         <v>51</v>
       </c>
       <c r="S291" s="6" t="s">
+        <v>1155</v>
+      </c>
+      <c r="T291" s="6" t="s">
         <v>1156</v>
       </c>
-      <c r="T291" s="6" t="s">
-        <v>1157</v>
-      </c>
       <c r="U291" s="8" t="s">
+        <v>1326</v>
+      </c>
+      <c r="V291" s="9" t="s">
         <v>1327</v>
-      </c>
-      <c r="V291" s="9" t="s">
-        <v>1328</v>
       </c>
       <c r="W291" s="6" t="s">
         <v>26</v>
@@ -27518,7 +27551,7 @@
     </row>
     <row r="292" spans="1:23" ht="64.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="5" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="B292" s="6"/>
       <c r="C292" s="7"/>
@@ -27580,15 +27613,15 @@
         <v>26</v>
       </c>
       <c r="W292" s="6" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="293" spans="1:23" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="5" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B293" s="6" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="C293" s="7" t="s">
         <v>1049</v>
@@ -27656,10 +27689,10 @@
     </row>
     <row r="294" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A294" s="5" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B294" s="6" t="s">
         <v>1160</v>
-      </c>
-      <c r="B294" s="6" t="s">
-        <v>1161</v>
       </c>
       <c r="C294" s="7" t="s">
         <v>114</v>
@@ -27727,7 +27760,7 @@
     </row>
     <row r="295" spans="1:23" ht="210" x14ac:dyDescent="0.25">
       <c r="A295" s="5" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B295" s="6" t="s">
         <v>26</v>
@@ -27742,43 +27775,43 @@
         <v>446</v>
       </c>
       <c r="F295" s="6" t="s">
+        <v>1162</v>
+      </c>
+      <c r="G295" s="6" t="s">
         <v>1163</v>
-      </c>
-      <c r="G295" s="6" t="s">
-        <v>1164</v>
       </c>
       <c r="H295" s="6" t="s">
         <v>147</v>
       </c>
       <c r="I295" s="6" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="J295" s="6" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="K295" s="6" t="s">
         <v>147</v>
       </c>
       <c r="L295" s="6" t="s">
+        <v>1164</v>
+      </c>
+      <c r="M295" s="6" t="s">
         <v>1165</v>
       </c>
-      <c r="M295" s="6" t="s">
+      <c r="N295" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O295" s="6" t="s">
         <v>1166</v>
       </c>
-      <c r="N295" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O295" s="6" t="s">
+      <c r="P295" s="6" t="s">
         <v>1167</v>
       </c>
-      <c r="P295" s="6" t="s">
+      <c r="Q295" s="6" t="s">
         <v>1168</v>
       </c>
-      <c r="Q295" s="6" t="s">
+      <c r="R295" s="6" t="s">
         <v>1169</v>
-      </c>
-      <c r="R295" s="6" t="s">
-        <v>1170</v>
       </c>
       <c r="S295" s="6" t="s">
         <v>791</v>
@@ -27787,24 +27820,24 @@
         <v>26</v>
       </c>
       <c r="U295" s="8" t="s">
+        <v>1328</v>
+      </c>
+      <c r="V295" s="9" t="s">
         <v>1329</v>
       </c>
-      <c r="V295" s="9" t="s">
-        <v>1330</v>
-      </c>
       <c r="W295" s="6" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="296" spans="1:23" ht="63" x14ac:dyDescent="0.25">
       <c r="A296" s="5" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B296" s="6" t="s">
         <v>1171</v>
       </c>
-      <c r="B296" s="6" t="s">
+      <c r="C296" s="7" t="s">
         <v>1172</v>
-      </c>
-      <c r="C296" s="7" t="s">
-        <v>1173</v>
       </c>
       <c r="D296" s="6" t="s">
         <v>25</v>
@@ -27825,7 +27858,7 @@
         <v>26</v>
       </c>
       <c r="J296" s="6" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="K296" s="6" t="s">
         <v>638</v>
@@ -27834,34 +27867,34 @@
         <v>638</v>
       </c>
       <c r="M296" s="6" t="s">
+        <v>1173</v>
+      </c>
+      <c r="N296" s="6" t="s">
         <v>1174</v>
       </c>
-      <c r="N296" s="6" t="s">
+      <c r="O296" s="6" t="s">
         <v>1175</v>
       </c>
-      <c r="O296" s="6" t="s">
+      <c r="P296" s="6" t="s">
         <v>1176</v>
       </c>
-      <c r="P296" s="6" t="s">
+      <c r="Q296" s="6" t="s">
         <v>1177</v>
       </c>
-      <c r="Q296" s="6" t="s">
+      <c r="R296" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="S296" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="T296" s="6" t="s">
         <v>1178</v>
       </c>
-      <c r="R296" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="S296" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="T296" s="6" t="s">
-        <v>1179</v>
-      </c>
       <c r="U296" s="8" t="s">
+        <v>1330</v>
+      </c>
+      <c r="V296" s="9" t="s">
         <v>1331</v>
-      </c>
-      <c r="V296" s="9" t="s">
-        <v>1332</v>
       </c>
       <c r="W296" s="6" t="s">
         <v>26</v>
@@ -27869,10 +27902,10 @@
     </row>
     <row r="297" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A297" s="5" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B297" s="6" t="s">
         <v>1180</v>
-      </c>
-      <c r="B297" s="6" t="s">
-        <v>1181</v>
       </c>
       <c r="C297" s="7" t="s">
         <v>777</v>
@@ -27896,7 +27929,7 @@
         <v>26</v>
       </c>
       <c r="J297" s="6" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="K297" s="6" t="s">
         <v>147</v>
@@ -27911,22 +27944,22 @@
         <v>26</v>
       </c>
       <c r="O297" s="6" t="s">
+        <v>1181</v>
+      </c>
+      <c r="P297" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q297" s="6" t="s">
         <v>1182</v>
       </c>
-      <c r="P297" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q297" s="6" t="s">
+      <c r="R297" s="6" t="s">
         <v>1183</v>
       </c>
-      <c r="R297" s="6" t="s">
+      <c r="S297" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="T297" s="6" t="s">
         <v>1184</v>
-      </c>
-      <c r="S297" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="T297" s="6" t="s">
-        <v>1185</v>
       </c>
       <c r="U297" s="6" t="s">
         <v>26</v>
@@ -27940,10 +27973,10 @@
     </row>
     <row r="298" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A298" s="5" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B298" s="6" t="s">
         <v>1180</v>
-      </c>
-      <c r="B298" s="6" t="s">
-        <v>1181</v>
       </c>
       <c r="C298" s="7" t="s">
         <v>777</v>
@@ -27982,7 +28015,7 @@
         <v>26</v>
       </c>
       <c r="O298" s="6" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="P298" s="6" t="s">
         <v>26</v>
@@ -27991,13 +28024,13 @@
         <v>26</v>
       </c>
       <c r="R298" s="6" t="s">
+        <v>1183</v>
+      </c>
+      <c r="S298" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="T298" s="6" t="s">
         <v>1184</v>
-      </c>
-      <c r="S298" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="T298" s="6" t="s">
-        <v>1185</v>
       </c>
       <c r="U298" s="6" t="s">
         <v>26</v>
@@ -28011,25 +28044,25 @@
     </row>
     <row r="299" spans="1:23" ht="75" x14ac:dyDescent="0.25">
       <c r="A299" s="15" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B299" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C299" s="17" t="s">
         <v>1187</v>
-      </c>
-      <c r="B299" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C299" s="17" t="s">
-        <v>1188</v>
       </c>
       <c r="D299" s="16" t="s">
         <v>25</v>
       </c>
       <c r="E299" s="16" t="s">
+        <v>1188</v>
+      </c>
+      <c r="F299" s="16" t="s">
         <v>1189</v>
       </c>
-      <c r="F299" s="16" t="s">
-        <v>1190</v>
-      </c>
       <c r="G299" s="16" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="H299" s="16" t="s">
         <v>26</v>
@@ -28038,7 +28071,7 @@
         <v>147</v>
       </c>
       <c r="J299" s="16" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="K299" s="16" t="s">
         <v>26</v>
@@ -28047,28 +28080,28 @@
         <v>147</v>
       </c>
       <c r="M299" s="16" t="s">
+        <v>1190</v>
+      </c>
+      <c r="N299" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="O299" s="16" t="s">
         <v>1191</v>
       </c>
-      <c r="N299" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="O299" s="16" t="s">
+      <c r="P299" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q299" s="16" t="s">
         <v>1192</v>
       </c>
-      <c r="P299" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q299" s="16" t="s">
+      <c r="R299" s="16" t="s">
         <v>1193</v>
       </c>
-      <c r="R299" s="16" t="s">
+      <c r="S299" s="16" t="s">
         <v>1194</v>
       </c>
-      <c r="S299" s="16" t="s">
+      <c r="T299" s="16" t="s">
         <v>1195</v>
-      </c>
-      <c r="T299" s="16" t="s">
-        <v>1196</v>
       </c>
       <c r="U299" s="16" t="s">
         <v>26</v>
